--- a/watch-microbrand-database.xlsx
+++ b/watch-microbrand-database.xlsx
@@ -469,35 +469,35 @@
       <c r="C2" t="str">
         <v>Paris</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
+      <c r="D2">
+        <v>2024</v>
+      </c>
+      <c r="E2">
+        <v>1703</v>
+      </c>
+      <c r="F2">
+        <v>1919</v>
       </c>
       <c r="G2" t="str">
         <v>Active</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>2026 Millésime (Edmond &amp; Arsène)</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>2026-04-02</v>
       </c>
       <c r="J2" t="str">
-        <v>https://www.1977watches.com</v>
+        <v>https://www.montres1977.com</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>1977montres</v>
       </c>
       <c r="L2" t="str">
         <v>existing-db</v>
       </c>
       <c r="M2" t="str">
-        <v>French micro-brand based in Paris. Founded 2019. Retro-inspired designs with strong vintage aesthetic. Swiss-assembled. Visitability unconfirmed.</v>
+        <v>French watch brand launched October 2024 (pre-orders) as a standalone spin-off of the Pierre Lannier family watchmaking house, based in Ernolsheim-lès-Saverne, Alsace. Offers two collections — Edmond (classic leather) and Arsène (sporty 904L steel/FKM) — produced in limited annual Millésimes of 99 numbered pieces each, powered by a 100% French France Ébauches automatic caliber and certified Origine France Garantie. Prices range from €1,577–€1,777 (~$1,703–$1,919 USD at ~1.08 EUR/USD).</v>
       </c>
     </row>
     <row r="3">
@@ -510,23 +510,23 @@
       <c r="C3" t="str">
         <v>Budapest, Hungary</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
+      <c r="D3">
+        <v>2007</v>
+      </c>
+      <c r="E3">
+        <v>65000</v>
+      </c>
+      <c r="F3">
+        <v>265000</v>
       </c>
       <c r="G3" t="str">
         <v>Active</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Dignitas Pure "Project XX"</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>2026-02-01</v>
       </c>
       <c r="J3" t="str">
         <v>https://www.bexei.hu</v>
@@ -552,34 +552,34 @@
         <v>Paris</v>
       </c>
       <c r="D4">
-        <v>2022</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
+        <v>2024</v>
+      </c>
+      <c r="E4">
+        <v>2430</v>
+      </c>
+      <c r="F4">
+        <v>2700</v>
       </c>
       <c r="G4" t="str">
         <v>Active</v>
       </c>
       <c r="H4" t="str">
-        <v>1712</v>
+        <v>1712 Glaz</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>2025-04-01</v>
       </c>
       <c r="J4" t="str">
         <v>https://www.abordage-horlogerie.com</v>
       </c>
       <c r="K4" t="str">
-        <v>nobox.nopapers</v>
+        <v>abordage_horlogerie</v>
       </c>
       <c r="L4" t="str">
         <v>existing-db</v>
       </c>
       <c r="M4" t="str">
-        <v>French independent with nautical and sailing heritage. Known for robust field and maritime watches. Based in Paris. Visitability unconfirmed.</v>
+        <v>French microbrand founded in 2024 by two brothers from Saint-Malo, Brittany, inspired by local corsair and maritime heritage. The debut '1712' collection honours privateer René Duguay-Trouin; watches feature guilloche dials, sapphire crystal, and 39mm steel cases water-resistant to 100m. Powered by France Ébauches automatic movements fully manufactured and assembled in France.</v>
       </c>
     </row>
     <row r="5">
@@ -592,23 +592,23 @@
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
+      <c r="D5">
+        <v>2014</v>
+      </c>
+      <c r="E5">
+        <v>249</v>
+      </c>
+      <c r="F5">
+        <v>599</v>
       </c>
       <c r="G5" t="str">
         <v>Active</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Earthrise WWF Partnership Automatic 2025 Edition</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>2025-04-22</v>
       </c>
       <c r="J5" t="str">
         <v>https://aboutvintage.com</v>
@@ -633,29 +633,29 @@
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
+      <c r="D6">
+        <v>1931</v>
+      </c>
+      <c r="E6">
+        <v>130</v>
+      </c>
+      <c r="F6">
+        <v>800</v>
       </c>
       <c r="G6" t="str">
         <v>Active</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Essence Collection</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>2025-12-09</v>
       </c>
       <c r="J6" t="str">
         <v>https://adriatica.hr</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>adriatica_official</v>
       </c>
       <c r="L6" t="str">
         <v>MBWDB</v>
@@ -715,14 +715,14 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
+      <c r="D8">
+        <v>2013</v>
+      </c>
+      <c r="E8">
+        <v>539</v>
+      </c>
+      <c r="F8">
+        <v>755</v>
       </c>
       <c r="G8" t="str">
         <v>Active</v>
@@ -731,7 +731,7 @@
         <v>Thyïlea GMT</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>2026-03-30</v>
       </c>
       <c r="J8" t="str">
         <v>https://www.aevig.com</v>
@@ -759,11 +759,11 @@
       <c r="D9">
         <v>1934</v>
       </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
+      <c r="E9">
+        <v>2214</v>
+      </c>
+      <c r="F9">
+        <v>4158</v>
       </c>
       <c r="G9" t="str">
         <v>Active</v>
@@ -772,7 +772,7 @@
         <v>Type 20 70 ANS</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>2025-10-23</v>
       </c>
       <c r="J9" t="str">
         <v>https://www.airain.com</v>
@@ -797,29 +797,29 @@
       <c r="C10" t="str">
         <v/>
       </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
+      <c r="D10">
+        <v>2016</v>
+      </c>
+      <c r="E10">
+        <v>291</v>
+      </c>
+      <c r="F10">
+        <v>526</v>
       </c>
       <c r="G10" t="str">
         <v>Active</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Aventyr</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>2025-12-23</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>https://akerfalk.se</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>akerfalk</v>
       </c>
       <c r="L10" t="str">
         <v>MBWDB</v>
@@ -838,8 +838,8 @@
       <c r="C11" t="str">
         <v>Paris</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
+      <c r="D11">
+        <v>2015</v>
       </c>
       <c r="E11">
         <v>549</v>
@@ -854,7 +854,7 @@
         <v>C-02 Baby Héritage Bourbon</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>2026-03-30</v>
       </c>
       <c r="J11" t="str">
         <v>https://www.akrone.fr</v>
@@ -879,8 +879,8 @@
       <c r="C12" t="str">
         <v>Paris</v>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>1987</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -892,16 +892,16 @@
         <v>Active</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>MeisterSinger x Alain Silberstein Edition Kaenos (2025 collaboration)</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>2025-08-08</v>
       </c>
       <c r="J12" t="str">
         <v>https://www.alainsilberstein.com</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>alainsilbersteinofficial</v>
       </c>
       <c r="L12" t="str">
         <v>existing-db</v>
@@ -920,8 +920,8 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>2003</v>
       </c>
       <c r="E13">
         <v>1750</v>
@@ -936,7 +936,7 @@
         <v>Kandy Fantasy</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>2025-12-16</v>
       </c>
       <c r="J13" t="str">
         <v>https://www.alexander-shorokhoff.com</v>
@@ -961,29 +961,29 @@
       <c r="C14" t="str">
         <v>Paris</v>
       </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
+      <c r="D14">
+        <v>2022</v>
+      </c>
+      <c r="E14">
+        <v>482</v>
+      </c>
+      <c r="F14">
+        <v>540</v>
       </c>
       <c r="G14" t="str">
         <v>Active</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>L'Odyssée GMT</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>2026-02-03</v>
       </c>
       <c r="J14" t="str">
         <v>https://www.amaroswatches.com</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>amaros_watches</v>
       </c>
       <c r="L14" t="str">
         <v>existing-db</v>
@@ -1002,29 +1002,29 @@
       <c r="C15" t="str">
         <v/>
       </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
+      <c r="D15">
+        <v>2014</v>
+      </c>
+      <c r="E15">
+        <v>1180</v>
+      </c>
+      <c r="F15">
+        <v>2180</v>
       </c>
       <c r="G15" t="str">
         <v>Active</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>OCEANMASTER II 1000M</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>2023-04-12</v>
       </c>
       <c r="J15" t="str">
         <v>https://andersmann-watches.com</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>andersmannwatch</v>
       </c>
       <c r="L15" t="str">
         <v>MBWDB</v>
@@ -1043,14 +1043,14 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
+      <c r="D16">
+        <v>1997</v>
+      </c>
+      <c r="E16">
+        <v>2951</v>
+      </c>
+      <c r="F16">
+        <v>5113</v>
       </c>
       <c r="G16" t="str">
         <v>Active</v>
@@ -1059,7 +1059,7 @@
         <v>Nautilo Vintage Green</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>2025-03-20</v>
       </c>
       <c r="J16" t="str">
         <v>https://www.anonimo.com</v>
@@ -1084,14 +1084,14 @@
       <c r="C17" t="str">
         <v>Glasgow, Scotland</v>
       </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
+      <c r="D17">
+        <v>2016</v>
+      </c>
+      <c r="E17">
+        <v>2255</v>
+      </c>
+      <c r="F17">
+        <v>4656</v>
       </c>
       <c r="G17" t="str">
         <v>Active</v>
@@ -1100,7 +1100,7 @@
         <v>Model 2 Porcelain</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>2025-05-29</v>
       </c>
       <c r="J17" t="str">
         <v>https://anordain.com</v>
@@ -1248,14 +1248,14 @@
       <c r="C21" t="str">
         <v>Paris</v>
       </c>
-      <c r="D21" t="str">
-        <v/>
+      <c r="D21">
+        <v>2022</v>
       </c>
       <c r="E21">
         <v>995</v>
       </c>
-      <c r="F21" t="str">
-        <v/>
+      <c r="F21">
+        <v>1075</v>
       </c>
       <c r="G21" t="str">
         <v>Active</v>
@@ -1264,13 +1264,13 @@
         <v>SPEED</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>2026-02-09</v>
       </c>
       <c r="J21" t="str">
         <v>https://www.aquilonandco.com</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>aquilonandco</v>
       </c>
       <c r="L21" t="str">
         <v>existing-db</v>
@@ -1289,29 +1289,29 @@
       <c r="C22" t="str">
         <v>Frederiksberg, Denmark</v>
       </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v/>
+      <c r="D22">
+        <v>2018</v>
+      </c>
+      <c r="E22">
+        <v>3950</v>
+      </c>
+      <c r="F22">
+        <v>5450</v>
       </c>
       <c r="G22" t="str">
         <v>Active</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>ARC II – D'Arc Sh'Arc</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>2025-08-01</v>
       </c>
       <c r="J22" t="str">
         <v>https://www.arcanaut.dk</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>arcanaut_watches</v>
       </c>
       <c r="L22" t="str">
         <v>existing-db</v>

--- a/watch-microbrand-database.xlsx
+++ b/watch-microbrand-database.xlsx
@@ -674,14 +674,14 @@
       <c r="C7" t="str">
         <v>Les Brenets</v>
       </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1942</v>
+      </c>
+      <c r="E7">
+        <v>400</v>
+      </c>
+      <c r="F7">
+        <v>800</v>
       </c>
       <c r="G7" t="str">
         <v>Active</v>
@@ -696,7 +696,7 @@
         <v>https://www.aerowatch.ch</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>aerowatchofficial</v>
       </c>
       <c r="L7" t="str">
         <v>existing-db</v>
@@ -882,11 +882,11 @@
       <c r="D12">
         <v>1987</v>
       </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
+      <c r="E12">
+        <v>3500</v>
+      </c>
+      <c r="F12">
+        <v>8000</v>
       </c>
       <c r="G12" t="str">
         <v>Active</v>
@@ -961,14 +961,14 @@
       <c r="C14" t="str">
         <v>Paris</v>
       </c>
-      <c r="D14">
-        <v>2022</v>
+      <c r="D14" t="str">
+        <v/>
       </c>
       <c r="E14">
-        <v>482</v>
+        <v>350</v>
       </c>
       <c r="F14">
-        <v>540</v>
+        <v>410</v>
       </c>
       <c r="G14" t="str">
         <v>Active</v>
@@ -1002,29 +1002,29 @@
       <c r="C15" t="str">
         <v/>
       </c>
-      <c r="D15">
-        <v>2014</v>
-      </c>
-      <c r="E15">
-        <v>1180</v>
-      </c>
-      <c r="F15">
-        <v>2180</v>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
       </c>
       <c r="G15" t="str">
         <v>Active</v>
       </c>
       <c r="H15" t="str">
-        <v>OCEANMASTER II 1000M</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>2023-04-12</v>
+        <v/>
       </c>
       <c r="J15" t="str">
         <v>https://andersmann-watches.com</v>
       </c>
       <c r="K15" t="str">
-        <v>andersmannwatch</v>
+        <v/>
       </c>
       <c r="L15" t="str">
         <v>MBWDB</v>
@@ -1043,14 +1043,14 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16">
-        <v>1997</v>
+      <c r="D16" t="str">
+        <v/>
       </c>
       <c r="E16">
-        <v>2951</v>
+        <v>2700</v>
       </c>
       <c r="F16">
-        <v>5113</v>
+        <v>4600</v>
       </c>
       <c r="G16" t="str">
         <v>Active</v>
@@ -1059,7 +1059,7 @@
         <v>Nautilo Vintage Green</v>
       </c>
       <c r="I16" t="str">
-        <v>2025-03-20</v>
+        <v>2022-11-14</v>
       </c>
       <c r="J16" t="str">
         <v>https://www.anonimo.com</v>
@@ -1085,13 +1085,13 @@
         <v>Glasgow, Scotland</v>
       </c>
       <c r="D17">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E17">
-        <v>2255</v>
+        <v>2273</v>
       </c>
       <c r="F17">
-        <v>4656</v>
+        <v>4693</v>
       </c>
       <c r="G17" t="str">
         <v>Active</v>
@@ -1125,8 +1125,8 @@
       <c r="C18" t="str">
         <v>Paris</v>
       </c>
-      <c r="D18" t="str">
-        <v/>
+      <c r="D18">
+        <v>2020</v>
       </c>
       <c r="E18">
         <v>2700</v>
@@ -1141,7 +1141,7 @@
         <v>Montre N°3 Douz - Or Rose &amp; Noir</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>2025-10-31</v>
       </c>
       <c r="J18" t="str">
         <v>https://www.apose.fr</v>
@@ -1166,29 +1166,29 @@
       <c r="C19" t="str">
         <v/>
       </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v/>
+      <c r="D19">
+        <v>1960</v>
+      </c>
+      <c r="E19">
+        <v>1390</v>
+      </c>
+      <c r="F19">
+        <v>1990</v>
       </c>
       <c r="G19" t="str">
         <v>Active</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>Poseidon</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>2025-07-01</v>
       </c>
       <c r="J19" t="str">
         <v>https://aquadive.de</v>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>aquadive</v>
       </c>
       <c r="L19" t="str">
         <v>MBWDB</v>
@@ -1248,14 +1248,14 @@
       <c r="C21" t="str">
         <v>Paris</v>
       </c>
-      <c r="D21">
-        <v>2022</v>
+      <c r="D21" t="str">
+        <v/>
       </c>
       <c r="E21">
         <v>995</v>
       </c>
       <c r="F21">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="G21" t="str">
         <v>Active</v>
@@ -1264,13 +1264,13 @@
         <v>SPEED</v>
       </c>
       <c r="I21" t="str">
-        <v>2026-02-09</v>
+        <v>2024-12-19</v>
       </c>
       <c r="J21" t="str">
         <v>https://www.aquilonandco.com</v>
       </c>
       <c r="K21" t="str">
-        <v>aquilonandco</v>
+        <v/>
       </c>
       <c r="L21" t="str">
         <v>existing-db</v>
@@ -1290,22 +1290,22 @@
         <v>Frederiksberg, Denmark</v>
       </c>
       <c r="D22">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="E22">
-        <v>3950</v>
+        <v>4620</v>
       </c>
       <c r="F22">
-        <v>5450</v>
+        <v>5719</v>
       </c>
       <c r="G22" t="str">
         <v>Active</v>
       </c>
       <c r="H22" t="str">
-        <v>ARC II – D'Arc Sh'Arc</v>
+        <v>Experimental: ARC II — Phantom</v>
       </c>
       <c r="I22" t="str">
-        <v>2025-08-01</v>
+        <v>2025-10-27</v>
       </c>
       <c r="J22" t="str">
         <v>https://www.arcanaut.dk</v>
@@ -1346,13 +1346,13 @@
         <v>Klassik 200</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J23" t="str">
         <v>https://www.archimede-watches.com</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>archimede_watch</v>
       </c>
       <c r="L23" t="str">
         <v>MBWDB</v>
@@ -1371,29 +1371,29 @@
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v/>
+      <c r="D24">
+        <v>1907</v>
+      </c>
+      <c r="E24">
+        <v>460</v>
+      </c>
+      <c r="F24">
+        <v>970</v>
       </c>
       <c r="G24" t="str">
         <v>Active</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>Aquaristo Automatic 4H98294 (Klassik Diver series)</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>2026-02-23</v>
       </c>
       <c r="J24" t="str">
         <v>https://www.aristo.de</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>aristouhren</v>
       </c>
       <c r="L24" t="str">
         <v>MBWDB</v>
@@ -1466,10 +1466,10 @@
         <v>Active</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>ASKANIA SMT Ergo Koax</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J26" t="str">
         <v>https://www.askania.de</v>
@@ -1494,23 +1494,23 @@
       <c r="C27" t="str">
         <v>Besançon</v>
       </c>
-      <c r="D27" t="str">
-        <v/>
+      <c r="D27">
+        <v>2022</v>
       </c>
       <c r="E27">
         <v>595</v>
       </c>
-      <c r="F27" t="str">
-        <v/>
+      <c r="F27">
+        <v>1079</v>
       </c>
       <c r="G27" t="str">
         <v>Active</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>FL 1889</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>2025-11-04</v>
       </c>
       <c r="J27" t="str">
         <v>https://www.ateliercaradant.com</v>
@@ -1535,29 +1535,29 @@
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <v/>
+      <c r="D28">
+        <v>1888</v>
+      </c>
+      <c r="E28">
+        <v>358</v>
+      </c>
+      <c r="F28">
+        <v>5577</v>
       </c>
       <c r="G28" t="str">
         <v>Active</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>Worldmaster Prestige Valjoux Limited Edition 2026</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="J28" t="str">
         <v>https://www.atlantic.de</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>atlantic_watch_ltd</v>
       </c>
       <c r="L28" t="str">
         <v>MBWDB</v>
@@ -1633,7 +1633,7 @@
         <v>Unity Day &amp; Night</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>2026-01-09</v>
       </c>
       <c r="J30" t="str">
         <v>https://www.augustereymond.ch</v>
@@ -1702,11 +1702,11 @@
       <c r="D32">
         <v>1854</v>
       </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
-      <c r="F32" t="str">
-        <v/>
+      <c r="E32">
+        <v>32</v>
+      </c>
+      <c r="F32">
+        <v>340</v>
       </c>
       <c r="G32" t="str">
         <v>Active</v>
@@ -1715,7 +1715,7 @@
         <v>La Royale</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>2024</v>
       </c>
       <c r="J32" t="str">
         <v>https://www.auricoste.com</v>
@@ -1740,8 +1740,8 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33" t="str">
-        <v/>
+      <c r="D33">
+        <v>2012</v>
       </c>
       <c r="E33">
         <v>129</v>
@@ -1756,7 +1756,7 @@
         <v>Spitfire Smith Paddy Limited Edition</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>2026-04-01</v>
       </c>
       <c r="J33" t="str">
         <v>https://www.avi-8.co.uk</v>
@@ -1794,7 +1794,7 @@
         <v>Active</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>Son Mài - Fragments</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1986,29 +1986,29 @@
       <c r="C39" t="str">
         <v>Paris</v>
       </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-      <c r="F39" t="str">
-        <v/>
+      <c r="D39">
+        <v>2016</v>
+      </c>
+      <c r="E39">
+        <v>400</v>
+      </c>
+      <c r="F39">
+        <v>800</v>
       </c>
       <c r="G39" t="str">
         <v>Active</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>Aquascaphe</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>2024-10-15</v>
       </c>
       <c r="J39" t="str">
         <v>https://www.balticwatches.com</v>
       </c>
       <c r="K39" t="str">
-        <v/>
+        <v>baltic_watches</v>
       </c>
       <c r="L39" t="str">
         <v>existing-db</v>
@@ -2068,14 +2068,14 @@
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v/>
+      <c r="D41">
+        <v>2002</v>
+      </c>
+      <c r="E41">
+        <v>2500</v>
+      </c>
+      <c r="F41">
+        <v>8000</v>
       </c>
       <c r="G41" t="str">
         <v>Active</v>
@@ -2090,7 +2090,7 @@
         <v>https://www.bamfordwatches.com</v>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>bamfordoflondon</v>
       </c>
       <c r="L41" t="str">
         <v>MBWDB</v>
@@ -2191,14 +2191,14 @@
       <c r="C44" t="str">
         <v/>
       </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v/>
+      <c r="D44">
+        <v>2014</v>
+      </c>
+      <c r="E44">
+        <v>400</v>
+      </c>
+      <c r="F44">
+        <v>700</v>
       </c>
       <c r="G44" t="str">
         <v>Active</v>
@@ -2213,7 +2213,7 @@
         <v>https://bausele.de</v>
       </c>
       <c r="K44" t="str">
-        <v/>
+        <v>bausele_watches</v>
       </c>
       <c r="L44" t="str">
         <v>MBWDB</v>
@@ -2289,7 +2289,7 @@
         <v>Rotary (2025)</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J46" t="str">
         <v>https://www.behrenswatches.com</v>
@@ -2330,7 +2330,7 @@
         <v>1247 VISUREN #22</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>2024-10-12</v>
       </c>
       <c r="J47" t="str">
         <v>https://www.belchengruppe.com</v>
@@ -2412,7 +2412,7 @@
         <v>UltraFino Rotondo</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J49" t="str">
         <v>https://www.bianchet.com</v>
@@ -2437,8 +2437,8 @@
       <c r="C50" t="str">
         <v/>
       </c>
-      <c r="D50" t="str">
-        <v/>
+      <c r="D50">
+        <v>2010</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Active</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>XP1</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2522,11 +2522,11 @@
       <c r="D52" t="str">
         <v/>
       </c>
-      <c r="E52" t="str">
-        <v/>
-      </c>
-      <c r="F52" t="str">
-        <v/>
+      <c r="E52">
+        <v>1095</v>
+      </c>
+      <c r="F52">
+        <v>3295</v>
       </c>
       <c r="G52" t="str">
         <v>Active</v>
@@ -2535,7 +2535,7 @@
         <v>Apex Carbon</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>2024-12-20</v>
       </c>
       <c r="J52" t="str">
         <v>https://www.bombergwatches.com</v>
@@ -2563,11 +2563,11 @@
       <c r="D53">
         <v>1986</v>
       </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
-      <c r="F53" t="str">
-        <v/>
+      <c r="E53">
+        <v>530</v>
+      </c>
+      <c r="F53">
+        <v>3116</v>
       </c>
       <c r="G53" t="str">
         <v>Active</v>
@@ -2576,7 +2576,7 @@
         <v>UNO 24 Slate</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J53" t="str">
         <v>https://www.botta-design.de</v>
@@ -2601,29 +2601,29 @@
       <c r="C54" t="str">
         <v>Öhringen</v>
       </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
-      <c r="E54" t="str">
-        <v/>
-      </c>
-      <c r="F54" t="str">
-        <v/>
+      <c r="D54">
+        <v>1961</v>
+      </c>
+      <c r="E54">
+        <v>400</v>
+      </c>
+      <c r="F54">
+        <v>800</v>
       </c>
       <c r="G54" t="str">
         <v>Active</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>Tres Horas</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J54" t="str">
         <v>https://www.botta.de</v>
       </c>
       <c r="K54" t="str">
-        <v/>
+        <v>bottadesign</v>
       </c>
       <c r="L54" t="str">
         <v>existing-db</v>
@@ -2724,8 +2724,8 @@
       <c r="C57" t="str">
         <v/>
       </c>
-      <c r="D57" t="str">
-        <v/>
+      <c r="D57">
+        <v>2002</v>
       </c>
       <c r="E57">
         <v>5250</v>
@@ -2740,7 +2740,7 @@
         <v>Terra Nova Jumping Hour</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J57" t="str">
         <v>https://www.bremont.com</v>
@@ -2847,29 +2847,29 @@
       <c r="C60" t="str">
         <v/>
       </c>
-      <c r="D60" t="str">
-        <v/>
-      </c>
-      <c r="E60" t="str">
-        <v/>
-      </c>
-      <c r="F60" t="str">
-        <v/>
+      <c r="D60">
+        <v>2005</v>
+      </c>
+      <c r="E60">
+        <v>2500</v>
+      </c>
+      <c r="F60">
+        <v>8000</v>
       </c>
       <c r="G60" t="str">
         <v>Active</v>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>V6-44</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>2024-06-01</v>
       </c>
       <c r="J60" t="str">
         <v>https://www.brmwatches.com</v>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>brm_timepieces</v>
       </c>
       <c r="L60" t="str">
         <v>MBWDB</v>
@@ -2901,10 +2901,10 @@
         <v>Active</v>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>V6-42-EV</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J61" t="str">
         <v>https://www.brm-manufacture.com</v>
@@ -2945,7 +2945,7 @@
         <v>Garde-temps automatique</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J62" t="str">
         <v>https://www.buci-paris.com</v>
@@ -3175,14 +3175,14 @@
       <c r="C68" t="str">
         <v>Paris</v>
       </c>
-      <c r="D68" t="str">
-        <v/>
-      </c>
-      <c r="E68" t="str">
-        <v/>
-      </c>
-      <c r="F68" t="str">
-        <v/>
+      <c r="D68">
+        <v>2012</v>
+      </c>
+      <c r="E68">
+        <v>250</v>
+      </c>
+      <c r="F68">
+        <v>550</v>
       </c>
       <c r="G68" t="str">
         <v>Active</v>
@@ -3197,7 +3197,7 @@
         <v>https://www.charlieparis.com</v>
       </c>
       <c r="K68" t="str">
-        <v/>
+        <v>charliepariswatch</v>
       </c>
       <c r="L68" t="str">
         <v>existing-db</v>
@@ -3216,14 +3216,14 @@
       <c r="C69" t="str">
         <v>Franeker, Netherlands</v>
       </c>
-      <c r="D69" t="str">
-        <v/>
-      </c>
-      <c r="E69" t="str">
-        <v/>
-      </c>
-      <c r="F69" t="str">
-        <v/>
+      <c r="D69">
+        <v>1970</v>
+      </c>
+      <c r="E69">
+        <v>2500</v>
+      </c>
+      <c r="F69">
+        <v>4500</v>
       </c>
       <c r="G69" t="str">
         <v>Active</v>
@@ -3238,7 +3238,7 @@
         <v>https://www.cvdk.com</v>
       </c>
       <c r="K69" t="str">
-        <v/>
+        <v>cvdklaauw</v>
       </c>
       <c r="L69" t="str">
         <v>existing-db</v>
@@ -3257,29 +3257,29 @@
       <c r="C70" t="str">
         <v/>
       </c>
-      <c r="D70" t="str">
-        <v/>
-      </c>
-      <c r="E70" t="str">
-        <v/>
-      </c>
-      <c r="F70" t="str">
-        <v/>
+      <c r="D70">
+        <v>2004</v>
+      </c>
+      <c r="E70">
+        <v>495</v>
+      </c>
+      <c r="F70">
+        <v>3200</v>
       </c>
       <c r="G70" t="str">
         <v>Active</v>
       </c>
       <c r="H70" t="str">
-        <v/>
+        <v>C60 Trident Pro</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J70" t="str">
         <v>https://www.christopherward.com</v>
       </c>
       <c r="K70" t="str">
-        <v/>
+        <v>christopherwardwatches</v>
       </c>
       <c r="L70" t="str">
         <v>MBWDB</v>
@@ -3342,20 +3342,20 @@
       <c r="D72">
         <v>1983</v>
       </c>
-      <c r="E72" t="str">
-        <v/>
-      </c>
-      <c r="F72" t="str">
-        <v/>
+      <c r="E72">
+        <v>9600</v>
+      </c>
+      <c r="F72">
+        <v>95000</v>
       </c>
       <c r="G72" t="str">
         <v>Active</v>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>Pulse GMT</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J72" t="str">
         <v>https://www.chronoswiss.com</v>
@@ -3396,7 +3396,7 @@
         <v>47° North</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J73" t="str">
         <v>https://www.cimier.com</v>
@@ -3421,14 +3421,14 @@
       <c r="C74" t="str">
         <v/>
       </c>
-      <c r="D74" t="str">
-        <v/>
-      </c>
-      <c r="E74" t="str">
-        <v/>
-      </c>
-      <c r="F74" t="str">
-        <v/>
+      <c r="D74">
+        <v>2013</v>
+      </c>
+      <c r="E74">
+        <v>400</v>
+      </c>
+      <c r="F74">
+        <v>800</v>
       </c>
       <c r="G74" t="str">
         <v>Active</v>
@@ -3443,7 +3443,7 @@
         <v>https://www.circula.com</v>
       </c>
       <c r="K74" t="str">
-        <v/>
+        <v>circula_watches</v>
       </c>
       <c r="L74" t="str">
         <v>MBWDB</v>
@@ -3462,14 +3462,14 @@
       <c r="C75" t="str">
         <v>Geneva</v>
       </c>
-      <c r="D75" t="str">
-        <v/>
-      </c>
-      <c r="E75" t="str">
-        <v/>
-      </c>
-      <c r="F75" t="str">
-        <v/>
+      <c r="D75">
+        <v>2017</v>
+      </c>
+      <c r="E75">
+        <v>2500</v>
+      </c>
+      <c r="F75">
+        <v>4500</v>
       </c>
       <c r="G75" t="str">
         <v>Active</v>
@@ -3503,29 +3503,29 @@
       <c r="C76" t="str">
         <v/>
       </c>
-      <c r="D76" t="str">
-        <v/>
-      </c>
-      <c r="E76" t="str">
-        <v/>
-      </c>
-      <c r="F76" t="str">
-        <v/>
+      <c r="D76">
+        <v>1905</v>
+      </c>
+      <c r="E76">
+        <v>1500</v>
+      </c>
+      <c r="F76">
+        <v>15000</v>
       </c>
       <c r="G76" t="str">
         <v>Active</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>Mariner</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>2024</v>
       </c>
       <c r="J76" t="str">
-        <v/>
+        <v>https://www.concordwatches.com</v>
       </c>
       <c r="K76" t="str">
-        <v/>
+        <v>concordwatches</v>
       </c>
       <c r="L76" t="str">
         <v>MBWDB</v>
@@ -3544,14 +3544,14 @@
       <c r="C77" t="str">
         <v/>
       </c>
-      <c r="D77" t="str">
-        <v/>
-      </c>
-      <c r="E77" t="str">
-        <v/>
-      </c>
-      <c r="F77" t="str">
-        <v/>
+      <c r="D77">
+        <v>2010</v>
+      </c>
+      <c r="E77">
+        <v>400</v>
+      </c>
+      <c r="F77">
+        <v>800</v>
       </c>
       <c r="G77" t="str">
         <v>Active</v>
@@ -3566,7 +3566,7 @@
         <v>https://www.cornavin.com</v>
       </c>
       <c r="K77" t="str">
-        <v/>
+        <v>cornavin_watches</v>
       </c>
       <c r="L77" t="str">
         <v>MBWDB</v>
@@ -3588,11 +3588,11 @@
       <c r="D78" t="str">
         <v/>
       </c>
-      <c r="E78" t="str">
-        <v/>
-      </c>
-      <c r="F78" t="str">
-        <v/>
+      <c r="E78">
+        <v>340</v>
+      </c>
+      <c r="F78">
+        <v>695</v>
       </c>
       <c r="G78" t="str">
         <v>Active</v>
@@ -3642,7 +3642,7 @@
         <v>Challenge K.Khachanov</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J79" t="str">
         <v>https://www.cvstos.com</v>
@@ -3667,20 +3667,20 @@
       <c r="C80" t="str">
         <v/>
       </c>
-      <c r="D80" t="str">
-        <v/>
-      </c>
-      <c r="E80" t="str">
-        <v/>
-      </c>
-      <c r="F80" t="str">
-        <v/>
+      <c r="D80">
+        <v>2012</v>
+      </c>
+      <c r="E80">
+        <v>2500</v>
+      </c>
+      <c r="F80">
+        <v>8000</v>
       </c>
       <c r="G80" t="str">
         <v>Active</v>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>Kuros</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -3689,7 +3689,7 @@
         <v>https://www.cyruswatches.com</v>
       </c>
       <c r="K80" t="str">
-        <v/>
+        <v>cyruswatches</v>
       </c>
       <c r="L80" t="str">
         <v>MBWDB</v>
@@ -3724,13 +3724,13 @@
         <v>Quai des Bergues No 33 M 'Sursum Corda'</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J81" t="str">
         <v>https://www.czapek.com</v>
       </c>
       <c r="K81" t="str">
-        <v/>
+        <v>czapekgeneve</v>
       </c>
       <c r="L81" t="str">
         <v>MBWDB</v>
@@ -3793,20 +3793,20 @@
       <c r="D83" t="str">
         <v/>
       </c>
-      <c r="E83" t="str">
-        <v/>
-      </c>
-      <c r="F83" t="str">
-        <v/>
+      <c r="E83">
+        <v>255</v>
+      </c>
+      <c r="F83">
+        <v>395</v>
       </c>
       <c r="G83" t="str">
         <v>Active</v>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>Dark Illusion Ultra Thin Watch</v>
       </c>
       <c r="I83" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J83" t="str">
         <v>https://www.d1milano.com</v>
@@ -3831,29 +3831,29 @@
       <c r="C84" t="str">
         <v/>
       </c>
-      <c r="D84" t="str">
-        <v/>
-      </c>
-      <c r="E84" t="str">
-        <v/>
-      </c>
-      <c r="F84" t="str">
-        <v/>
+      <c r="D84">
+        <v>2005</v>
+      </c>
+      <c r="E84">
+        <v>1200</v>
+      </c>
+      <c r="F84">
+        <v>2800</v>
       </c>
       <c r="G84" t="str">
         <v>Active</v>
       </c>
       <c r="H84" t="str">
-        <v/>
+        <v>DA47</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J84" t="str">
         <v>https://www.damasko.de</v>
       </c>
       <c r="K84" t="str">
-        <v/>
+        <v>damasko_watches</v>
       </c>
       <c r="L84" t="str">
         <v>MBWDB</v>
@@ -3872,14 +3872,14 @@
       <c r="C85" t="str">
         <v/>
       </c>
-      <c r="D85" t="str">
-        <v/>
-      </c>
-      <c r="E85" t="str">
-        <v/>
-      </c>
-      <c r="F85" t="str">
-        <v/>
+      <c r="D85">
+        <v>1990</v>
+      </c>
+      <c r="E85">
+        <v>200</v>
+      </c>
+      <c r="F85">
+        <v>500</v>
       </c>
       <c r="G85" t="str">
         <v>Active</v>
@@ -3894,7 +3894,7 @@
         <v>https://www.danishdesignwatches.com</v>
       </c>
       <c r="K85" t="str">
-        <v/>
+        <v>danishdesignwatches</v>
       </c>
       <c r="L85" t="str">
         <v>MBWDB</v>
@@ -3967,7 +3967,7 @@
         <v>Active</v>
       </c>
       <c r="H87" t="str">
-        <v/>
+        <v>Transit</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -3995,14 +3995,14 @@
       <c r="C88" t="str">
         <v/>
       </c>
-      <c r="D88" t="str">
-        <v/>
-      </c>
-      <c r="E88" t="str">
-        <v/>
-      </c>
-      <c r="F88" t="str">
-        <v/>
+      <c r="D88">
+        <v>1924</v>
+      </c>
+      <c r="E88">
+        <v>400</v>
+      </c>
+      <c r="F88">
+        <v>1200</v>
       </c>
       <c r="G88" t="str">
         <v>Active</v>
@@ -4017,7 +4017,7 @@
         <v>https://www.delbana.com</v>
       </c>
       <c r="K88" t="str">
-        <v/>
+        <v>delbanawatches</v>
       </c>
       <c r="L88" t="str">
         <v>MBWDB</v>
@@ -4200,14 +4200,14 @@
       <c r="C93" t="str">
         <v/>
       </c>
-      <c r="D93" t="str">
-        <v/>
-      </c>
-      <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
-        <v/>
+      <c r="D93">
+        <v>2014</v>
+      </c>
+      <c r="E93">
+        <v>300</v>
+      </c>
+      <c r="F93">
+        <v>800</v>
       </c>
       <c r="G93" t="str">
         <v>Active</v>
@@ -4222,7 +4222,7 @@
         <v>https://www.detomaso.de</v>
       </c>
       <c r="K93" t="str">
-        <v/>
+        <v>detomaso_watches</v>
       </c>
       <c r="L93" t="str">
         <v>MBWDB</v>
@@ -4241,8 +4241,8 @@
       <c r="C94" t="str">
         <v/>
       </c>
-      <c r="D94" t="str">
-        <v/>
+      <c r="D94">
+        <v>1936</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -4339,7 +4339,7 @@
         <v>Ultrawerk™ Titanium</v>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J96" t="str">
         <v>https://www.dievaswatches.com</v>
@@ -4528,8 +4528,8 @@
       <c r="C101" t="str">
         <v/>
       </c>
-      <c r="D101" t="str">
-        <v/>
+      <c r="D101">
+        <v>1926</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4550,7 +4550,7 @@
         <v>https://www.doxawatch.com</v>
       </c>
       <c r="K101" t="str">
-        <v/>
+        <v>doxawatch</v>
       </c>
       <c r="L101" t="str">
         <v>MBWDB</v>
@@ -4610,14 +4610,14 @@
       <c r="C103" t="str">
         <v/>
       </c>
-      <c r="D103" t="str">
-        <v/>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
-        <v/>
+      <c r="D103">
+        <v>1859</v>
+      </c>
+      <c r="E103">
+        <v>400</v>
+      </c>
+      <c r="F103">
+        <v>800</v>
       </c>
       <c r="G103" t="str">
         <v>Active</v>
@@ -4632,7 +4632,7 @@
         <v>https://www.dreyfuss.co.uk</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>dreyfussandco</v>
       </c>
       <c r="L103" t="str">
         <v>MBWDB</v>
@@ -4692,14 +4692,14 @@
       <c r="C105" t="str">
         <v/>
       </c>
-      <c r="D105" t="str">
-        <v/>
-      </c>
-      <c r="E105" t="str">
-        <v/>
-      </c>
-      <c r="F105" t="str">
-        <v/>
+      <c r="D105">
+        <v>2007</v>
+      </c>
+      <c r="E105">
+        <v>350</v>
+      </c>
+      <c r="F105">
+        <v>650</v>
       </c>
       <c r="G105" t="str">
         <v>Active</v>
@@ -4714,7 +4714,7 @@
         <v>https://www.dufa.com</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>dufauhren</v>
       </c>
       <c r="L105" t="str">
         <v>MBWDB</v>
@@ -4774,14 +4774,14 @@
       <c r="C107" t="str">
         <v/>
       </c>
-      <c r="D107" t="str">
-        <v/>
-      </c>
-      <c r="E107" t="str">
-        <v/>
-      </c>
-      <c r="F107" t="str">
-        <v/>
+      <c r="D107">
+        <v>2013</v>
+      </c>
+      <c r="E107">
+        <v>300</v>
+      </c>
+      <c r="F107">
+        <v>700</v>
       </c>
       <c r="G107" t="str">
         <v>Active</v>
@@ -4796,7 +4796,7 @@
         <v>https://www.earnshawwatches.com</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>earnshawwatches</v>
       </c>
       <c r="L107" t="str">
         <v>MBWDB</v>
@@ -4815,29 +4815,29 @@
       <c r="C108" t="str">
         <v/>
       </c>
-      <c r="D108" t="str">
-        <v/>
-      </c>
-      <c r="E108" t="str">
-        <v/>
-      </c>
-      <c r="F108" t="str">
-        <v/>
+      <c r="D108">
+        <v>1887</v>
+      </c>
+      <c r="E108">
+        <v>3500</v>
+      </c>
+      <c r="F108">
+        <v>8000</v>
       </c>
       <c r="G108" t="str">
         <v>Active</v>
       </c>
       <c r="H108" t="str">
-        <v/>
+        <v>Chrono 4</v>
       </c>
       <c r="I108" t="str">
-        <v/>
+        <v>2024-09-01</v>
       </c>
       <c r="J108" t="str">
         <v>https://www.eberhard-watches.com</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>eberhard_watches</v>
       </c>
       <c r="L108" t="str">
         <v>MBWDB</v>
@@ -4941,11 +4941,11 @@
       <c r="D111" t="str">
         <v/>
       </c>
-      <c r="E111" t="str">
-        <v/>
-      </c>
-      <c r="F111" t="str">
-        <v/>
+      <c r="E111">
+        <v>840</v>
+      </c>
+      <c r="F111">
+        <v>870</v>
       </c>
       <c r="G111" t="str">
         <v>Active</v>
@@ -4954,7 +4954,7 @@
         <v>Chamonix</v>
       </c>
       <c r="I111" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J111" t="str">
         <v>https://www.elge-watches.com</v>
@@ -4979,29 +4979,29 @@
       <c r="C112" t="str">
         <v/>
       </c>
-      <c r="D112" t="str">
-        <v/>
-      </c>
-      <c r="E112" t="str">
-        <v/>
-      </c>
-      <c r="F112" t="str">
-        <v/>
+      <c r="D112">
+        <v>2012</v>
+      </c>
+      <c r="E112">
+        <v>400</v>
+      </c>
+      <c r="F112">
+        <v>800</v>
       </c>
       <c r="G112" t="str">
         <v>Active</v>
       </c>
       <c r="H112" t="str">
-        <v/>
+        <v>Canford</v>
       </c>
       <c r="I112" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J112" t="str">
         <v>https://www.elliotbrown.com</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>elliotbrownwatches</v>
       </c>
       <c r="L112" t="str">
         <v>MBWDB</v>
@@ -5020,14 +5020,14 @@
       <c r="C113" t="str">
         <v/>
       </c>
-      <c r="D113" t="str">
-        <v/>
-      </c>
-      <c r="E113" t="str">
-        <v/>
-      </c>
-      <c r="F113" t="str">
-        <v/>
+      <c r="D113">
+        <v>1992</v>
+      </c>
+      <c r="E113">
+        <v>300</v>
+      </c>
+      <c r="F113">
+        <v>800</v>
       </c>
       <c r="G113" t="str">
         <v>Active</v>
@@ -5039,10 +5039,10 @@
         <v/>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://www.elysee.de</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>elysee_watches</v>
       </c>
       <c r="L113" t="str">
         <v>MBWDB</v>
@@ -5061,8 +5061,8 @@
       <c r="C114" t="str">
         <v/>
       </c>
-      <c r="D114" t="str">
-        <v/>
+      <c r="D114">
+        <v>1948</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -5102,29 +5102,29 @@
       <c r="C115" t="str">
         <v/>
       </c>
-      <c r="D115" t="str">
-        <v/>
-      </c>
-      <c r="E115" t="str">
-        <v/>
-      </c>
-      <c r="F115" t="str">
-        <v/>
+      <c r="D115">
+        <v>1983</v>
+      </c>
+      <c r="E115">
+        <v>400</v>
+      </c>
+      <c r="F115">
+        <v>1200</v>
       </c>
       <c r="G115" t="str">
         <v>Active</v>
       </c>
       <c r="H115" t="str">
-        <v/>
+        <v>Sportive</v>
       </c>
       <c r="I115" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J115" t="str">
         <v>https://www.epos-watches.com</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>eposwatches</v>
       </c>
       <c r="L115" t="str">
         <v>MBWDB</v>
@@ -5200,7 +5200,7 @@
         <v>35mm Cushion Case Collection</v>
       </c>
       <c r="I117" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J117" t="str">
         <v>https://www.farer.co.uk</v>
@@ -5269,11 +5269,11 @@
       <c r="D119" t="str">
         <v/>
       </c>
-      <c r="E119" t="str">
-        <v/>
-      </c>
-      <c r="F119" t="str">
-        <v/>
+      <c r="E119">
+        <v>750</v>
+      </c>
+      <c r="F119">
+        <v>4300</v>
       </c>
       <c r="G119" t="str">
         <v>Active</v>
@@ -5282,7 +5282,7 @@
         <v>Essence Ceramica GT</v>
       </c>
       <c r="I119" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J119" t="str">
         <v>https://www.formexwatch.com</v>
@@ -5307,29 +5307,29 @@
       <c r="C120" t="str">
         <v/>
       </c>
-      <c r="D120" t="str">
-        <v/>
-      </c>
-      <c r="E120" t="str">
-        <v/>
-      </c>
-      <c r="F120" t="str">
-        <v/>
+      <c r="D120">
+        <v>1912</v>
+      </c>
+      <c r="E120">
+        <v>1200</v>
+      </c>
+      <c r="F120">
+        <v>4500</v>
       </c>
       <c r="G120" t="str">
         <v>Active</v>
       </c>
       <c r="H120" t="str">
-        <v/>
+        <v>Abyss</v>
       </c>
       <c r="I120" t="str">
-        <v/>
+        <v>2024-10-15</v>
       </c>
       <c r="J120" t="str">
         <v>https://www.fortis-watches.com</v>
       </c>
       <c r="K120" t="str">
-        <v/>
+        <v>fortis_watches</v>
       </c>
       <c r="L120" t="str">
         <v>MBWDB</v>
@@ -5361,10 +5361,10 @@
         <v>Active</v>
       </c>
       <c r="H121" t="str">
-        <v/>
+        <v>Kolibri</v>
       </c>
       <c r="I121" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J121" t="str">
         <v>https://www.frankjutzi.com</v>
@@ -5392,20 +5392,20 @@
       <c r="D122">
         <v>2021</v>
       </c>
-      <c r="E122" t="str">
-        <v/>
-      </c>
-      <c r="F122" t="str">
-        <v/>
+      <c r="E122">
+        <v>635</v>
+      </c>
+      <c r="F122">
+        <v>3800</v>
       </c>
       <c r="G122" t="str">
         <v>Active</v>
       </c>
       <c r="H122" t="str">
-        <v/>
+        <v>Disco Onyx Diamonds</v>
       </c>
       <c r="I122" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J122" t="str">
         <v>https://www.furlanmarri.com</v>
@@ -5430,8 +5430,8 @@
       <c r="C123" t="str">
         <v>Florence, Italy</v>
       </c>
-      <c r="D123" t="str">
-        <v/>
+      <c r="D123">
+        <v>2024</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5446,7 +5446,7 @@
         <v>Labormatic Azzurro</v>
       </c>
       <c r="I123" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J123" t="str">
         <v>https://www.gagalaboratorio.com</v>
@@ -5487,7 +5487,7 @@
         <v>S3 Deadbeat Seconds - Power Reserve</v>
       </c>
       <c r="I124" t="str">
-        <v/>
+        <v>2026-03-30</v>
       </c>
       <c r="J124" t="str">
         <v>https://garrick.co.uk</v>
@@ -5534,7 +5534,7 @@
         <v>https://www.geckota.com</v>
       </c>
       <c r="K125" t="str">
-        <v/>
+        <v>geckota</v>
       </c>
       <c r="L125" t="str">
         <v>MBWDB</v>
@@ -5569,7 +5569,7 @@
         <v>World Trip GMT</v>
       </c>
       <c r="I126" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J126" t="str">
         <v>https://www.gigandet.com</v>
@@ -5607,7 +5607,7 @@
         <v>Active</v>
       </c>
       <c r="H127" t="str">
-        <v/>
+        <v>Airman</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -5638,11 +5638,11 @@
       <c r="D128" t="str">
         <v/>
       </c>
-      <c r="E128" t="str">
-        <v/>
-      </c>
-      <c r="F128" t="str">
-        <v/>
+      <c r="E128">
+        <v>6450</v>
+      </c>
+      <c r="F128">
+        <v>12950</v>
       </c>
       <c r="G128" t="str">
         <v>Active</v>
@@ -5651,7 +5651,7 @@
         <v>Chronofighter Superlight</v>
       </c>
       <c r="I128" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J128" t="str">
         <v>https://www.graham1695.com</v>
@@ -5733,7 +5733,7 @@
         <v>Marie 2 Aiguilles</v>
       </c>
       <c r="I130" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J130" t="str">
         <v>https://www.gustave-et-cie.fr</v>
@@ -5758,8 +5758,8 @@
       <c r="C131" t="str">
         <v/>
       </c>
-      <c r="D131" t="str">
-        <v/>
+      <c r="D131">
+        <v>1828</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5771,10 +5771,10 @@
         <v>Active</v>
       </c>
       <c r="H131" t="str">
-        <v/>
+        <v>Streamliner Alpine Drivers and Mechanics Pink Editions</v>
       </c>
       <c r="I131" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J131" t="str">
         <v>https://www.h-moser.com</v>
@@ -5815,7 +5815,7 @@
         <v>Oskar</v>
       </c>
       <c r="I132" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J132" t="str">
         <v>https://www.habring2.com</v>
@@ -5856,7 +5856,7 @@
         <v/>
       </c>
       <c r="I133" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J133" t="str">
         <v>https://www.halda.com</v>
@@ -5881,23 +5881,23 @@
       <c r="C134" t="str">
         <v/>
       </c>
-      <c r="D134" t="str">
-        <v/>
-      </c>
-      <c r="E134" t="str">
-        <v/>
-      </c>
-      <c r="F134" t="str">
-        <v/>
+      <c r="D134">
+        <v>1882</v>
+      </c>
+      <c r="E134">
+        <v>3500</v>
+      </c>
+      <c r="F134">
+        <v>4800</v>
       </c>
       <c r="G134" t="str">
         <v>Active</v>
       </c>
       <c r="H134" t="str">
-        <v/>
+        <v>417 TI Desert Pilot</v>
       </c>
       <c r="I134" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J134" t="str">
         <v>https://www.hanhart.com</v>
@@ -5922,8 +5922,8 @@
       <c r="C135" t="str">
         <v>Haute-Rive</v>
       </c>
-      <c r="D135" t="str">
-        <v/>
+      <c r="D135">
+        <v>1888</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5935,7 +5935,7 @@
         <v>Active</v>
       </c>
       <c r="H135" t="str">
-        <v/>
+        <v>Honoris Lagoverde</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -6004,8 +6004,8 @@
       <c r="C137" t="str">
         <v/>
       </c>
-      <c r="D137" t="str">
-        <v/>
+      <c r="D137">
+        <v>2009</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -6017,16 +6017,16 @@
         <v>Active</v>
       </c>
       <c r="H137" t="str">
-        <v/>
+        <v>Shark Diver 45 Brass</v>
       </c>
       <c r="I137" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J137" t="str">
         <v>https://www.helsonwatches.com</v>
       </c>
       <c r="K137" t="str">
-        <v/>
+        <v>helsonwatches</v>
       </c>
       <c r="L137" t="str">
         <v>MBWDB</v>
@@ -6061,7 +6061,7 @@
         <v/>
       </c>
       <c r="I138" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J138" t="str">
         <v>https://www.herzwerk-watchmaking.com</v>
@@ -6089,8 +6089,8 @@
       <c r="D139" t="str">
         <v/>
       </c>
-      <c r="E139" t="str">
-        <v/>
+      <c r="E139">
+        <v>360</v>
       </c>
       <c r="F139" t="str">
         <v/>
@@ -6102,7 +6102,7 @@
         <v>Diver 300M Automatic Commando</v>
       </c>
       <c r="I139" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J139" t="str">
         <v>https://www.hgp-watches.com</v>
@@ -6140,10 +6140,10 @@
         <v>Active</v>
       </c>
       <c r="H140" t="str">
-        <v/>
+        <v>K-TMR Micro-Rotor Tourbillon</v>
       </c>
       <c r="I140" t="str">
-        <v/>
+        <v>2024-07-24</v>
       </c>
       <c r="J140" t="str">
         <v>https://www.horage.com</v>
@@ -6168,8 +6168,8 @@
       <c r="C141" t="str">
         <v>Heerde, Netherlands</v>
       </c>
-      <c r="D141" t="str">
-        <v/>
+      <c r="D141">
+        <v>2014</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -6181,10 +6181,10 @@
         <v>Active</v>
       </c>
       <c r="H141" t="str">
-        <v/>
+        <v>Easy Perpetual</v>
       </c>
       <c r="I141" t="str">
-        <v/>
+        <v>2025-07</v>
       </c>
       <c r="J141" t="str">
         <v>https://www.hulsman-timepieces.com</v>
@@ -6266,7 +6266,7 @@
         <v>Circular C</v>
       </c>
       <c r="I143" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J143" t="str">
         <v>https://www.idwatch.ch</v>
@@ -6291,23 +6291,23 @@
       <c r="C144" t="str">
         <v>Geneva</v>
       </c>
-      <c r="D144" t="str">
-        <v/>
-      </c>
-      <c r="E144" t="str">
-        <v/>
-      </c>
-      <c r="F144" t="str">
-        <v/>
+      <c r="D144">
+        <v>1994</v>
+      </c>
+      <c r="E144">
+        <v>690</v>
+      </c>
+      <c r="F144">
+        <v>790</v>
       </c>
       <c r="G144" t="str">
         <v>Active</v>
       </c>
       <c r="H144" t="str">
-        <v/>
+        <v>Horopod</v>
       </c>
       <c r="I144" t="str">
-        <v/>
+        <v>2025-01-08</v>
       </c>
       <c r="J144" t="str">
         <v>https://www.ikepod.com</v>
@@ -6332,20 +6332,20 @@
       <c r="C145" t="str">
         <v/>
       </c>
-      <c r="D145" t="str">
-        <v/>
-      </c>
-      <c r="E145" t="str">
-        <v/>
-      </c>
-      <c r="F145" t="str">
-        <v/>
+      <c r="D145">
+        <v>2014</v>
+      </c>
+      <c r="E145">
+        <v>350</v>
+      </c>
+      <c r="F145">
+        <v>750</v>
       </c>
       <c r="G145" t="str">
         <v>Active</v>
       </c>
       <c r="H145" t="str">
-        <v/>
+        <v>Mk III</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -6354,7 +6354,7 @@
         <v>https://www.ilwwatches.com</v>
       </c>
       <c r="K145" t="str">
-        <v/>
+        <v>ilwwatches</v>
       </c>
       <c r="L145" t="str">
         <v>MBWDB</v>
@@ -6373,20 +6373,20 @@
       <c r="C146" t="str">
         <v/>
       </c>
-      <c r="D146" t="str">
-        <v/>
-      </c>
-      <c r="E146" t="str">
-        <v/>
-      </c>
-      <c r="F146" t="str">
-        <v/>
+      <c r="D146">
+        <v>2014</v>
+      </c>
+      <c r="E146">
+        <v>400</v>
+      </c>
+      <c r="F146">
+        <v>800</v>
       </c>
       <c r="G146" t="str">
         <v>Active</v>
       </c>
       <c r="H146" t="str">
-        <v/>
+        <v>Amazonas</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -6395,7 +6395,7 @@
         <v>https://www.iron-annie.com</v>
       </c>
       <c r="K146" t="str">
-        <v/>
+        <v>iron_annie_official</v>
       </c>
       <c r="L146" t="str">
         <v>MBWDB</v>
@@ -6455,14 +6455,14 @@
       <c r="C148" t="str">
         <v/>
       </c>
-      <c r="D148" t="str">
-        <v/>
-      </c>
-      <c r="E148" t="str">
-        <v/>
-      </c>
-      <c r="F148" t="str">
-        <v/>
+      <c r="D148">
+        <v>1961</v>
+      </c>
+      <c r="E148">
+        <v>300</v>
+      </c>
+      <c r="F148">
+        <v>800</v>
       </c>
       <c r="G148" t="str">
         <v>Active</v>
@@ -6474,10 +6474,10 @@
         <v/>
       </c>
       <c r="J148" t="str">
-        <v/>
+        <v>https://www.jacobjensen.com</v>
       </c>
       <c r="K148" t="str">
-        <v/>
+        <v>jacobjensendesign</v>
       </c>
       <c r="L148" t="str">
         <v>MBWDB</v>
@@ -6619,14 +6619,14 @@
       <c r="C152" t="str">
         <v/>
       </c>
-      <c r="D152" t="str">
-        <v/>
-      </c>
-      <c r="E152" t="str">
-        <v/>
-      </c>
-      <c r="F152" t="str">
-        <v/>
+      <c r="D152">
+        <v>1992</v>
+      </c>
+      <c r="E152">
+        <v>2000</v>
+      </c>
+      <c r="F152">
+        <v>6000</v>
       </c>
       <c r="G152" t="str">
         <v>Active</v>
@@ -6641,7 +6641,7 @@
         <v>https://www.jean-marcel.com</v>
       </c>
       <c r="K152" t="str">
-        <v/>
+        <v>jeanmarcelwatches</v>
       </c>
       <c r="L152" t="str">
         <v>MBWDB</v>
@@ -6660,29 +6660,29 @@
       <c r="C153" t="str">
         <v/>
       </c>
-      <c r="D153" t="str">
-        <v/>
-      </c>
-      <c r="E153" t="str">
-        <v/>
-      </c>
-      <c r="F153" t="str">
-        <v/>
+      <c r="D153">
+        <v>1681</v>
+      </c>
+      <c r="E153">
+        <v>3000</v>
+      </c>
+      <c r="F153">
+        <v>15000</v>
       </c>
       <c r="G153" t="str">
         <v>Active</v>
       </c>
       <c r="H153" t="str">
-        <v/>
+        <v>Terrascope</v>
       </c>
       <c r="I153" t="str">
         <v/>
       </c>
       <c r="J153" t="str">
-        <v/>
+        <v>https://www.jeanrichard.com</v>
       </c>
       <c r="K153" t="str">
-        <v/>
+        <v>jeanrichardwatches</v>
       </c>
       <c r="L153" t="str">
         <v>MBWDB</v>
@@ -6742,8 +6742,8 @@
       <c r="C155" t="str">
         <v/>
       </c>
-      <c r="D155" t="str">
-        <v/>
+      <c r="D155">
+        <v>1861</v>
       </c>
       <c r="E155">
         <v>1190</v>
@@ -6758,7 +6758,7 @@
         <v>Aquaris Diver</v>
       </c>
       <c r="I155" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J155" t="str">
         <v>https://www.junghans.de</v>
@@ -6783,20 +6783,20 @@
       <c r="C156" t="str">
         <v/>
       </c>
-      <c r="D156" t="str">
-        <v/>
-      </c>
-      <c r="E156" t="str">
-        <v/>
-      </c>
-      <c r="F156" t="str">
-        <v/>
+      <c r="D156">
+        <v>1897</v>
+      </c>
+      <c r="E156">
+        <v>300</v>
+      </c>
+      <c r="F156">
+        <v>800</v>
       </c>
       <c r="G156" t="str">
         <v>Active</v>
       </c>
       <c r="H156" t="str">
-        <v/>
+        <v>Junkers Bauhaus</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -6805,7 +6805,7 @@
         <v>https://www.junkers-watches.com</v>
       </c>
       <c r="K156" t="str">
-        <v/>
+        <v>junkers_watches</v>
       </c>
       <c r="L156" t="str">
         <v>MBWDB</v>
@@ -6878,10 +6878,10 @@
         <v>Active</v>
       </c>
       <c r="H158" t="str">
-        <v/>
+        <v>EINSER Voyager</v>
       </c>
       <c r="I158" t="str">
-        <v/>
+        <v>2025-02-25</v>
       </c>
       <c r="J158" t="str">
         <v>https://www.kallinichclaeys.com</v>
@@ -7001,10 +7001,10 @@
         <v>Active</v>
       </c>
       <c r="H161" t="str">
-        <v/>
+        <v>Montre Héritage Croco - édition spéciale 70 ans</v>
       </c>
       <c r="I161" t="str">
-        <v/>
+        <v>2024-04-01</v>
       </c>
       <c r="J161" t="str">
         <v>https://www.kelton.fr</v>
@@ -7051,7 +7051,7 @@
         <v>https://www.kerbedanz.com</v>
       </c>
       <c r="K162" t="str">
-        <v/>
+        <v>kerbedanz_official</v>
       </c>
       <c r="L162" t="str">
         <v>MBWDB</v>
@@ -7127,7 +7127,7 @@
         <v>Klok-01 5th Anniversary</v>
       </c>
       <c r="I164" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J164" t="str">
         <v>https://www.klokers.com</v>
@@ -7152,20 +7152,20 @@
       <c r="C165" t="str">
         <v/>
       </c>
-      <c r="D165" t="str">
-        <v/>
-      </c>
-      <c r="E165" t="str">
-        <v/>
-      </c>
-      <c r="F165" t="str">
-        <v/>
+      <c r="D165">
+        <v>1916</v>
+      </c>
+      <c r="E165">
+        <v>179</v>
+      </c>
+      <c r="F165">
+        <v>269</v>
       </c>
       <c r="G165" t="str">
         <v>Active</v>
       </c>
       <c r="H165" t="str">
-        <v/>
+        <v>Cult Diver</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -7316,23 +7316,23 @@
       <c r="C169" t="str">
         <v>Sainte-Suzanne</v>
       </c>
-      <c r="D169" t="str">
-        <v/>
-      </c>
-      <c r="E169" t="str">
-        <v/>
-      </c>
-      <c r="F169" t="str">
-        <v/>
+      <c r="D169">
+        <v>1839</v>
+      </c>
+      <c r="E169">
+        <v>27500</v>
+      </c>
+      <c r="F169">
+        <v>220000</v>
       </c>
       <c r="G169" t="str">
         <v>Active</v>
       </c>
       <c r="H169" t="str">
-        <v/>
+        <v>Creative Art Residency</v>
       </c>
       <c r="I169" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J169" t="str">
         <v>https://www.lepee1839.com</v>
@@ -7357,14 +7357,14 @@
       <c r="C170" t="str">
         <v>Geneva</v>
       </c>
-      <c r="D170" t="str">
-        <v/>
-      </c>
-      <c r="E170" t="str">
-        <v/>
-      </c>
-      <c r="F170" t="str">
-        <v/>
+      <c r="D170">
+        <v>2011</v>
+      </c>
+      <c r="E170">
+        <v>2250</v>
+      </c>
+      <c r="F170">
+        <v>6720</v>
       </c>
       <c r="G170" t="str">
         <v>Active</v>
@@ -7373,7 +7373,7 @@
         <v>AIKON</v>
       </c>
       <c r="I170" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J170" t="str">
         <v>https://www.labelnoir.com</v>
@@ -7414,7 +7414,7 @@
         <v>Laco Köln</v>
       </c>
       <c r="I171" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J171" t="str">
         <v>https://www.laco.de</v>
@@ -7534,10 +7534,10 @@
         <v>Active</v>
       </c>
       <c r="H174" t="str">
-        <v/>
+        <v>Bobby</v>
       </c>
       <c r="I174" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J174" t="str">
         <v>https://www.laps.fr</v>
@@ -7660,7 +7660,7 @@
         <v>Heritage Small Seconds</v>
       </c>
       <c r="I177" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J177" t="str">
         <v>https://www.leboisandco.com</v>
@@ -7701,7 +7701,7 @@
         <v>Huxley II</v>
       </c>
       <c r="I178" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J178" t="str">
         <v>https://www.lilienthal-berlin.com</v>
@@ -7729,11 +7729,11 @@
       <c r="D179">
         <v>2004</v>
       </c>
-      <c r="E179" t="str">
-        <v/>
-      </c>
-      <c r="F179" t="str">
-        <v/>
+      <c r="E179">
+        <v>20500</v>
+      </c>
+      <c r="F179">
+        <v>56000</v>
       </c>
       <c r="G179" t="str">
         <v>Active</v>
@@ -7742,7 +7742,7 @@
         <v>Oktopus III</v>
       </c>
       <c r="I179" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J179" t="str">
         <v>https://www.lindewerdelin.com</v>
@@ -7783,7 +7783,7 @@
         <v>Type 14</v>
       </c>
       <c r="I180" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J180" t="str">
         <v>https://www.lip.fr</v>
@@ -7821,10 +7821,10 @@
         <v>Active</v>
       </c>
       <c r="H181" t="str">
-        <v/>
+        <v>Frecce Tricolori Edizione Limitata - 65°</v>
       </c>
       <c r="I181" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J181" t="str">
         <v>https://www.locman.it</v>
@@ -7865,7 +7865,7 @@
         <v>Mare 300 MT</v>
       </c>
       <c r="I182" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J182" t="str">
         <v>https://www.locman.com</v>
@@ -7893,20 +7893,20 @@
       <c r="D183" t="str">
         <v/>
       </c>
-      <c r="E183" t="str">
-        <v/>
-      </c>
-      <c r="F183" t="str">
-        <v/>
+      <c r="E183">
+        <v>1890</v>
+      </c>
+      <c r="F183">
+        <v>1890</v>
       </c>
       <c r="G183" t="str">
         <v>Active</v>
       </c>
       <c r="H183" t="str">
-        <v/>
+        <v>Model No.2 Chronograph</v>
       </c>
       <c r="I183" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J183" t="str">
         <v>https://www.lorcawatches.com</v>
@@ -7937,8 +7937,8 @@
       <c r="E184">
         <v>4400</v>
       </c>
-      <c r="F184" t="str">
-        <v/>
+      <c r="F184">
+        <v>17300</v>
       </c>
       <c r="G184" t="str">
         <v>Active</v>
@@ -7947,7 +7947,7 @@
         <v>Louis Erard x Kudoke Le Régulateur Forest Green</v>
       </c>
       <c r="I184" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J184" t="str">
         <v>https://www.louiserard.com</v>
@@ -7985,10 +7985,10 @@
         <v>Active</v>
       </c>
       <c r="H185" t="str">
-        <v/>
+        <v>Mechanica Karel Rotation</v>
       </c>
       <c r="I185" t="str">
-        <v/>
+        <v>2024-12-31</v>
       </c>
       <c r="J185" t="str">
         <v>https://www.serynwatches.com</v>
@@ -8098,20 +8098,20 @@
       <c r="D188" t="str">
         <v/>
       </c>
-      <c r="E188" t="str">
-        <v/>
-      </c>
-      <c r="F188" t="str">
-        <v/>
+      <c r="E188">
+        <v>8000</v>
+      </c>
+      <c r="F188">
+        <v>12700</v>
       </c>
       <c r="G188" t="str">
         <v>Active</v>
       </c>
       <c r="H188" t="str">
-        <v/>
+        <v>Persée</v>
       </c>
       <c r="I188" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J188" t="str">
         <v>https://www.maison-alcee.com</v>
@@ -8139,20 +8139,20 @@
       <c r="D189" t="str">
         <v/>
       </c>
-      <c r="E189" t="str">
-        <v/>
-      </c>
-      <c r="F189" t="str">
-        <v/>
+      <c r="E189">
+        <v>1050</v>
+      </c>
+      <c r="F189">
+        <v>1850</v>
       </c>
       <c r="G189" t="str">
         <v>Active</v>
       </c>
       <c r="H189" t="str">
-        <v/>
+        <v>MM25-08</v>
       </c>
       <c r="I189" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J189" t="str">
         <v>https://www.maisonmorfin.com</v>
@@ -8218,14 +8218,14 @@
       <c r="C191" t="str">
         <v/>
       </c>
-      <c r="D191" t="str">
-        <v/>
-      </c>
-      <c r="E191" t="str">
-        <v/>
-      </c>
-      <c r="F191" t="str">
-        <v/>
+      <c r="D191">
+        <v>2014</v>
+      </c>
+      <c r="E191">
+        <v>400</v>
+      </c>
+      <c r="F191">
+        <v>800</v>
       </c>
       <c r="G191" t="str">
         <v>Active</v>
@@ -8240,7 +8240,7 @@
         <v>https://www.marc-and-sons.com</v>
       </c>
       <c r="K191" t="str">
-        <v/>
+        <v>marcandsonswatches</v>
       </c>
       <c r="L191" t="str">
         <v>MBWDB</v>
@@ -8303,20 +8303,20 @@
       <c r="D193" t="str">
         <v/>
       </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
-        <v/>
+      <c r="E193">
+        <v>775</v>
+      </c>
+      <c r="F193">
+        <v>2900</v>
       </c>
       <c r="G193" t="str">
         <v>Active</v>
       </c>
       <c r="H193" t="str">
-        <v/>
+        <v>AM2 AUTOMATIQUE NYCTALOPE CARBONE - Millésime Mars 2026</v>
       </c>
       <c r="I193" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J193" t="str">
         <v>https://www.march-lab.com</v>
@@ -8423,14 +8423,14 @@
       <c r="C196" t="str">
         <v/>
       </c>
-      <c r="D196" t="str">
-        <v/>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
-        <v/>
+      <c r="D196">
+        <v>2015</v>
+      </c>
+      <c r="E196">
+        <v>350</v>
+      </c>
+      <c r="F196">
+        <v>650</v>
       </c>
       <c r="G196" t="str">
         <v>Active</v>
@@ -8445,7 +8445,7 @@
         <v>https://www.marloewatchco.com</v>
       </c>
       <c r="K196" t="str">
-        <v/>
+        <v>marloewatch</v>
       </c>
       <c r="L196" t="str">
         <v>MBWDB</v>
@@ -8477,7 +8477,7 @@
         <v>Active</v>
       </c>
       <c r="H197" t="str">
-        <v/>
+        <v>Aerodyne</v>
       </c>
       <c r="I197" t="str">
         <v/>
@@ -8505,8 +8505,8 @@
       <c r="C198" t="str">
         <v>Paris</v>
       </c>
-      <c r="D198" t="str">
-        <v/>
+      <c r="D198">
+        <v>2004</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -8521,7 +8521,7 @@
         <v>Timer Pro</v>
       </c>
       <c r="I198" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J198" t="str">
         <v>https://www.matwatches.com</v>
@@ -8546,14 +8546,14 @@
       <c r="C199" t="str">
         <v/>
       </c>
-      <c r="D199" t="str">
-        <v/>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v/>
+      <c r="D199">
+        <v>1886</v>
+      </c>
+      <c r="E199">
+        <v>400</v>
+      </c>
+      <c r="F199">
+        <v>1200</v>
       </c>
       <c r="G199" t="str">
         <v>Active</v>
@@ -8568,7 +8568,7 @@
         <v>https://www.mathey-tissot.com</v>
       </c>
       <c r="K199" t="str">
-        <v/>
+        <v>matheytissot</v>
       </c>
       <c r="L199" t="str">
         <v>MBWDB</v>
@@ -8603,13 +8603,13 @@
         <v/>
       </c>
       <c r="I200" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J200" t="str">
         <v>https://www.mauricedemauriac.ch</v>
       </c>
       <c r="K200" t="str">
-        <v/>
+        <v>mauricedemauriac</v>
       </c>
       <c r="L200" t="str">
         <v>existing-db</v>
@@ -8631,11 +8631,11 @@
       <c r="D201" t="str">
         <v/>
       </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v/>
+      <c r="E201">
+        <v>15620</v>
+      </c>
+      <c r="F201">
+        <v>84700</v>
       </c>
       <c r="G201" t="str">
         <v>Active</v>
@@ -8644,7 +8644,7 @@
         <v>MU06 UNIX</v>
       </c>
       <c r="I201" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J201" t="str">
         <v>https://www.mauronmusy.com</v>
@@ -8669,14 +8669,14 @@
       <c r="C202" t="str">
         <v/>
       </c>
-      <c r="D202" t="str">
-        <v/>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v/>
+      <c r="D202">
+        <v>2010</v>
+      </c>
+      <c r="E202">
+        <v>400</v>
+      </c>
+      <c r="F202">
+        <v>800</v>
       </c>
       <c r="G202" t="str">
         <v>Active</v>
@@ -8691,7 +8691,7 @@
         <v>https://www.meccanichevenziane.com</v>
       </c>
       <c r="K202" t="str">
-        <v/>
+        <v>meccanichevenziane</v>
       </c>
       <c r="L202" t="str">
         <v>MBWDB</v>
@@ -8726,13 +8726,13 @@
         <v>Panthero Jumping Hour</v>
       </c>
       <c r="I203" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J203" t="str">
         <v>https://www.meistersinger.com</v>
       </c>
       <c r="K203" t="str">
-        <v/>
+        <v>meistersinger_official</v>
       </c>
       <c r="L203" t="str">
         <v>MBWDB</v>
@@ -8836,20 +8836,20 @@
       <c r="D206" t="str">
         <v/>
       </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v/>
+      <c r="E206">
+        <v>1670</v>
+      </c>
+      <c r="F206">
+        <v>3850</v>
       </c>
       <c r="G206" t="str">
         <v>Active</v>
       </c>
       <c r="H206" t="str">
-        <v/>
+        <v>Milgraph T5 Pilot Series Worldtimer</v>
       </c>
       <c r="I206" t="str">
-        <v/>
+        <v>2025-08-14</v>
       </c>
       <c r="J206" t="str">
         <v>https://www.micromilspec.com</v>
@@ -8874,29 +8874,29 @@
       <c r="C207" t="str">
         <v/>
       </c>
-      <c r="D207" t="str">
-        <v/>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v/>
+      <c r="D207">
+        <v>2012</v>
+      </c>
+      <c r="E207">
+        <v>2500</v>
+      </c>
+      <c r="F207">
+        <v>5000</v>
       </c>
       <c r="G207" t="str">
         <v>Active</v>
       </c>
       <c r="H207" t="str">
-        <v/>
+        <v>TriCompax</v>
       </c>
       <c r="I207" t="str">
-        <v/>
+        <v>2024-09-01</v>
       </c>
       <c r="J207" t="str">
         <v>https://www.milus.ch</v>
       </c>
       <c r="K207" t="str">
-        <v/>
+        <v>milus_watches</v>
       </c>
       <c r="L207" t="str">
         <v>MBWDB</v>
@@ -8915,8 +8915,8 @@
       <c r="C208" t="str">
         <v/>
       </c>
-      <c r="D208" t="str">
-        <v/>
+      <c r="D208">
+        <v>1858</v>
       </c>
       <c r="E208" t="str">
         <v/>
@@ -8959,20 +8959,20 @@
       <c r="D209" t="str">
         <v/>
       </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v/>
+      <c r="E209">
+        <v>88</v>
+      </c>
+      <c r="F209">
+        <v>765</v>
       </c>
       <c r="G209" t="str">
         <v>Active</v>
       </c>
       <c r="H209" t="str">
-        <v/>
+        <v>ORIGINALE - Monkeybird</v>
       </c>
       <c r="I209" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J209" t="str">
         <v>https://www.monawatches.com</v>
@@ -9000,20 +9000,20 @@
       <c r="D210" t="str">
         <v/>
       </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v/>
+      <c r="E210">
+        <v>375</v>
+      </c>
+      <c r="F210">
+        <v>1065</v>
       </c>
       <c r="G210" t="str">
         <v>Active</v>
       </c>
       <c r="H210" t="str">
-        <v/>
+        <v>stop2go</v>
       </c>
       <c r="I210" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J210" t="str">
         <v>https://www.mondaine.com</v>
@@ -9126,17 +9126,17 @@
       <c r="E213">
         <v>225</v>
       </c>
-      <c r="F213" t="str">
-        <v/>
+      <c r="F213">
+        <v>3125</v>
       </c>
       <c r="G213" t="str">
         <v>Active</v>
       </c>
       <c r="H213" t="str">
-        <v/>
+        <v>Daydreamer</v>
       </c>
       <c r="I213" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J213" t="str">
         <v>https://www.mrjoneswatches.com</v>
@@ -9202,29 +9202,29 @@
       <c r="C215" t="str">
         <v/>
       </c>
-      <c r="D215" t="str">
-        <v/>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v/>
+      <c r="D215">
+        <v>1926</v>
+      </c>
+      <c r="E215">
+        <v>400</v>
+      </c>
+      <c r="F215">
+        <v>800</v>
       </c>
       <c r="G215" t="str">
         <v>Active</v>
       </c>
       <c r="H215" t="str">
-        <v/>
+        <v>Grenchen</v>
       </c>
       <c r="I215" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J215" t="str">
         <v>https://www.nivada.ch</v>
       </c>
       <c r="K215" t="str">
-        <v/>
+        <v>nivadawatches</v>
       </c>
       <c r="L215" t="str">
         <v>MBWDB</v>
@@ -9284,29 +9284,29 @@
       <c r="C217" t="str">
         <v/>
       </c>
-      <c r="D217" t="str">
-        <v/>
-      </c>
-      <c r="E217" t="str">
-        <v/>
-      </c>
-      <c r="F217" t="str">
-        <v/>
+      <c r="D217">
+        <v>2017</v>
+      </c>
+      <c r="E217">
+        <v>400</v>
+      </c>
+      <c r="F217">
+        <v>800</v>
       </c>
       <c r="G217" t="str">
         <v>Active</v>
       </c>
       <c r="H217" t="str">
-        <v/>
+        <v>Avalon</v>
       </c>
       <c r="I217" t="str">
-        <v/>
+        <v>2024-09-01</v>
       </c>
       <c r="J217" t="str">
         <v>https://www.noduswatch.com</v>
       </c>
       <c r="K217" t="str">
-        <v/>
+        <v>noduswatch</v>
       </c>
       <c r="L217" t="str">
         <v>MBWDB</v>
@@ -9325,14 +9325,14 @@
       <c r="C218" t="str">
         <v/>
       </c>
-      <c r="D218" t="str">
-        <v/>
-      </c>
-      <c r="E218" t="str">
-        <v/>
-      </c>
-      <c r="F218" t="str">
-        <v/>
+      <c r="D218">
+        <v>2017</v>
+      </c>
+      <c r="E218">
+        <v>295</v>
+      </c>
+      <c r="F218">
+        <v>695</v>
       </c>
       <c r="G218" t="str">
         <v>Active</v>
@@ -9347,7 +9347,7 @@
         <v>https://www.nordgreen.io</v>
       </c>
       <c r="K218" t="str">
-        <v/>
+        <v>nordgreenofficial</v>
       </c>
       <c r="L218" t="str">
         <v>MBWDB</v>
@@ -9366,23 +9366,23 @@
       <c r="C219" t="str">
         <v/>
       </c>
-      <c r="D219" t="str">
-        <v/>
-      </c>
-      <c r="E219" t="str">
-        <v/>
-      </c>
-      <c r="F219" t="str">
-        <v/>
+      <c r="D219">
+        <v>2010</v>
+      </c>
+      <c r="E219">
+        <v>3500</v>
+      </c>
+      <c r="F219">
+        <v>17000</v>
       </c>
       <c r="G219" t="str">
         <v>Active</v>
       </c>
       <c r="H219" t="str">
-        <v/>
+        <v>Wild ONE of 1</v>
       </c>
       <c r="I219" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J219" t="str">
         <v>https://www.norqain.com</v>
@@ -9489,23 +9489,23 @@
       <c r="C222" t="str">
         <v>Geneva</v>
       </c>
-      <c r="D222" t="str">
-        <v/>
-      </c>
-      <c r="E222" t="str">
-        <v/>
-      </c>
-      <c r="F222" t="str">
-        <v/>
+      <c r="D222">
+        <v>2022</v>
+      </c>
+      <c r="E222">
+        <v>3500</v>
+      </c>
+      <c r="F222">
+        <v>11000</v>
       </c>
       <c r="G222" t="str">
         <v>Active</v>
       </c>
       <c r="H222" t="str">
-        <v/>
+        <v>OLIGO FM01</v>
       </c>
       <c r="I222" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J222" t="str">
         <v>https://www.oligowatches.com</v>
@@ -9669,7 +9669,7 @@
         <v>Sector</v>
       </c>
       <c r="I226" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J226" t="str">
         <v>https://www.pareawatches.com</v>
@@ -9779,11 +9779,11 @@
       <c r="D229">
         <v>2013</v>
       </c>
-      <c r="E229" t="str">
-        <v/>
-      </c>
-      <c r="F229" t="str">
-        <v/>
+      <c r="E229">
+        <v>1238</v>
+      </c>
+      <c r="F229">
+        <v>2564</v>
       </c>
       <c r="G229" t="str">
         <v>Active</v>
@@ -9792,7 +9792,7 @@
         <v>Pure</v>
       </c>
       <c r="I229" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J229" t="str">
         <v>https://www.pinionwatches.com</v>
@@ -9940,8 +9940,8 @@
       <c r="C233" t="str">
         <v/>
       </c>
-      <c r="D233" t="str">
-        <v/>
+      <c r="D233">
+        <v>1949</v>
       </c>
       <c r="E233" t="str">
         <v/>
@@ -9953,10 +9953,10 @@
         <v>Active</v>
       </c>
       <c r="H233" t="str">
-        <v/>
+        <v>PRIM Orlík ARMA LE</v>
       </c>
       <c r="I233" t="str">
-        <v/>
+        <v>2024-12-31</v>
       </c>
       <c r="J233" t="str">
         <v>https://www.prim.cz</v>
@@ -9984,26 +9984,26 @@
       <c r="D234" t="str">
         <v/>
       </c>
-      <c r="E234" t="str">
-        <v/>
-      </c>
-      <c r="F234" t="str">
-        <v/>
+      <c r="E234">
+        <v>2500</v>
+      </c>
+      <c r="F234">
+        <v>21000</v>
       </c>
       <c r="G234" t="str">
         <v>Active</v>
       </c>
       <c r="H234" t="str">
-        <v/>
+        <v>QLOCKTWO W</v>
       </c>
       <c r="I234" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J234" t="str">
         <v>https://www.qlocktwo.com</v>
       </c>
       <c r="K234" t="str">
-        <v/>
+        <v>qlocktwo</v>
       </c>
       <c r="L234" t="str">
         <v>existing-db</v>
@@ -10079,7 +10079,7 @@
         <v>ATMAUS</v>
       </c>
       <c r="I236" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J236" t="str">
         <v>https://www.radial-watch.com</v>
@@ -10186,23 +10186,23 @@
       <c r="C239" t="str">
         <v>La Rochelle</v>
       </c>
-      <c r="D239" t="str">
-        <v/>
-      </c>
-      <c r="E239" t="str">
-        <v/>
-      </c>
-      <c r="F239" t="str">
-        <v/>
+      <c r="D239">
+        <v>1996</v>
+      </c>
+      <c r="E239">
+        <v>1800</v>
+      </c>
+      <c r="F239">
+        <v>8200</v>
       </c>
       <c r="G239" t="str">
         <v>Active</v>
       </c>
       <c r="H239" t="str">
-        <v/>
+        <v>WRX Automatic Carbon Tech Shark</v>
       </c>
       <c r="I239" t="str">
-        <v/>
+        <v>2026-03-01</v>
       </c>
       <c r="J239" t="str">
         <v>https://www.ralftech.com</v>
@@ -10230,11 +10230,11 @@
       <c r="D240" t="str">
         <v/>
       </c>
-      <c r="E240" t="str">
-        <v/>
-      </c>
-      <c r="F240" t="str">
-        <v/>
+      <c r="E240">
+        <v>876</v>
+      </c>
+      <c r="F240">
+        <v>2895</v>
       </c>
       <c r="G240" t="str">
         <v>Active</v>
@@ -10243,7 +10243,7 @@
         <v>Habu DNA Edition</v>
       </c>
       <c r="I240" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J240" t="str">
         <v>https://www.recwatches.com</v>
@@ -10281,7 +10281,7 @@
         <v>Active</v>
       </c>
       <c r="H241" t="str">
-        <v/>
+        <v>390 Fastback</v>
       </c>
       <c r="I241" t="str">
         <v/>
@@ -10325,7 +10325,7 @@
         <v>TYPE 9 IKEDA</v>
       </c>
       <c r="I242" t="str">
-        <v/>
+        <v>2024-12-31</v>
       </c>
       <c r="J242" t="str">
         <v>https://www.ressencewatches.com</v>
@@ -10350,14 +10350,14 @@
       <c r="C243" t="str">
         <v/>
       </c>
-      <c r="D243" t="str">
-        <v/>
-      </c>
-      <c r="E243" t="str">
-        <v/>
-      </c>
-      <c r="F243" t="str">
-        <v/>
+      <c r="D243">
+        <v>1853</v>
+      </c>
+      <c r="E243">
+        <v>2500</v>
+      </c>
+      <c r="F243">
+        <v>8000</v>
       </c>
       <c r="G243" t="str">
         <v>Active</v>
@@ -10372,7 +10372,7 @@
         <v>https://www.revue-thommen.com</v>
       </c>
       <c r="K243" t="str">
-        <v/>
+        <v>revuethommen</v>
       </c>
       <c r="L243" t="str">
         <v>MBWDB</v>
@@ -10391,23 +10391,23 @@
       <c r="C244" t="str">
         <v/>
       </c>
-      <c r="D244" t="str">
-        <v/>
-      </c>
-      <c r="E244" t="str">
-        <v/>
-      </c>
-      <c r="F244" t="str">
-        <v/>
+      <c r="D244">
+        <v>1888</v>
+      </c>
+      <c r="E244">
+        <v>247</v>
+      </c>
+      <c r="F244">
+        <v>842</v>
       </c>
       <c r="G244" t="str">
         <v>Active</v>
       </c>
       <c r="H244" t="str">
-        <v/>
+        <v>Deep Sea Automatic 43mm</v>
       </c>
       <c r="I244" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J244" t="str">
         <v>https://www.roamer.ch</v>
@@ -10473,14 +10473,14 @@
       <c r="C246" t="str">
         <v/>
       </c>
-      <c r="D246" t="str">
-        <v/>
-      </c>
-      <c r="E246" t="str">
-        <v/>
-      </c>
-      <c r="F246" t="str">
-        <v/>
+      <c r="D246">
+        <v>1895</v>
+      </c>
+      <c r="E246">
+        <v>150</v>
+      </c>
+      <c r="F246">
+        <v>800</v>
       </c>
       <c r="G246" t="str">
         <v>Active</v>
@@ -10495,7 +10495,7 @@
         <v>https://www.rotary.swiss</v>
       </c>
       <c r="K246" t="str">
-        <v/>
+        <v>rotarywatches</v>
       </c>
       <c r="L246" t="str">
         <v>MBWDB</v>
@@ -10530,7 +10530,7 @@
         <v>OCTA Open Heart Automatique</v>
       </c>
       <c r="I247" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J247" t="str">
         <v>https://www.rswswiss.com</v>
@@ -10596,14 +10596,14 @@
       <c r="C249" t="str">
         <v/>
       </c>
-      <c r="D249" t="str">
-        <v/>
-      </c>
-      <c r="E249" t="str">
-        <v/>
-      </c>
-      <c r="F249" t="str">
-        <v/>
+      <c r="D249">
+        <v>1927</v>
+      </c>
+      <c r="E249">
+        <v>400</v>
+      </c>
+      <c r="F249">
+        <v>1200</v>
       </c>
       <c r="G249" t="str">
         <v>Active</v>
@@ -10618,7 +10618,7 @@
         <v>https://www.ferragamo.com</v>
       </c>
       <c r="K249" t="str">
-        <v/>
+        <v>ferragamo</v>
       </c>
       <c r="L249" t="str">
         <v>MBWDB</v>
@@ -10681,11 +10681,11 @@
       <c r="D251" t="str">
         <v/>
       </c>
-      <c r="E251" t="str">
-        <v/>
-      </c>
-      <c r="F251" t="str">
-        <v/>
+      <c r="E251">
+        <v>3050</v>
+      </c>
+      <c r="F251">
+        <v>5920</v>
       </c>
       <c r="G251" t="str">
         <v>Active</v>
@@ -10694,7 +10694,7 @@
         <v>Octolune</v>
       </c>
       <c r="I251" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J251" t="str">
         <v>https://www.schaefer-and-companions.art</v>
@@ -10760,20 +10760,20 @@
       <c r="C253" t="str">
         <v/>
       </c>
-      <c r="D253" t="str">
-        <v/>
-      </c>
-      <c r="E253" t="str">
-        <v/>
-      </c>
-      <c r="F253" t="str">
-        <v/>
+      <c r="D253">
+        <v>2014</v>
+      </c>
+      <c r="E253">
+        <v>395</v>
+      </c>
+      <c r="F253">
+        <v>595</v>
       </c>
       <c r="G253" t="str">
         <v>Active</v>
       </c>
       <c r="H253" t="str">
-        <v/>
+        <v>The GMT</v>
       </c>
       <c r="I253" t="str">
         <v/>
@@ -10782,7 +10782,7 @@
         <v>https://www.schofieldwatches.com</v>
       </c>
       <c r="K253" t="str">
-        <v/>
+        <v>schofieldwatches</v>
       </c>
       <c r="L253" t="str">
         <v>MBWDB</v>
@@ -10804,11 +10804,11 @@
       <c r="D254" t="str">
         <v/>
       </c>
-      <c r="E254" t="str">
-        <v/>
-      </c>
-      <c r="F254" t="str">
-        <v/>
+      <c r="E254">
+        <v>220</v>
+      </c>
+      <c r="F254">
+        <v>530</v>
       </c>
       <c r="G254" t="str">
         <v>Active</v>
@@ -10817,7 +10817,7 @@
         <v>Diver One D1-500</v>
       </c>
       <c r="I254" t="str">
-        <v/>
+        <v>2026-03-06</v>
       </c>
       <c r="J254" t="str">
         <v>https://www.scurfawatches.com</v>
@@ -10883,8 +10883,8 @@
       <c r="C256" t="str">
         <v/>
       </c>
-      <c r="D256" t="str">
-        <v/>
+      <c r="D256">
+        <v>1966</v>
       </c>
       <c r="E256" t="str">
         <v/>
@@ -10899,7 +10899,7 @@
         <v/>
       </c>
       <c r="I256" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J256" t="str">
         <v>https://www.sekonda.co.uk</v>
@@ -11006,29 +11006,29 @@
       <c r="C259" t="str">
         <v/>
       </c>
-      <c r="D259" t="str">
-        <v/>
-      </c>
-      <c r="E259" t="str">
-        <v/>
-      </c>
-      <c r="F259" t="str">
-        <v/>
+      <c r="D259">
+        <v>2012</v>
+      </c>
+      <c r="E259">
+        <v>400</v>
+      </c>
+      <c r="F259">
+        <v>800</v>
       </c>
       <c r="G259" t="str">
         <v>Active</v>
       </c>
       <c r="H259" t="str">
-        <v/>
+        <v>Serica Field Watch</v>
       </c>
       <c r="I259" t="str">
-        <v/>
+        <v>2024-09-15</v>
       </c>
       <c r="J259" t="str">
         <v>https://www.serica.watches</v>
       </c>
       <c r="K259" t="str">
-        <v/>
+        <v>serica_watches</v>
       </c>
       <c r="L259" t="str">
         <v>MBWDB</v>
@@ -11060,7 +11060,7 @@
         <v>Active</v>
       </c>
       <c r="H260" t="str">
-        <v/>
+        <v>Ultradive</v>
       </c>
       <c r="I260" t="str">
         <v/>
@@ -11088,8 +11088,8 @@
       <c r="C261" t="str">
         <v/>
       </c>
-      <c r="D261" t="str">
-        <v/>
+      <c r="D261">
+        <v>1961</v>
       </c>
       <c r="E261" t="str">
         <v/>
@@ -11104,7 +11104,7 @@
         <v/>
       </c>
       <c r="I261" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J261" t="str">
         <v>https://www.sinn.de</v>
@@ -11132,20 +11132,20 @@
       <c r="D262" t="str">
         <v/>
       </c>
-      <c r="E262" t="str">
-        <v/>
-      </c>
-      <c r="F262" t="str">
-        <v/>
+      <c r="E262">
+        <v>4000</v>
+      </c>
+      <c r="F262">
+        <v>4800</v>
       </c>
       <c r="G262" t="str">
         <v>Active</v>
       </c>
       <c r="H262" t="str">
-        <v/>
+        <v>Annual Edition 2025</v>
       </c>
       <c r="I262" t="str">
-        <v/>
+        <v>2025-01-15</v>
       </c>
       <c r="J262" t="str">
         <v>https://www.sjoosandstrom.com</v>
@@ -11170,29 +11170,29 @@
       <c r="C263" t="str">
         <v/>
       </c>
-      <c r="D263" t="str">
-        <v/>
-      </c>
-      <c r="E263" t="str">
-        <v/>
-      </c>
-      <c r="F263" t="str">
-        <v/>
+      <c r="D263">
+        <v>1851</v>
+      </c>
+      <c r="E263">
+        <v>400</v>
+      </c>
+      <c r="F263">
+        <v>800</v>
       </c>
       <c r="G263" t="str">
         <v>Active</v>
       </c>
       <c r="H263" t="str">
-        <v/>
+        <v>Everest</v>
       </c>
       <c r="I263" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J263" t="str">
         <v>https://www.smiths-watches.co.uk</v>
       </c>
       <c r="K263" t="str">
-        <v/>
+        <v>smithswatches</v>
       </c>
       <c r="L263" t="str">
         <v>MBWDB</v>
@@ -11309,7 +11309,7 @@
         <v>Ripples Kármán Line</v>
       </c>
       <c r="I266" t="str">
-        <v/>
+        <v>2025-03-11</v>
       </c>
       <c r="J266" t="str">
         <v>https://www.speake-marin.com</v>
@@ -11337,20 +11337,20 @@
       <c r="D267">
         <v>1959</v>
       </c>
-      <c r="E267" t="str">
-        <v/>
-      </c>
-      <c r="F267" t="str">
-        <v/>
+      <c r="E267">
+        <v>999</v>
+      </c>
+      <c r="F267">
+        <v>1750</v>
       </c>
       <c r="G267" t="str">
         <v>Active</v>
       </c>
       <c r="H267" t="str">
-        <v/>
+        <v>Squale Matic S</v>
       </c>
       <c r="I267" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J267" t="str">
         <v>https://www.squalewatches.com</v>
@@ -11416,23 +11416,23 @@
       <c r="C269" t="str">
         <v/>
       </c>
-      <c r="D269" t="str">
-        <v/>
-      </c>
-      <c r="E269" t="str">
-        <v/>
-      </c>
-      <c r="F269" t="str">
-        <v/>
+      <c r="D269">
+        <v>2001</v>
+      </c>
+      <c r="E269">
+        <v>400</v>
+      </c>
+      <c r="F269">
+        <v>800</v>
       </c>
       <c r="G269" t="str">
         <v>Active</v>
       </c>
       <c r="H269" t="str">
-        <v/>
+        <v>Ocean One</v>
       </c>
       <c r="I269" t="str">
-        <v/>
+        <v>2024-10-15</v>
       </c>
       <c r="J269" t="str">
         <v>https://www.steinhartwatches.de</v>
@@ -11457,8 +11457,8 @@
       <c r="C270" t="str">
         <v>Hamburg</v>
       </c>
-      <c r="D270" t="str">
-        <v/>
+      <c r="D270">
+        <v>2016</v>
       </c>
       <c r="E270">
         <v>210</v>
@@ -11473,7 +11473,7 @@
         <v>Marus 2.0 Edition Küste</v>
       </c>
       <c r="I270" t="str">
-        <v/>
+        <v>2025-12-03</v>
       </c>
       <c r="J270" t="str">
         <v>https://www.sternglas.com</v>
@@ -11514,7 +11514,7 @@
         <v>Chrono Black Forest Moon</v>
       </c>
       <c r="I271" t="str">
-        <v/>
+        <v>2024-11-01</v>
       </c>
       <c r="J271" t="str">
         <v>https://www.stowa.de</v>
@@ -11583,20 +11583,20 @@
       <c r="D273" t="str">
         <v/>
       </c>
-      <c r="E273" t="str">
-        <v/>
-      </c>
-      <c r="F273" t="str">
-        <v/>
+      <c r="E273">
+        <v>2206</v>
+      </c>
+      <c r="F273">
+        <v>2206</v>
       </c>
       <c r="G273" t="str">
         <v>Active</v>
       </c>
       <c r="H273" t="str">
-        <v/>
+        <v>Salmon</v>
       </c>
       <c r="I273" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J273" t="str">
         <v>https://underd0g.com</v>
@@ -11678,7 +11678,7 @@
         <v>Dark Matter</v>
       </c>
       <c r="I275" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J275" t="str">
         <v>https://www.swissmilitary.ch</v>
@@ -11706,20 +11706,20 @@
       <c r="D276" t="str">
         <v/>
       </c>
-      <c r="E276" t="str">
-        <v/>
-      </c>
-      <c r="F276" t="str">
-        <v/>
+      <c r="E276">
+        <v>498</v>
+      </c>
+      <c r="F276">
+        <v>823</v>
       </c>
       <c r="G276" t="str">
         <v>Active</v>
       </c>
       <c r="H276" t="str">
-        <v/>
+        <v>Cannonball GMT</v>
       </c>
       <c r="I276" t="str">
-        <v/>
+        <v>2024-12-31</v>
       </c>
       <c r="J276" t="str">
         <v>https://www.syewatches.com</v>
@@ -11867,23 +11867,23 @@
       <c r="C280" t="str">
         <v/>
       </c>
-      <c r="D280" t="str">
-        <v/>
-      </c>
-      <c r="E280" t="str">
-        <v/>
-      </c>
-      <c r="F280" t="str">
-        <v/>
+      <c r="D280">
+        <v>1996</v>
+      </c>
+      <c r="E280">
+        <v>280</v>
+      </c>
+      <c r="F280">
+        <v>620</v>
       </c>
       <c r="G280" t="str">
         <v>Active</v>
       </c>
       <c r="H280" t="str">
-        <v/>
+        <v>Smiths Commander 71 PRS-71</v>
       </c>
       <c r="I280" t="str">
-        <v/>
+        <v>2026-03-10</v>
       </c>
       <c r="J280" t="str">
         <v>https://www.timefactors.com</v>
@@ -11990,29 +11990,29 @@
       <c r="C283" t="str">
         <v/>
       </c>
-      <c r="D283" t="str">
-        <v/>
-      </c>
-      <c r="E283" t="str">
-        <v/>
-      </c>
-      <c r="F283" t="str">
-        <v/>
+      <c r="D283">
+        <v>2014</v>
+      </c>
+      <c r="E283">
+        <v>400</v>
+      </c>
+      <c r="F283">
+        <v>800</v>
       </c>
       <c r="G283" t="str">
         <v>Active</v>
       </c>
       <c r="H283" t="str">
-        <v/>
+        <v>1000M</v>
       </c>
       <c r="I283" t="str">
-        <v/>
+        <v>2024-06-01</v>
       </c>
       <c r="J283" t="str">
         <v>https://www.trematic.de</v>
       </c>
       <c r="K283" t="str">
-        <v/>
+        <v>trematic_watches</v>
       </c>
       <c r="L283" t="str">
         <v>MBWDB</v>
@@ -12044,16 +12044,16 @@
         <v>Active</v>
       </c>
       <c r="H284" t="str">
-        <v/>
+        <v>Aquatic Nevil</v>
       </c>
       <c r="I284" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J284" t="str">
         <v>https://www.triwa.com</v>
       </c>
       <c r="K284" t="str">
-        <v/>
+        <v>triwa</v>
       </c>
       <c r="L284" t="str">
         <v>MBWDB</v>
@@ -12113,8 +12113,8 @@
       <c r="C286" t="str">
         <v/>
       </c>
-      <c r="D286" t="str">
-        <v/>
+      <c r="D286">
+        <v>1927</v>
       </c>
       <c r="E286" t="str">
         <v/>
@@ -12126,7 +12126,7 @@
         <v>Active</v>
       </c>
       <c r="H286" t="str">
-        <v/>
+        <v>Hommage Minute Repeater</v>
       </c>
       <c r="I286" t="str">
         <v/>
@@ -12154,23 +12154,23 @@
       <c r="C287" t="str">
         <v/>
       </c>
-      <c r="D287" t="str">
-        <v/>
-      </c>
-      <c r="E287" t="str">
-        <v/>
-      </c>
-      <c r="F287" t="str">
-        <v/>
+      <c r="D287">
+        <v>2005</v>
+      </c>
+      <c r="E287">
+        <v>375</v>
+      </c>
+      <c r="F287">
+        <v>1180</v>
       </c>
       <c r="G287" t="str">
         <v>Active</v>
       </c>
       <c r="H287" t="str">
-        <v/>
+        <v>ACE Genesis</v>
       </c>
       <c r="I287" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J287" t="str">
         <v>https://www.twsteel.com</v>
@@ -12198,11 +12198,11 @@
       <c r="D288">
         <v>2000</v>
       </c>
-      <c r="E288" t="str">
-        <v/>
-      </c>
-      <c r="F288" t="str">
-        <v/>
+      <c r="E288">
+        <v>1070</v>
+      </c>
+      <c r="F288">
+        <v>109000</v>
       </c>
       <c r="G288" t="str">
         <v>Active</v>
@@ -12211,7 +12211,7 @@
         <v>Black Widow</v>
       </c>
       <c r="I288" t="str">
-        <v/>
+        <v>2025-12-10</v>
       </c>
       <c r="J288" t="str">
         <v>https://www.uboatwatch.com</v>
@@ -12249,7 +12249,7 @@
         <v>Active</v>
       </c>
       <c r="H289" t="str">
-        <v/>
+        <v>TREK DUAL SERIES 01</v>
       </c>
       <c r="I289" t="str">
         <v/>
@@ -12318,14 +12318,14 @@
       <c r="C291" t="str">
         <v/>
       </c>
-      <c r="D291" t="str">
-        <v/>
-      </c>
-      <c r="E291" t="str">
-        <v/>
-      </c>
-      <c r="F291" t="str">
-        <v/>
+      <c r="D291">
+        <v>2014</v>
+      </c>
+      <c r="E291">
+        <v>300</v>
+      </c>
+      <c r="F291">
+        <v>800</v>
       </c>
       <c r="G291" t="str">
         <v>Active</v>
@@ -12340,7 +12340,7 @@
         <v>https://www.undonewatches.com</v>
       </c>
       <c r="K291" t="str">
-        <v/>
+        <v>undone_watches</v>
       </c>
       <c r="L291" t="str">
         <v>MBWDB</v>
@@ -12362,20 +12362,20 @@
       <c r="D292" t="str">
         <v/>
       </c>
-      <c r="E292" t="str">
-        <v/>
-      </c>
-      <c r="F292" t="str">
-        <v/>
+      <c r="E292">
+        <v>470</v>
+      </c>
+      <c r="F292">
+        <v>1770</v>
       </c>
       <c r="G292" t="str">
         <v>Active</v>
       </c>
       <c r="H292" t="str">
-        <v/>
+        <v>Modello Tre U3FB-ROPS</v>
       </c>
       <c r="I292" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J292" t="str">
         <v>https://www.unimaticwatches.com</v>
@@ -12523,8 +12523,8 @@
       <c r="C296" t="str">
         <v/>
       </c>
-      <c r="D296" t="str">
-        <v/>
+      <c r="D296">
+        <v>2011</v>
       </c>
       <c r="E296" t="str">
         <v/>
@@ -12567,20 +12567,20 @@
       <c r="D297" t="str">
         <v/>
       </c>
-      <c r="E297" t="str">
-        <v/>
-      </c>
-      <c r="F297" t="str">
-        <v/>
+      <c r="E297">
+        <v>950</v>
+      </c>
+      <c r="F297">
+        <v>4900</v>
       </c>
       <c r="G297" t="str">
         <v>Active</v>
       </c>
       <c r="H297" t="str">
-        <v/>
+        <v>Redentore Utopia II</v>
       </c>
       <c r="I297" t="str">
-        <v/>
+        <v>2026-01-25</v>
       </c>
       <c r="J297" t="str">
         <v>https://www.venezianico.it</v>
@@ -12621,7 +12621,7 @@
         <v>M60 AquaLion</v>
       </c>
       <c r="I298" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J298" t="str">
         <v>https://www.vertexwatches.com</v>
@@ -12703,7 +12703,7 @@
         <v/>
       </c>
       <c r="I300" t="str">
-        <v/>
+        <v>2024</v>
       </c>
       <c r="J300" t="str">
         <v>https://www.victorinox.com</v>
@@ -12785,7 +12785,7 @@
         <v/>
       </c>
       <c r="I302" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J302" t="str">
         <v>https://www.voxelwatches.com</v>
@@ -12810,29 +12810,29 @@
       <c r="C303" t="str">
         <v/>
       </c>
-      <c r="D303" t="str">
-        <v/>
-      </c>
-      <c r="E303" t="str">
-        <v/>
-      </c>
-      <c r="F303" t="str">
-        <v/>
+      <c r="D303">
+        <v>1858</v>
+      </c>
+      <c r="E303">
+        <v>3000</v>
+      </c>
+      <c r="F303">
+        <v>8000</v>
       </c>
       <c r="G303" t="str">
         <v>Active</v>
       </c>
       <c r="H303" t="str">
-        <v/>
+        <v>Cricket Nautical</v>
       </c>
       <c r="I303" t="str">
-        <v/>
+        <v>2024-09-01</v>
       </c>
       <c r="J303" t="str">
         <v>https://www.vulcain-watches.com</v>
       </c>
       <c r="K303" t="str">
-        <v/>
+        <v>vulcain_watches</v>
       </c>
       <c r="L303" t="str">
         <v>MBWDB</v>
@@ -12854,20 +12854,20 @@
       <c r="D304">
         <v>2015</v>
       </c>
-      <c r="E304" t="str">
-        <v/>
-      </c>
-      <c r="F304" t="str">
-        <v/>
+      <c r="E304">
+        <v>3475</v>
+      </c>
+      <c r="F304">
+        <v>3475</v>
       </c>
       <c r="G304" t="str">
         <v>Active</v>
       </c>
       <c r="H304" t="str">
-        <v/>
+        <v>Velocity</v>
       </c>
       <c r="I304" t="str">
-        <v/>
+        <v>2025-07-10</v>
       </c>
       <c r="J304" t="str">
         <v>https://www.wessexwatches.co.uk</v>
@@ -12908,7 +12908,7 @@
         <v>Pan4Timer® Automatic</v>
       </c>
       <c r="I305" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J305" t="str">
         <v>https://www.wolbrook.com</v>
@@ -12936,20 +12936,20 @@
       <c r="D306">
         <v>1948</v>
       </c>
-      <c r="E306" t="str">
-        <v/>
-      </c>
-      <c r="F306" t="str">
-        <v/>
+      <c r="E306">
+        <v>449</v>
+      </c>
+      <c r="F306">
+        <v>13000</v>
       </c>
       <c r="G306" t="str">
         <v>Active</v>
       </c>
       <c r="H306" t="str">
-        <v/>
+        <v>Superman Titanium MoonTide CMM.11 Limited Edition</v>
       </c>
       <c r="I306" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J306" t="str">
         <v>https://www.yema.com</v>
@@ -13015,14 +13015,14 @@
       <c r="C308" t="str">
         <v/>
       </c>
-      <c r="D308" t="str">
-        <v/>
-      </c>
-      <c r="E308" t="str">
-        <v/>
-      </c>
-      <c r="F308" t="str">
-        <v/>
+      <c r="D308">
+        <v>1960</v>
+      </c>
+      <c r="E308">
+        <v>400</v>
+      </c>
+      <c r="F308">
+        <v>2000</v>
       </c>
       <c r="G308" t="str">
         <v>Active</v>
@@ -13037,7 +13037,7 @@
         <v>https://www.zenowatch.ch</v>
       </c>
       <c r="K308" t="str">
-        <v/>
+        <v>zenowatch</v>
       </c>
       <c r="L308" t="str">
         <v>MBWDB</v>
@@ -13056,20 +13056,20 @@
       <c r="C309" t="str">
         <v/>
       </c>
-      <c r="D309" t="str">
-        <v/>
-      </c>
-      <c r="E309" t="str">
-        <v/>
-      </c>
-      <c r="F309" t="str">
-        <v/>
+      <c r="D309">
+        <v>2017</v>
+      </c>
+      <c r="E309">
+        <v>400</v>
+      </c>
+      <c r="F309">
+        <v>800</v>
       </c>
       <c r="G309" t="str">
         <v>Active</v>
       </c>
       <c r="H309" t="str">
-        <v/>
+        <v>Dubnium</v>
       </c>
       <c r="I309" t="str">
         <v/>
@@ -13078,7 +13078,7 @@
         <v>https://www.zinvo.com</v>
       </c>
       <c r="K309" t="str">
-        <v/>
+        <v>zinvo_watches</v>
       </c>
       <c r="L309" t="str">
         <v>MBWDB</v>
@@ -13113,7 +13113,7 @@
         <v>PHENIX Q157</v>
       </c>
       <c r="I310" t="str">
-        <v/>
+        <v>2024-01-11</v>
       </c>
       <c r="J310" t="str">
         <v>https://www.zrc1904.com</v>
@@ -13246,14 +13246,14 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
+      <c r="D3">
+        <v>2003</v>
+      </c>
+      <c r="E3">
+        <v>95</v>
+      </c>
+      <c r="F3">
+        <v>500</v>
       </c>
       <c r="G3" t="str">
         <v>Active</v>
@@ -13268,7 +13268,7 @@
         <v>https://akriboswatches.com</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>akriboswatches</v>
       </c>
       <c r="L3" t="str">
         <v>MBWDB</v>
@@ -13382,7 +13382,7 @@
         <v>Active</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>A1</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -13426,7 +13426,7 @@
         <v>Trove Series</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>2025-09-29</v>
       </c>
       <c r="J7" t="str">
         <v>https://artefktwatches.com</v>
@@ -13467,7 +13467,7 @@
         <v>Terra Scout</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>2026-02-01</v>
       </c>
       <c r="J8" t="str">
         <v>https://astorandbanks.com</v>
@@ -13549,7 +13549,7 @@
         <v>Quantum</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>2025-12-22</v>
       </c>
       <c r="J10" t="str">
         <v>https://audazwatches.com</v>
@@ -13574,8 +13574,8 @@
       <c r="C11" t="str">
         <v>New York, New York</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
+      <c r="D11">
+        <v>2011</v>
       </c>
       <c r="E11">
         <v>525</v>
@@ -13590,7 +13590,7 @@
         <v>racing team chronograph</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>2026-04-06</v>
       </c>
       <c r="J11" t="str">
         <v>https://www.autodromo.com</v>
@@ -13656,29 +13656,29 @@
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
+      <c r="D13">
+        <v>2012</v>
+      </c>
+      <c r="E13">
+        <v>595</v>
+      </c>
+      <c r="F13">
+        <v>795</v>
       </c>
       <c r="G13" t="str">
         <v>Active</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Makai</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>2024-10-15</v>
       </c>
       <c r="J13" t="str">
         <v>https://www.bathyshawaii.com</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>bathyshawaii</v>
       </c>
       <c r="L13" t="str">
         <v>MBWDB</v>
@@ -13697,20 +13697,20 @@
       <c r="C14" t="str">
         <v>Honolulu, Hawaii</v>
       </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
+      <c r="D14">
+        <v>2012</v>
+      </c>
+      <c r="E14">
+        <v>495</v>
+      </c>
+      <c r="F14">
+        <v>595</v>
       </c>
       <c r="G14" t="str">
         <v>Active</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Kahala</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -13719,7 +13719,7 @@
         <v>https://www.bathys.com</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>bathyshawaii</v>
       </c>
       <c r="L14" t="str">
         <v>existing-db</v>
@@ -13738,20 +13738,20 @@
       <c r="C15" t="str">
         <v/>
       </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
+      <c r="D15">
+        <v>2010</v>
+      </c>
+      <c r="E15">
+        <v>495</v>
+      </c>
+      <c r="F15">
+        <v>795</v>
       </c>
       <c r="G15" t="str">
         <v>Active</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Deep Diver</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -13760,7 +13760,7 @@
         <v>https://www.benarus.com</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>benaruswatches</v>
       </c>
       <c r="L15" t="str">
         <v>MBWDB</v>
@@ -13779,14 +13779,14 @@
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
+      <c r="D16">
+        <v>2023</v>
+      </c>
+      <c r="E16">
+        <v>630</v>
+      </c>
+      <c r="F16">
+        <v>1200</v>
       </c>
       <c r="G16" t="str">
         <v>Active</v>
@@ -13795,7 +13795,7 @@
         <v>Scarifour Automatic</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>2026-01-08</v>
       </c>
       <c r="J16" t="str">
         <v>https://benjaminjameswatches.com</v>
@@ -13820,14 +13820,14 @@
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v/>
+      <c r="D17">
+        <v>1921</v>
+      </c>
+      <c r="E17">
+        <v>300</v>
+      </c>
+      <c r="F17">
+        <v>600</v>
       </c>
       <c r="G17" t="str">
         <v>Active</v>
@@ -13839,10 +13839,10 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>https://www.benruswatches.com</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>benruswatches</v>
       </c>
       <c r="L17" t="str">
         <v>MBWDB</v>
@@ -13943,29 +13943,29 @@
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
+      <c r="D20">
+        <v>1990</v>
+      </c>
+      <c r="E20">
+        <v>295</v>
+      </c>
+      <c r="F20">
+        <v>595</v>
       </c>
       <c r="G20" t="str">
         <v>Active</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>Analog II</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>2024-09-15</v>
       </c>
       <c r="J20" t="str">
         <v>https://www.bertucci.com</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>bertucciwatch</v>
       </c>
       <c r="L20" t="str">
         <v>MBWDB</v>
@@ -13987,11 +13987,11 @@
       <c r="D21" t="str">
         <v/>
       </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
+      <c r="E21">
+        <v>301</v>
+      </c>
+      <c r="F21">
+        <v>872</v>
       </c>
       <c r="G21" t="str">
         <v>Active</v>
@@ -14000,7 +14000,7 @@
         <v>Odyssey MGP</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J21" t="str">
         <v>https://www.boldrwatches.com</v>
@@ -14025,14 +14025,14 @@
       <c r="C22" t="str">
         <v/>
       </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v/>
+      <c r="D22">
+        <v>2013</v>
+      </c>
+      <c r="E22">
+        <v>300</v>
+      </c>
+      <c r="F22">
+        <v>600</v>
       </c>
       <c r="G22" t="str">
         <v>Active</v>
@@ -14047,7 +14047,7 @@
         <v>https://www.borealiswatches.com</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>borealiswatches</v>
       </c>
       <c r="L22" t="str">
         <v>MBWDB</v>
@@ -14082,7 +14082,7 @@
         <v>Nocturne Time Ring</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J23" t="str">
         <v>https://www.bredawatches.com</v>
@@ -14120,7 +14120,7 @@
         <v>Active</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>Super Metric</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -14148,29 +14148,29 @@
       <c r="C25" t="str">
         <v/>
       </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v/>
+      <c r="D25">
+        <v>2011</v>
+      </c>
+      <c r="E25">
+        <v>295</v>
+      </c>
+      <c r="F25">
+        <v>495</v>
       </c>
       <c r="G25" t="str">
         <v>Active</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>Dial Automatic</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>2024-08-15</v>
       </c>
       <c r="J25" t="str">
         <v>https://www.californiawatch.co</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>californiawatch</v>
       </c>
       <c r="L25" t="str">
         <v>MBWDB</v>
@@ -14271,14 +14271,14 @@
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <v/>
+      <c r="D28">
+        <v>2009</v>
+      </c>
+      <c r="E28">
+        <v>1200</v>
+      </c>
+      <c r="F28">
+        <v>2500</v>
       </c>
       <c r="G28" t="str">
         <v>Active</v>
@@ -14293,7 +14293,7 @@
         <v>https://www.chasedurer.com</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>chasedurer</v>
       </c>
       <c r="L28" t="str">
         <v>MBWDB</v>
@@ -14394,14 +14394,14 @@
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-      <c r="F31" t="str">
-        <v/>
+      <c r="D31">
+        <v>2016</v>
+      </c>
+      <c r="E31">
+        <v>449</v>
+      </c>
+      <c r="F31">
+        <v>449</v>
       </c>
       <c r="G31" t="str">
         <v>Active</v>
@@ -14410,7 +14410,7 @@
         <v>Mechanic Ocean Mark II</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J31" t="str">
         <v>https://www.crafterblue.com</v>
@@ -14435,14 +14435,14 @@
       <c r="C32" t="str">
         <v/>
       </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
-      <c r="F32" t="str">
-        <v/>
+      <c r="D32">
+        <v>1970</v>
+      </c>
+      <c r="E32">
+        <v>200</v>
+      </c>
+      <c r="F32">
+        <v>600</v>
       </c>
       <c r="G32" t="str">
         <v>Active</v>
@@ -14454,10 +14454,10 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>https://www.crotonwatch.com</v>
       </c>
       <c r="K32" t="str">
-        <v/>
+        <v>crotonwatches</v>
       </c>
       <c r="L32" t="str">
         <v>MBWDB</v>
@@ -14476,23 +14476,23 @@
       <c r="C33" t="str">
         <v/>
       </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
-      <c r="E33" t="str">
-        <v/>
-      </c>
-      <c r="F33" t="str">
-        <v/>
+      <c r="D33">
+        <v>1972</v>
+      </c>
+      <c r="E33">
+        <v>399</v>
+      </c>
+      <c r="F33">
+        <v>4995</v>
       </c>
       <c r="G33" t="str">
         <v>Active</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>G40</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>2025-12-11</v>
       </c>
       <c r="J33" t="str">
         <v>https://www.cwcwatch.com</v>
@@ -14517,14 +14517,14 @@
       <c r="C34" t="str">
         <v/>
       </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
-      <c r="E34" t="str">
-        <v/>
-      </c>
-      <c r="F34" t="str">
-        <v/>
+      <c r="D34">
+        <v>2011</v>
+      </c>
+      <c r="E34">
+        <v>300</v>
+      </c>
+      <c r="F34">
+        <v>600</v>
       </c>
       <c r="G34" t="str">
         <v>Active</v>
@@ -14539,7 +14539,7 @@
         <v>https://www.dagazwatch.com</v>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>dagazwatch</v>
       </c>
       <c r="L34" t="str">
         <v>MBWDB</v>
@@ -14561,17 +14561,17 @@
       <c r="D35" t="str">
         <v/>
       </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35" t="str">
-        <v/>
+      <c r="E35">
+        <v>230</v>
+      </c>
+      <c r="F35">
+        <v>380</v>
       </c>
       <c r="G35" t="str">
         <v>Active</v>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>1975 Skin Diver</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -14615,7 +14615,7 @@
         <v>Ocean Mariner 300</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J36" t="str">
         <v>https://www.deepbluewatches.com</v>
@@ -14763,14 +14763,14 @@
       <c r="C40" t="str">
         <v/>
       </c>
-      <c r="D40" t="str">
-        <v/>
-      </c>
-      <c r="E40" t="str">
-        <v/>
-      </c>
-      <c r="F40" t="str">
-        <v/>
+      <c r="D40">
+        <v>2014</v>
+      </c>
+      <c r="E40">
+        <v>295</v>
+      </c>
+      <c r="F40">
+        <v>595</v>
       </c>
       <c r="G40" t="str">
         <v>Active</v>
@@ -14785,7 +14785,7 @@
         <v>https://www.egardwatch.com</v>
       </c>
       <c r="K40" t="str">
-        <v/>
+        <v>egardwatch</v>
       </c>
       <c r="L40" t="str">
         <v>MBWDB</v>
@@ -14820,7 +14820,7 @@
         <v>Bradley Element Black</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J41" t="str">
         <v>https://www.eone-time.com</v>
@@ -14927,14 +14927,14 @@
       <c r="C44" t="str">
         <v/>
       </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v/>
+      <c r="D44">
+        <v>1758</v>
+      </c>
+      <c r="E44">
+        <v>295</v>
+      </c>
+      <c r="F44">
+        <v>895</v>
       </c>
       <c r="G44" t="str">
         <v>Active</v>
@@ -14946,10 +14946,10 @@
         <v/>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>https://www.gevrilgroup.com</v>
       </c>
       <c r="K44" t="str">
-        <v/>
+        <v>gevrilgroup</v>
       </c>
       <c r="L44" t="str">
         <v>MBWDB</v>
@@ -14968,20 +14968,20 @@
       <c r="C45" t="str">
         <v/>
       </c>
-      <c r="D45" t="str">
-        <v/>
-      </c>
-      <c r="E45" t="str">
-        <v/>
-      </c>
-      <c r="F45" t="str">
-        <v/>
+      <c r="D45">
+        <v>2017</v>
+      </c>
+      <c r="E45">
+        <v>395</v>
+      </c>
+      <c r="F45">
+        <v>595</v>
       </c>
       <c r="G45" t="str">
         <v>Active</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>Ocean Rover</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -14990,7 +14990,7 @@
         <v>https://www.ginaultocean.com</v>
       </c>
       <c r="K45" t="str">
-        <v/>
+        <v>ginaultwatches</v>
       </c>
       <c r="L45" t="str">
         <v>MBWDB</v>
@@ -15091,14 +15091,14 @@
       <c r="C48" t="str">
         <v/>
       </c>
-      <c r="D48" t="str">
-        <v/>
-      </c>
-      <c r="E48" t="str">
-        <v/>
-      </c>
-      <c r="F48" t="str">
-        <v/>
+      <c r="D48">
+        <v>2015</v>
+      </c>
+      <c r="E48">
+        <v>395</v>
+      </c>
+      <c r="F48">
+        <v>695</v>
       </c>
       <c r="G48" t="str">
         <v>Active</v>
@@ -15113,7 +15113,7 @@
         <v>https://www.helgraywatch.com</v>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>helgraywatch</v>
       </c>
       <c r="L48" t="str">
         <v>MBWDB</v>
@@ -15176,20 +15176,20 @@
       <c r="D50" t="str">
         <v/>
       </c>
-      <c r="E50" t="str">
-        <v/>
-      </c>
-      <c r="F50" t="str">
-        <v/>
+      <c r="E50">
+        <v>585</v>
+      </c>
+      <c r="F50">
+        <v>1065</v>
       </c>
       <c r="G50" t="str">
         <v>Active</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>Bexley</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J50" t="str">
         <v>https://www.heritorwatches.com</v>
@@ -15214,14 +15214,14 @@
       <c r="C51" t="str">
         <v/>
       </c>
-      <c r="D51" t="str">
-        <v/>
-      </c>
-      <c r="E51" t="str">
-        <v/>
-      </c>
-      <c r="F51" t="str">
-        <v/>
+      <c r="D51">
+        <v>1892</v>
+      </c>
+      <c r="E51">
+        <v>150</v>
+      </c>
+      <c r="F51">
+        <v>500</v>
       </c>
       <c r="G51" t="str">
         <v>Active</v>
@@ -15236,7 +15236,7 @@
         <v>https://www.ingersollwatches.com</v>
       </c>
       <c r="K51" t="str">
-        <v/>
+        <v>ingersollwatches</v>
       </c>
       <c r="L51" t="str">
         <v>MBWDB</v>
@@ -15271,7 +15271,7 @@
         <v>I-Tech</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J52" t="str">
         <v>https://www.invictawatch.com</v>
@@ -15337,14 +15337,14 @@
       <c r="C54" t="str">
         <v/>
       </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
-      <c r="E54" t="str">
-        <v/>
-      </c>
-      <c r="F54" t="str">
-        <v/>
+      <c r="D54">
+        <v>2015</v>
+      </c>
+      <c r="E54">
+        <v>350</v>
+      </c>
+      <c r="F54">
+        <v>650</v>
       </c>
       <c r="G54" t="str">
         <v>Active</v>
@@ -15359,7 +15359,7 @@
         <v>https://www.lewhuey.com</v>
       </c>
       <c r="K54" t="str">
-        <v/>
+        <v>lewandhuey</v>
       </c>
       <c r="L54" t="str">
         <v>MBWDB</v>
@@ -15391,10 +15391,10 @@
         <v>Active</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>Astra</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J55" t="str">
         <v>https://www.lorierwatches.com</v>
@@ -15422,20 +15422,20 @@
       <c r="D56" t="str">
         <v/>
       </c>
-      <c r="E56" t="str">
-        <v/>
-      </c>
-      <c r="F56" t="str">
-        <v/>
+      <c r="E56">
+        <v>445</v>
+      </c>
+      <c r="F56">
+        <v>960</v>
       </c>
       <c r="G56" t="str">
         <v>Active</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>M94 Bronze Date</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J56" t="str">
         <v>https://www.lum-tec.com</v>
@@ -15501,14 +15501,14 @@
       <c r="C58" t="str">
         <v/>
       </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
-      <c r="E58" t="str">
-        <v/>
-      </c>
-      <c r="F58" t="str">
-        <v/>
+      <c r="D58">
+        <v>1939</v>
+      </c>
+      <c r="E58">
+        <v>1600</v>
+      </c>
+      <c r="F58">
+        <v>5900</v>
       </c>
       <c r="G58" t="str">
         <v>Active</v>
@@ -15517,7 +15517,7 @@
         <v>Anthracite</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>2024-12-20</v>
       </c>
       <c r="J58" t="str">
         <v>https://www.marathonwatch.com</v>
@@ -15583,14 +15583,14 @@
       <c r="C60" t="str">
         <v/>
       </c>
-      <c r="D60" t="str">
-        <v/>
-      </c>
-      <c r="E60" t="str">
-        <v/>
-      </c>
-      <c r="F60" t="str">
-        <v/>
+      <c r="D60">
+        <v>2012</v>
+      </c>
+      <c r="E60">
+        <v>400</v>
+      </c>
+      <c r="F60">
+        <v>800</v>
       </c>
       <c r="G60" t="str">
         <v>Active</v>
@@ -15605,7 +15605,7 @@
         <v>https://minus8watches.com</v>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>minus8watches</v>
       </c>
       <c r="L60" t="str">
         <v>MBWDB</v>
@@ -15627,11 +15627,11 @@
       <c r="D61" t="str">
         <v/>
       </c>
-      <c r="E61" t="str">
-        <v/>
-      </c>
-      <c r="F61" t="str">
-        <v/>
+      <c r="E61">
+        <v>1995</v>
+      </c>
+      <c r="F61">
+        <v>1995</v>
       </c>
       <c r="G61" t="str">
         <v>Active</v>
@@ -15640,7 +15640,7 @@
         <v>Project Recover Baku Edition</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>2023-05-16</v>
       </c>
       <c r="J61" t="str">
         <v>https://www.mkiiwatches.com</v>
@@ -15668,11 +15668,11 @@
       <c r="D62" t="str">
         <v/>
       </c>
-      <c r="E62" t="str">
-        <v/>
-      </c>
-      <c r="F62" t="str">
-        <v/>
+      <c r="E62">
+        <v>1995</v>
+      </c>
+      <c r="F62">
+        <v>1995</v>
       </c>
       <c r="G62" t="str">
         <v>Active</v>
@@ -15681,7 +15681,7 @@
         <v>Project Recover BAKU Edition</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>2023-05-16</v>
       </c>
       <c r="J62" t="str">
         <v>https://www.mkiiwatches.com</v>
@@ -15722,7 +15722,7 @@
         <v>Splash Eclipse</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J63" t="str">
         <v>https://www.momentumwatch.com</v>
@@ -15763,7 +15763,7 @@
         <v>Triumph</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J64" t="str">
         <v>https://www.montawatch.com</v>
@@ -15791,11 +15791,11 @@
       <c r="D65" t="str">
         <v/>
       </c>
-      <c r="E65" t="str">
-        <v/>
-      </c>
-      <c r="F65" t="str">
-        <v/>
+      <c r="E65">
+        <v>295</v>
+      </c>
+      <c r="F65">
+        <v>775</v>
       </c>
       <c r="G65" t="str">
         <v>Active</v>
@@ -15804,7 +15804,7 @@
         <v>M61 Series</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J65" t="str">
         <v>https://www.morphicwatches.com</v>
@@ -15829,14 +15829,14 @@
       <c r="C66" t="str">
         <v/>
       </c>
-      <c r="D66" t="str">
-        <v/>
-      </c>
-      <c r="E66" t="str">
-        <v/>
-      </c>
-      <c r="F66" t="str">
-        <v/>
+      <c r="D66">
+        <v>2009</v>
+      </c>
+      <c r="E66">
+        <v>295</v>
+      </c>
+      <c r="F66">
+        <v>595</v>
       </c>
       <c r="G66" t="str">
         <v>Active</v>
@@ -15851,7 +15851,7 @@
         <v>https://www.mulcowatches.com</v>
       </c>
       <c r="K66" t="str">
-        <v/>
+        <v>mulcowatches</v>
       </c>
       <c r="L66" t="str">
         <v>MBWDB</v>
@@ -15873,20 +15873,20 @@
       <c r="D67" t="str">
         <v/>
       </c>
-      <c r="E67" t="str">
-        <v/>
-      </c>
-      <c r="F67" t="str">
-        <v/>
+      <c r="E67">
+        <v>160</v>
+      </c>
+      <c r="F67">
+        <v>690</v>
       </c>
       <c r="G67" t="str">
         <v>Active</v>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>Admiralty Pro</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J67" t="str">
         <v>https://www.nautiswatches.com</v>
@@ -15927,7 +15927,7 @@
         <v>Sector Deep</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J68" t="str">
         <v>https://www.noduswatches.com</v>
@@ -15952,29 +15952,29 @@
       <c r="C69" t="str">
         <v/>
       </c>
-      <c r="D69" t="str">
-        <v/>
-      </c>
-      <c r="E69" t="str">
-        <v/>
-      </c>
-      <c r="F69" t="str">
-        <v/>
+      <c r="D69">
+        <v>2017</v>
+      </c>
+      <c r="E69">
+        <v>395</v>
+      </c>
+      <c r="F69">
+        <v>595</v>
       </c>
       <c r="G69" t="str">
         <v>Active</v>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>Subs</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>2024-09-15</v>
       </c>
       <c r="J69" t="str">
         <v>https://www.nthwatches.com</v>
       </c>
       <c r="K69" t="str">
-        <v/>
+        <v>nthorological</v>
       </c>
       <c r="L69" t="str">
         <v>MBWDB</v>
@@ -16009,7 +16009,7 @@
         <v>Torrent Automatic Atari Rainbow Limited Edition</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>2026-04-01</v>
       </c>
       <c r="J70" t="str">
         <v>https://www.nubeowatches.com</v>
@@ -16034,14 +16034,14 @@
       <c r="C71" t="str">
         <v>Chicago, Illinois</v>
       </c>
-      <c r="D71" t="str">
-        <v/>
-      </c>
-      <c r="E71" t="str">
-        <v/>
-      </c>
-      <c r="F71" t="str">
-        <v/>
+      <c r="D71">
+        <v>2015</v>
+      </c>
+      <c r="E71">
+        <v>1211</v>
+      </c>
+      <c r="F71">
+        <v>2038</v>
       </c>
       <c r="G71" t="str">
         <v>Active</v>
@@ -16050,7 +16050,7 @@
         <v>The Atwood Chronograph</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>2026-03-02</v>
       </c>
       <c r="J71" t="str">
         <v>https://www.oakandoscar.com</v>
@@ -16075,20 +16075,20 @@
       <c r="C72" t="str">
         <v/>
       </c>
-      <c r="D72" t="str">
-        <v/>
-      </c>
-      <c r="E72" t="str">
-        <v/>
-      </c>
-      <c r="F72" t="str">
-        <v/>
+      <c r="D72">
+        <v>2012</v>
+      </c>
+      <c r="E72">
+        <v>400</v>
+      </c>
+      <c r="F72">
+        <v>600</v>
       </c>
       <c r="G72" t="str">
         <v>Active</v>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>Core Diver</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -16097,7 +16097,7 @@
         <v>https://www.oceancrawlerwatch.com</v>
       </c>
       <c r="K72" t="str">
-        <v/>
+        <v>oceancrawlerwatch</v>
       </c>
       <c r="L72" t="str">
         <v>MBWDB</v>
@@ -16116,29 +16116,29 @@
       <c r="C73" t="str">
         <v/>
       </c>
-      <c r="D73" t="str">
-        <v/>
-      </c>
-      <c r="E73" t="str">
-        <v/>
-      </c>
-      <c r="F73" t="str">
-        <v/>
+      <c r="D73">
+        <v>2015</v>
+      </c>
+      <c r="E73">
+        <v>495</v>
+      </c>
+      <c r="F73">
+        <v>795</v>
       </c>
       <c r="G73" t="str">
         <v>Active</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>Titanium Deep Ocean Automatic</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>2024-10-15</v>
       </c>
       <c r="J73" t="str">
         <v>https://www.oceaneva.com</v>
       </c>
       <c r="K73" t="str">
-        <v/>
+        <v>oceaneva_watches</v>
       </c>
       <c r="L73" t="str">
         <v>MBWDB</v>
@@ -16157,29 +16157,29 @@
       <c r="C74" t="str">
         <v/>
       </c>
-      <c r="D74" t="str">
-        <v/>
-      </c>
-      <c r="E74" t="str">
-        <v/>
-      </c>
-      <c r="F74" t="str">
-        <v/>
+      <c r="D74">
+        <v>2012</v>
+      </c>
+      <c r="E74">
+        <v>2500</v>
+      </c>
+      <c r="F74">
+        <v>4500</v>
       </c>
       <c r="G74" t="str">
         <v>Active</v>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>Deep Sea Automatic</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J74" t="str">
         <v>https://www.ocean-x.com</v>
       </c>
       <c r="K74" t="str">
-        <v/>
+        <v>oceanxwatch</v>
       </c>
       <c r="L74" t="str">
         <v>MBWDB</v>
@@ -16198,14 +16198,14 @@
       <c r="C75" t="str">
         <v/>
       </c>
-      <c r="D75" t="str">
-        <v/>
+      <c r="D75">
+        <v>2013</v>
       </c>
       <c r="E75">
         <v>349</v>
       </c>
-      <c r="F75" t="str">
-        <v/>
+      <c r="F75">
+        <v>384</v>
       </c>
       <c r="G75" t="str">
         <v>Active</v>
@@ -16214,13 +16214,13 @@
         <v>Ancient Malachite Stone Watch</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J75" t="str">
         <v>https://www.originalgrain.com</v>
       </c>
       <c r="K75" t="str">
-        <v/>
+        <v>originalgrain</v>
       </c>
       <c r="L75" t="str">
         <v>MBWDB</v>
@@ -16296,7 +16296,7 @@
         <v>Jungle Field Automatic 38</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J77" t="str">
         <v>https://www.praesidus.com</v>
@@ -16362,8 +16362,8 @@
       <c r="C79" t="str">
         <v/>
       </c>
-      <c r="D79" t="str">
-        <v/>
+      <c r="D79">
+        <v>1992</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -16406,11 +16406,11 @@
       <c r="D80" t="str">
         <v/>
       </c>
-      <c r="E80" t="str">
-        <v/>
-      </c>
-      <c r="F80" t="str">
-        <v/>
+      <c r="E80">
+        <v>138</v>
+      </c>
+      <c r="F80">
+        <v>552</v>
       </c>
       <c r="G80" t="str">
         <v>Active</v>
@@ -16419,7 +16419,7 @@
         <v/>
       </c>
       <c r="I80" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J80" t="str">
         <v>https://www.sophieandfreda.com</v>
@@ -16444,8 +16444,8 @@
       <c r="C81" t="str">
         <v/>
       </c>
-      <c r="D81" t="str">
-        <v/>
+      <c r="D81">
+        <v>1924</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -16463,7 +16463,7 @@
         <v/>
       </c>
       <c r="J81" t="str">
-        <v/>
+        <v>https://www.speidel.com</v>
       </c>
       <c r="K81" t="str">
         <v/>
@@ -16501,7 +16501,7 @@
         <v>Fleuss 40 Automatic</v>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>2024-03-24</v>
       </c>
       <c r="J82" t="str">
         <v>https://www.spinnaker-watches.com</v>
@@ -16526,23 +16526,23 @@
       <c r="C83" t="str">
         <v/>
       </c>
-      <c r="D83" t="str">
-        <v/>
-      </c>
-      <c r="E83" t="str">
-        <v/>
-      </c>
-      <c r="F83" t="str">
-        <v/>
+      <c r="D83">
+        <v>2004</v>
+      </c>
+      <c r="E83">
+        <v>99</v>
+      </c>
+      <c r="F83">
+        <v>249</v>
       </c>
       <c r="G83" t="str">
         <v>Active</v>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>Swiss Tactical Watch</v>
       </c>
       <c r="I83" t="str">
-        <v/>
+        <v>2024-12-23</v>
       </c>
       <c r="J83" t="str">
         <v>https://www.stauer.com</v>
@@ -16567,14 +16567,14 @@
       <c r="C84" t="str">
         <v/>
       </c>
-      <c r="D84" t="str">
-        <v/>
-      </c>
-      <c r="E84" t="str">
-        <v/>
-      </c>
-      <c r="F84" t="str">
-        <v/>
+      <c r="D84">
+        <v>2012</v>
+      </c>
+      <c r="E84">
+        <v>295</v>
+      </c>
+      <c r="F84">
+        <v>495</v>
       </c>
       <c r="G84" t="str">
         <v>Active</v>
@@ -16589,7 +16589,7 @@
         <v>https://www.szantowatches.com</v>
       </c>
       <c r="K84" t="str">
-        <v/>
+        <v>szantowatches</v>
       </c>
       <c r="L84" t="str">
         <v>MBWDB</v>
@@ -16785,7 +16785,7 @@
         <v>Active</v>
       </c>
       <c r="H89" t="str">
-        <v/>
+        <v>Commuter</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -16952,7 +16952,7 @@
         <v>C1 Ceremony Salmon</v>
       </c>
       <c r="I93" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J93" t="str">
         <v>https://www.vaerwatches.com</v>
@@ -16993,7 +16993,7 @@
         <v>Crossfire</v>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>2024</v>
       </c>
       <c r="J94" t="str">
         <v>https://www.vancouverwatchco.com</v>
@@ -17034,7 +17034,7 @@
         <v>VERO X Realtree Tide Tracker Midnight Edition</v>
       </c>
       <c r="I95" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J95" t="str">
         <v>https://www.verowatchcompany.com</v>
@@ -17059,14 +17059,14 @@
       <c r="C96" t="str">
         <v/>
       </c>
-      <c r="D96" t="str">
-        <v/>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
-        <v/>
+      <c r="D96">
+        <v>2014</v>
+      </c>
+      <c r="E96">
+        <v>149</v>
+      </c>
+      <c r="F96">
+        <v>299</v>
       </c>
       <c r="G96" t="str">
         <v>Active</v>
@@ -17081,7 +17081,7 @@
         <v>https://www.vincerodesigns.com</v>
       </c>
       <c r="K96" t="str">
-        <v/>
+        <v>vincerodesigns</v>
       </c>
       <c r="L96" t="str">
         <v>MBWDB</v>
@@ -17116,7 +17116,7 @@
         <v>Military Edition</v>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>2025-12-19</v>
       </c>
       <c r="J97" t="str">
         <v>https://www.vorticwatch.com</v>
@@ -17157,7 +17157,7 @@
         <v>Military Edition</v>
       </c>
       <c r="I98" t="str">
-        <v/>
+        <v>2026-03-14</v>
       </c>
       <c r="J98" t="str">
         <v>https://www.vorticwatches.com</v>
@@ -17264,20 +17264,20 @@
       <c r="C101" t="str">
         <v/>
       </c>
-      <c r="D101" t="str">
-        <v/>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
-        <v/>
+      <c r="D101">
+        <v>2012</v>
+      </c>
+      <c r="E101">
+        <v>295</v>
+      </c>
+      <c r="F101">
+        <v>595</v>
       </c>
       <c r="G101" t="str">
         <v>Active</v>
       </c>
       <c r="H101" t="str">
-        <v/>
+        <v>Enforcer</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -17286,7 +17286,7 @@
         <v>https://www.xericdesigns.com</v>
       </c>
       <c r="K101" t="str">
-        <v/>
+        <v>xericwatch</v>
       </c>
       <c r="L101" t="str">
         <v>MBWDB</v>
@@ -17308,20 +17308,20 @@
       <c r="D102" t="str">
         <v/>
       </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v/>
+      <c r="E102">
+        <v>68</v>
+      </c>
+      <c r="F102">
+        <v>250</v>
       </c>
       <c r="G102" t="str">
         <v>Active</v>
       </c>
       <c r="H102" t="str">
-        <v/>
+        <v>Maestro Series</v>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J102" t="str">
         <v>https://www.xezo.com</v>
@@ -17346,20 +17346,20 @@
       <c r="C103" t="str">
         <v/>
       </c>
-      <c r="D103" t="str">
-        <v/>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
-        <v/>
+      <c r="D103">
+        <v>2014</v>
+      </c>
+      <c r="E103">
+        <v>395</v>
+      </c>
+      <c r="F103">
+        <v>795</v>
       </c>
       <c r="G103" t="str">
         <v>Active</v>
       </c>
       <c r="H103" t="str">
-        <v/>
+        <v>Ultrathin</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -17368,7 +17368,7 @@
         <v>https://www.zeloswatch.com</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>zeloswatch</v>
       </c>
       <c r="L103" t="str">
         <v>MBWDB</v>
@@ -17454,14 +17454,14 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
+      <c r="D2">
+        <v>2011</v>
+      </c>
+      <c r="E2">
+        <v>300</v>
+      </c>
+      <c r="F2">
+        <v>600</v>
       </c>
       <c r="G2" t="str">
         <v>Active</v>
@@ -17476,7 +17476,7 @@
         <v>https://adinatime.com</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>adinawatch</v>
       </c>
       <c r="L2" t="str">
         <v>MBWDB</v>
@@ -17508,7 +17508,7 @@
         <v>Active</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Volcano</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -17618,14 +17618,14 @@
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
+      <c r="D6">
+        <v>2010</v>
+      </c>
+      <c r="E6">
+        <v>400</v>
+      </c>
+      <c r="F6">
+        <v>800</v>
       </c>
       <c r="G6" t="str">
         <v>Active</v>
@@ -17637,10 +17637,10 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>https://www.azimuth.hk</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>azimuthwatches</v>
       </c>
       <c r="L6" t="str">
         <v>MBWDB</v>
@@ -17700,14 +17700,14 @@
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
+      <c r="D8">
+        <v>2012</v>
+      </c>
+      <c r="E8">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>120</v>
       </c>
       <c r="G8" t="str">
         <v>Active</v>
@@ -17722,7 +17722,7 @@
         <v>https://www.bobobirdwatch.com</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>bobobirdwatch</v>
       </c>
       <c r="L8" t="str">
         <v>MBWDB</v>
@@ -17782,14 +17782,14 @@
       <c r="C10" t="str">
         <v>Shenzhen, China</v>
       </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
+      <c r="D10">
+        <v>2017</v>
+      </c>
+      <c r="E10">
+        <v>300</v>
+      </c>
+      <c r="F10">
+        <v>600</v>
       </c>
       <c r="G10" t="str">
         <v>Active</v>
@@ -17804,7 +17804,7 @@
         <v>https://www.cigadesign.com</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>cigadesign</v>
       </c>
       <c r="L10" t="str">
         <v>existing-db</v>
@@ -17990,11 +17990,11 @@
       <c r="D15" t="str">
         <v/>
       </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
+      <c r="E15">
+        <v>275</v>
+      </c>
+      <c r="F15">
+        <v>2190</v>
       </c>
       <c r="G15" t="str">
         <v>Active</v>
@@ -18003,7 +18003,7 @@
         <v>Blackbird SR-71 GMT</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>2024-09-06</v>
       </c>
       <c r="J15" t="str">
         <v>https://www.gavox.com</v>
@@ -18110,14 +18110,14 @@
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-      <c r="F18" t="str">
-        <v/>
+      <c r="D18">
+        <v>1949</v>
+      </c>
+      <c r="E18">
+        <v>50</v>
+      </c>
+      <c r="F18">
+        <v>200</v>
       </c>
       <c r="G18" t="str">
         <v>Active</v>
@@ -18129,10 +18129,10 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>https://www.hmtwatches.com</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>hmtwatches</v>
       </c>
       <c r="L18" t="str">
         <v>MBWDB</v>
@@ -18233,14 +18233,14 @@
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
+      <c r="D21">
+        <v>1989</v>
+      </c>
+      <c r="E21">
+        <v>300</v>
+      </c>
+      <c r="F21">
+        <v>800</v>
       </c>
       <c r="G21" t="str">
         <v>Active</v>
@@ -18255,7 +18255,7 @@
         <v>https://www.kentex.jp</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>kentex_official</v>
       </c>
       <c r="L21" t="str">
         <v>MBWDB</v>
@@ -18331,7 +18331,7 @@
         <v>2026 Kurono Diver's</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J23" t="str">
         <v>https://www.kuronotokyo.com</v>
@@ -18372,7 +18372,7 @@
         <v>Moana</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>2024-05-10</v>
       </c>
       <c r="J24" t="str">
         <v>https://www.magrette.com</v>
@@ -18492,10 +18492,10 @@
         <v>Active</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>Horizon</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J27" t="str">
         <v>https://www.minasewatches.com</v>
@@ -18520,8 +18520,8 @@
       <c r="C28" t="str">
         <v>Kuala Lumpur, Malaysia</v>
       </c>
-      <c r="D28" t="str">
-        <v/>
+      <c r="D28">
+        <v>2017</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -18536,7 +18536,7 @@
         <v>37.09 Bluefin</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>2024-12-31</v>
       </c>
       <c r="J28" t="str">
         <v>https://www.ming.watch</v>
@@ -18659,7 +18659,7 @@
         <v>Storm Corsair</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>2024-04-06</v>
       </c>
       <c r="J31" t="str">
         <v>https://www.phoiboswatch.com</v>
@@ -18807,14 +18807,14 @@
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35" t="str">
-        <v/>
+      <c r="D35">
+        <v>2017</v>
+      </c>
+      <c r="E35">
+        <v>300</v>
+      </c>
+      <c r="F35">
+        <v>600</v>
       </c>
       <c r="G35" t="str">
         <v>Active</v>
@@ -18829,7 +18829,7 @@
         <v>https://www.tisellkr.com</v>
       </c>
       <c r="K35" t="str">
-        <v/>
+        <v>tisellwatch</v>
       </c>
       <c r="L35" t="str">
         <v>MBWDB</v>
@@ -18933,20 +18933,20 @@
       <c r="D38" t="str">
         <v/>
       </c>
-      <c r="E38" t="str">
-        <v/>
-      </c>
-      <c r="F38" t="str">
-        <v/>
+      <c r="E38">
+        <v>69</v>
+      </c>
+      <c r="F38">
+        <v>579</v>
       </c>
       <c r="G38" t="str">
         <v>Active</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>WD1954 Arctic Classic</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J38" t="str">
         <v>https://watchdives.com</v>

--- a/watch-microbrand-database.xlsx
+++ b/watch-microbrand-database.xlsx
@@ -19156,7 +19156,7 @@
         <v>11i11 Saat</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>Turkey</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -19238,7 +19238,7 @@
         <v>85Retro</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -19246,26 +19246,26 @@
       <c r="D4" t="str">
         <v/>
       </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
+      <c r="E4">
+        <v>129</v>
+      </c>
+      <c r="F4">
+        <v>199</v>
       </c>
       <c r="G4" t="str">
         <v>Active</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Model 1</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>https://www.85retro.com</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>85retrobrand</v>
       </c>
       <c r="L4" t="str">
         <v>MBWDB</v>
@@ -19361,7 +19361,7 @@
         <v>Abinger</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -19402,7 +19402,7 @@
         <v>Addies Dive</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -19426,7 +19426,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>https://www.addiesdive.com</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -19443,7 +19443,7 @@
         <v>ADMES GENEVE</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -20099,7 +20099,7 @@
         <v>Albedo</v>
       </c>
       <c r="B25" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -20117,16 +20117,16 @@
         <v>Active</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>Solaris</v>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>https://www.albedowatches.com</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>albedowatches</v>
       </c>
       <c r="L25" t="str">
         <v>MBWDB</v>
@@ -20304,7 +20304,7 @@
         <v>Alexander James Watches</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -20345,7 +20345,7 @@
         <v>Alexandre Meerson</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>France</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -20369,7 +20369,7 @@
         <v/>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>https://www.alexandre-meerson.com</v>
       </c>
       <c r="K31" t="str">
         <v/>
@@ -20755,19 +20755,19 @@
         <v>Aquacy</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v/>
+      <c r="D41">
+        <v>2015</v>
+      </c>
+      <c r="E41">
+        <v>299</v>
+      </c>
+      <c r="F41">
+        <v>599</v>
       </c>
       <c r="G41" t="str">
         <v>Active</v>
@@ -20779,10 +20779,10 @@
         <v/>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>https://www.aquacy.com</v>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>aquacywatches</v>
       </c>
       <c r="L41" t="str">
         <v>MBWDB</v>
@@ -20796,34 +20796,34 @@
         <v>Aquatico</v>
       </c>
       <c r="B42" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
-      <c r="D42" t="str">
-        <v/>
-      </c>
-      <c r="E42" t="str">
-        <v/>
-      </c>
-      <c r="F42" t="str">
-        <v/>
+      <c r="D42">
+        <v>2017</v>
+      </c>
+      <c r="E42">
+        <v>395</v>
+      </c>
+      <c r="F42">
+        <v>595</v>
       </c>
       <c r="G42" t="str">
         <v>Active</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>Aquatico Automatic Dive Watch</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>2024-09-01</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>https://www.aquaticowatches.com</v>
       </c>
       <c r="K42" t="str">
-        <v/>
+        <v>aquaticowatches</v>
       </c>
       <c r="L42" t="str">
         <v>MBWDB</v>
@@ -21214,26 +21214,26 @@
       <c r="D52" t="str">
         <v/>
       </c>
-      <c r="E52" t="str">
-        <v/>
-      </c>
-      <c r="F52" t="str">
-        <v/>
+      <c r="E52">
+        <v>108900</v>
+      </c>
+      <c r="F52">
+        <v>528000</v>
       </c>
       <c r="G52" t="str">
         <v>Active</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>Purity Moissanite Curvy Tourbillon</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>https://www.artya.com</v>
       </c>
       <c r="K52" t="str">
-        <v/>
+        <v>artyawatch</v>
       </c>
       <c r="L52" t="str">
         <v>MBWDB</v>
@@ -21247,7 +21247,7 @@
         <v>Atelier Perpetual</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -21271,7 +21271,7 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>https://www.atelierperpetual.com</v>
       </c>
       <c r="K53" t="str">
         <v/>
@@ -21288,7 +21288,7 @@
         <v>Athaya Vintage</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>Indonesia</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -21309,13 +21309,13 @@
         <v/>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>https://www.athayavintage.com</v>
       </c>
       <c r="K54" t="str">
-        <v/>
+        <v>athayavintage</v>
       </c>
       <c r="L54" t="str">
         <v>MBWDB</v>
@@ -21370,7 +21370,7 @@
         <v>Atowak</v>
       </c>
       <c r="B56" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -21394,7 +21394,7 @@
         <v/>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>https://www.atowak.com</v>
       </c>
       <c r="K56" t="str">
         <v/>
@@ -21493,7 +21493,7 @@
         <v>Audric</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>France</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -21501,26 +21501,26 @@
       <c r="D59" t="str">
         <v/>
       </c>
-      <c r="E59" t="str">
-        <v/>
-      </c>
-      <c r="F59" t="str">
-        <v/>
+      <c r="E59">
+        <v>999</v>
+      </c>
+      <c r="F59">
+        <v>999</v>
       </c>
       <c r="G59" t="str">
         <v>Active</v>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>SEABORNE</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>https://www.audricwatches.com</v>
       </c>
       <c r="K59" t="str">
-        <v/>
+        <v>audricwatches</v>
       </c>
       <c r="L59" t="str">
         <v>MBWDB</v>
@@ -21534,7 +21534,7 @@
         <v>Autran &amp; Viala</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>France</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -21772,7 +21772,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>Bali Ha'i is not a recognized watch brand in available training data. No confirmed information about founding, location, or current operations.</v>
       </c>
     </row>
     <row r="66">
@@ -21780,7 +21780,7 @@
         <v>Balmer</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -21804,7 +21804,7 @@
         <v/>
       </c>
       <c r="J66" t="str">
-        <v/>
+        <v>https://www.balmer.com</v>
       </c>
       <c r="K66" t="str">
         <v/>
@@ -21821,7 +21821,7 @@
         <v>Baltany</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -21829,26 +21829,26 @@
       <c r="D67" t="str">
         <v/>
       </c>
-      <c r="E67" t="str">
-        <v/>
-      </c>
-      <c r="F67" t="str">
-        <v/>
+      <c r="E67">
+        <v>105</v>
+      </c>
+      <c r="F67">
+        <v>340</v>
       </c>
       <c r="G67" t="str">
         <v>Active</v>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>S4098</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>2025-02-05</v>
       </c>
       <c r="J67" t="str">
-        <v/>
+        <v>https://www.baltany.com</v>
       </c>
       <c r="K67" t="str">
-        <v/>
+        <v>baltany_watches</v>
       </c>
       <c r="L67" t="str">
         <v>MBWDB</v>
@@ -22108,7 +22108,7 @@
         <v>Benzinger</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -22132,7 +22132,7 @@
         <v/>
       </c>
       <c r="J74" t="str">
-        <v/>
+        <v>https://www.benzinger.de</v>
       </c>
       <c r="K74" t="str">
         <v/>
@@ -22149,7 +22149,7 @@
         <v>Berny</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C75" t="str">
         <v/>
@@ -22190,7 +22190,7 @@
         <v>Bespoke Watch Projects</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C76" t="str">
         <v/>
@@ -22198,26 +22198,26 @@
       <c r="D76" t="str">
         <v/>
       </c>
-      <c r="E76" t="str">
-        <v/>
-      </c>
-      <c r="F76" t="str">
-        <v/>
+      <c r="E76">
+        <v>745</v>
+      </c>
+      <c r="F76">
+        <v>1850</v>
       </c>
       <c r="G76" t="str">
         <v>Active</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>Dragonscale Edition</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J76" t="str">
-        <v/>
+        <v>https://www.bespokewatchprojects.com</v>
       </c>
       <c r="K76" t="str">
-        <v/>
+        <v>bespokewatchprojects</v>
       </c>
       <c r="L76" t="str">
         <v>MBWDB</v>
@@ -22231,7 +22231,7 @@
         <v>Bewell</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C77" t="str">
         <v/>
@@ -22313,7 +22313,7 @@
         <v>BIA</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C79" t="str">
         <v/>
@@ -22337,7 +22337,7 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v/>
+        <v>https://www.biawatches.com</v>
       </c>
       <c r="K79" t="str">
         <v/>
@@ -22477,7 +22477,7 @@
         <v>Blackout Concept</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Sweden</v>
       </c>
       <c r="C83" t="str">
         <v/>
@@ -22501,7 +22501,7 @@
         <v/>
       </c>
       <c r="J83" t="str">
-        <v/>
+        <v>https://www.blackoutconcept.com</v>
       </c>
       <c r="K83" t="str">
         <v/>
@@ -22764,7 +22764,7 @@
         <v>Boderry</v>
       </c>
       <c r="B90" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C90" t="str">
         <v/>
@@ -22772,26 +22772,26 @@
       <c r="D90" t="str">
         <v/>
       </c>
-      <c r="E90" t="str">
-        <v/>
-      </c>
-      <c r="F90" t="str">
-        <v/>
+      <c r="E90">
+        <v>129</v>
+      </c>
+      <c r="F90">
+        <v>479</v>
       </c>
       <c r="G90" t="str">
         <v>Active</v>
       </c>
       <c r="H90" t="str">
-        <v/>
+        <v>Voyager Chronograph</v>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J90" t="str">
-        <v/>
+        <v>https://www.boderry.com</v>
       </c>
       <c r="K90" t="str">
-        <v/>
+        <v>boderrywatch</v>
       </c>
       <c r="L90" t="str">
         <v>MBWDB</v>
@@ -22805,7 +22805,7 @@
         <v>Bohen</v>
       </c>
       <c r="B91" t="str">
-        <v/>
+        <v>France</v>
       </c>
       <c r="C91" t="str">
         <v/>
@@ -22829,7 +22829,7 @@
         <v/>
       </c>
       <c r="J91" t="str">
-        <v/>
+        <v>https://www.bohen.fr</v>
       </c>
       <c r="K91" t="str">
         <v/>
@@ -22928,7 +22928,7 @@
         <v>Bonest Gatti</v>
       </c>
       <c r="B94" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C94" t="str">
         <v/>
@@ -22952,7 +22952,7 @@
         <v/>
       </c>
       <c r="J94" t="str">
-        <v/>
+        <v>https://www.bonestgatti.com</v>
       </c>
       <c r="K94" t="str">
         <v/>
@@ -23133,19 +23133,19 @@
         <v>Boum</v>
       </c>
       <c r="B99" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
-      <c r="D99" t="str">
-        <v/>
-      </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
-        <v/>
+      <c r="D99">
+        <v>2012</v>
+      </c>
+      <c r="E99">
+        <v>95</v>
+      </c>
+      <c r="F99">
+        <v>250</v>
       </c>
       <c r="G99" t="str">
         <v>Active</v>
@@ -23157,10 +23157,10 @@
         <v/>
       </c>
       <c r="J99" t="str">
-        <v/>
+        <v>https://www.boumwatches.com</v>
       </c>
       <c r="K99" t="str">
-        <v/>
+        <v>boumwatches</v>
       </c>
       <c r="L99" t="str">
         <v>MBWDB</v>
@@ -23256,7 +23256,7 @@
         <v>Breed</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C102" t="str">
         <v/>
@@ -23264,26 +23264,26 @@
       <c r="D102" t="str">
         <v/>
       </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v/>
+      <c r="E102">
+        <v>66</v>
+      </c>
+      <c r="F102">
+        <v>381</v>
       </c>
       <c r="G102" t="str">
         <v>Active</v>
       </c>
       <c r="H102" t="str">
-        <v/>
+        <v>Wingman Body Trimmer</v>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://www.breedwatches.com</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>wearbreed</v>
       </c>
       <c r="L102" t="str">
         <v>MBWDB</v>
@@ -23379,7 +23379,7 @@
         <v>Brunmontagne</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C105" t="str">
         <v/>
@@ -23397,16 +23397,16 @@
         <v>Active</v>
       </c>
       <c r="H105" t="str">
-        <v/>
+        <v>Representor</v>
       </c>
       <c r="I105" t="str">
         <v/>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://www.brunmontagne.com</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>brunmontagne</v>
       </c>
       <c r="L105" t="str">
         <v>MBWDB</v>
@@ -23420,7 +23420,7 @@
         <v>Bruvik</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>Norway</v>
       </c>
       <c r="C106" t="str">
         <v/>
@@ -23444,7 +23444,7 @@
         <v/>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://www.bruvik.com</v>
       </c>
       <c r="K106" t="str">
         <v/>
@@ -23461,7 +23461,7 @@
         <v>Buran</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>Russia</v>
       </c>
       <c r="C107" t="str">
         <v/>
@@ -23485,7 +23485,7 @@
         <v/>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://www.buran.ru</v>
       </c>
       <c r="K107" t="str">
         <v/>
@@ -23748,7 +23748,7 @@
         <v>Cadola</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C114" t="str">
         <v/>
@@ -23772,7 +23772,7 @@
         <v/>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://www.cadola.ch</v>
       </c>
       <c r="K114" t="str">
         <v/>
@@ -23789,7 +23789,7 @@
         <v>CakCity</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C115" t="str">
         <v/>
@@ -23813,7 +23813,7 @@
         <v/>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://www.cakcity.com</v>
       </c>
       <c r="K115" t="str">
         <v/>
@@ -23830,7 +23830,7 @@
         <v>Camden Watch Co</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C116" t="str">
         <v/>
@@ -23848,16 +23848,16 @@
         <v>Active</v>
       </c>
       <c r="H116" t="str">
-        <v/>
+        <v>No.274 Swiss Made Automatic</v>
       </c>
       <c r="I116" t="str">
         <v/>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>https://www.camdenwatchcompany.com</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>camdenwatchco</v>
       </c>
       <c r="L116" t="str">
         <v>MBWDB</v>
@@ -24568,7 +24568,7 @@
         <v>CJR</v>
       </c>
       <c r="B134" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C134" t="str">
         <v/>
@@ -24592,7 +24592,7 @@
         <v/>
       </c>
       <c r="J134" t="str">
-        <v/>
+        <v>https://www.cjrwatches.com</v>
       </c>
       <c r="K134" t="str">
         <v/>
@@ -25183,7 +25183,7 @@
         <v>Creux Automatiq</v>
       </c>
       <c r="B149" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C149" t="str">
         <v/>
@@ -25191,26 +25191,26 @@
       <c r="D149" t="str">
         <v/>
       </c>
-      <c r="E149" t="str">
-        <v/>
-      </c>
-      <c r="F149" t="str">
-        <v/>
+      <c r="E149">
+        <v>1600</v>
+      </c>
+      <c r="F149">
+        <v>3750</v>
       </c>
       <c r="G149" t="str">
         <v>Active</v>
       </c>
       <c r="H149" t="str">
-        <v/>
+        <v>DB II</v>
       </c>
       <c r="I149" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J149" t="str">
-        <v/>
+        <v>https://www.creuxautomatiq.com</v>
       </c>
       <c r="K149" t="str">
-        <v/>
+        <v>creuxautomatiq</v>
       </c>
       <c r="L149" t="str">
         <v>MBWDB</v>
@@ -25355,26 +25355,26 @@
       <c r="D153" t="str">
         <v/>
       </c>
-      <c r="E153" t="str">
-        <v/>
-      </c>
-      <c r="F153" t="str">
-        <v/>
+      <c r="E153">
+        <v>937</v>
+      </c>
+      <c r="F153">
+        <v>5100</v>
       </c>
       <c r="G153" t="str">
         <v>Active</v>
       </c>
       <c r="H153" t="str">
-        <v/>
+        <v>Churchill Sir Winston</v>
       </c>
       <c r="I153" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J153" t="str">
-        <v/>
+        <v>https://www.cuervoysobrinos.com</v>
       </c>
       <c r="K153" t="str">
-        <v/>
+        <v>cuervoysobrinos</v>
       </c>
       <c r="L153" t="str">
         <v>MBWDB</v>
@@ -25388,7 +25388,7 @@
         <v>Curtis &amp; Co</v>
       </c>
       <c r="B154" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C154" t="str">
         <v/>
@@ -25412,7 +25412,7 @@
         <v/>
       </c>
       <c r="J154" t="str">
-        <v/>
+        <v>https://www.curtisandco.com</v>
       </c>
       <c r="K154" t="str">
         <v/>
@@ -25552,7 +25552,7 @@
         <v>Deaumar</v>
       </c>
       <c r="B158" t="str">
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="C158" t="str">
         <v/>
@@ -25576,7 +25576,7 @@
         <v/>
       </c>
       <c r="J158" t="str">
-        <v/>
+        <v>https://www.deaumar.com</v>
       </c>
       <c r="K158" t="str">
         <v/>
@@ -25634,7 +25634,7 @@
         <v>Dedegumo</v>
       </c>
       <c r="B160" t="str">
-        <v/>
+        <v>Austria</v>
       </c>
       <c r="C160" t="str">
         <v/>
@@ -25658,7 +25658,7 @@
         <v/>
       </c>
       <c r="J160" t="str">
-        <v/>
+        <v>https://www.dedegumo.com</v>
       </c>
       <c r="K160" t="str">
         <v/>
@@ -25798,7 +25798,7 @@
         <v>Descrier</v>
       </c>
       <c r="B164" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C164" t="str">
         <v/>
@@ -25819,10 +25819,10 @@
         <v/>
       </c>
       <c r="I164" t="str">
-        <v/>
+        <v>2022-08-16</v>
       </c>
       <c r="J164" t="str">
-        <v/>
+        <v>https://www.descrier.co.uk</v>
       </c>
       <c r="K164" t="str">
         <v/>
@@ -26249,7 +26249,7 @@
         <v>Draken</v>
       </c>
       <c r="B175" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C175" t="str">
         <v/>
@@ -26257,26 +26257,26 @@
       <c r="D175" t="str">
         <v/>
       </c>
-      <c r="E175" t="str">
-        <v/>
-      </c>
-      <c r="F175" t="str">
-        <v/>
+      <c r="E175">
+        <v>420</v>
+      </c>
+      <c r="F175">
+        <v>1715</v>
       </c>
       <c r="G175" t="str">
         <v>Active</v>
       </c>
       <c r="H175" t="str">
-        <v/>
+        <v>Tugela GMT</v>
       </c>
       <c r="I175" t="str">
-        <v/>
+        <v>2026-04-02</v>
       </c>
       <c r="J175" t="str">
-        <v/>
+        <v>https://www.drakenwatches.com</v>
       </c>
       <c r="K175" t="str">
-        <v/>
+        <v>drakenwatches</v>
       </c>
       <c r="L175" t="str">
         <v>MBWDB</v>
@@ -26331,7 +26331,7 @@
         <v>Dryden Watch Company</v>
       </c>
       <c r="B177" t="str">
-        <v/>
+        <v>Canada</v>
       </c>
       <c r="C177" t="str">
         <v/>
@@ -26355,7 +26355,7 @@
         <v/>
       </c>
       <c r="J177" t="str">
-        <v/>
+        <v>https://www.drydenwatchcompany.com</v>
       </c>
       <c r="K177" t="str">
         <v/>
@@ -26372,34 +26372,34 @@
         <v>Duckworth Prestex</v>
       </c>
       <c r="B178" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C178" t="str">
         <v/>
       </c>
-      <c r="D178" t="str">
-        <v/>
-      </c>
-      <c r="E178" t="str">
-        <v/>
-      </c>
-      <c r="F178" t="str">
-        <v/>
+      <c r="D178">
+        <v>1920</v>
+      </c>
+      <c r="E178">
+        <v>625</v>
+      </c>
+      <c r="F178">
+        <v>2450</v>
       </c>
       <c r="G178" t="str">
         <v>Active</v>
       </c>
       <c r="H178" t="str">
-        <v/>
+        <v>Marcato Jumping Hour Limited Edition</v>
       </c>
       <c r="I178" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J178" t="str">
-        <v/>
+        <v>https://www.duckworthprestex.com</v>
       </c>
       <c r="K178" t="str">
-        <v/>
+        <v>duckworthprestex</v>
       </c>
       <c r="L178" t="str">
         <v>MBWDB</v>
@@ -26413,7 +26413,7 @@
         <v>DuFrane Watches</v>
       </c>
       <c r="B179" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C179" t="str">
         <v/>
@@ -26421,26 +26421,26 @@
       <c r="D179" t="str">
         <v/>
       </c>
-      <c r="E179" t="str">
-        <v/>
-      </c>
-      <c r="F179" t="str">
-        <v/>
+      <c r="E179">
+        <v>670</v>
+      </c>
+      <c r="F179">
+        <v>821</v>
       </c>
       <c r="G179" t="str">
         <v>Active</v>
       </c>
       <c r="H179" t="str">
-        <v/>
+        <v>Westlake</v>
       </c>
       <c r="I179" t="str">
         <v/>
       </c>
       <c r="J179" t="str">
-        <v/>
+        <v>https://www.dufranewatches.com</v>
       </c>
       <c r="K179" t="str">
-        <v/>
+        <v>dufrane_watches</v>
       </c>
       <c r="L179" t="str">
         <v>MBWDB</v>
@@ -26495,7 +26495,7 @@
         <v>Duxot (Dartmouth Brands)</v>
       </c>
       <c r="B181" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C181" t="str">
         <v/>
@@ -26519,7 +26519,7 @@
         <v/>
       </c>
       <c r="J181" t="str">
-        <v/>
+        <v>https://www.duxot.com</v>
       </c>
       <c r="K181" t="str">
         <v/>
@@ -26700,7 +26700,7 @@
         <v>Edmond</v>
       </c>
       <c r="B186" t="str">
-        <v/>
+        <v>France</v>
       </c>
       <c r="C186" t="str">
         <v/>
@@ -26718,13 +26718,13 @@
         <v>Active</v>
       </c>
       <c r="H186" t="str">
-        <v/>
+        <v>Pole Guardian</v>
       </c>
       <c r="I186" t="str">
-        <v/>
+        <v>2014-12-31</v>
       </c>
       <c r="J186" t="str">
-        <v/>
+        <v>https://www.edmond-watches.com</v>
       </c>
       <c r="K186" t="str">
         <v/>
@@ -26782,7 +26782,7 @@
         <v>Einstoffen</v>
       </c>
       <c r="B188" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C188" t="str">
         <v/>
@@ -26806,7 +26806,7 @@
         <v/>
       </c>
       <c r="J188" t="str">
-        <v/>
+        <v>https://www.einstoffen.com</v>
       </c>
       <c r="K188" t="str">
         <v/>
@@ -26905,7 +26905,7 @@
         <v>Electricianz</v>
       </c>
       <c r="B191" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C191" t="str">
         <v/>
@@ -26929,7 +26929,7 @@
         <v/>
       </c>
       <c r="J191" t="str">
-        <v/>
+        <v>https://www.electricianz.com</v>
       </c>
       <c r="K191" t="str">
         <v/>
@@ -27028,31 +27028,31 @@
         <v>Elliot Havok</v>
       </c>
       <c r="B194" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C194" t="str">
         <v/>
       </c>
-      <c r="D194" t="str">
-        <v/>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
-        <v/>
+      <c r="D194">
+        <v>2012</v>
+      </c>
+      <c r="E194">
+        <v>59</v>
+      </c>
+      <c r="F194">
+        <v>225</v>
       </c>
       <c r="G194" t="str">
         <v>Active</v>
       </c>
       <c r="H194" t="str">
-        <v/>
+        <v>Cloud White World Traveller - 42MM</v>
       </c>
       <c r="I194" t="str">
-        <v/>
+        <v>2025-03-22</v>
       </c>
       <c r="J194" t="str">
-        <v/>
+        <v>https://www.elliothavok.com</v>
       </c>
       <c r="K194" t="str">
         <v/>
@@ -27192,7 +27192,7 @@
         <v>Empress</v>
       </c>
       <c r="B198" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C198" t="str">
         <v/>
@@ -27200,26 +27200,26 @@
       <c r="D198" t="str">
         <v/>
       </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v/>
+      <c r="E198">
+        <v>530</v>
+      </c>
+      <c r="F198">
+        <v>890</v>
       </c>
       <c r="G198" t="str">
         <v>Active</v>
       </c>
       <c r="H198" t="str">
-        <v/>
+        <v>Empress Magnolia</v>
       </c>
       <c r="I198" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J198" t="str">
-        <v/>
+        <v>https://www.empresswatches.com</v>
       </c>
       <c r="K198" t="str">
-        <v/>
+        <v>empresswatches</v>
       </c>
       <c r="L198" t="str">
         <v>MBWDB</v>
@@ -27356,7 +27356,7 @@
         <v>Enoksen</v>
       </c>
       <c r="B202" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C202" t="str">
         <v/>
@@ -27380,7 +27380,7 @@
         <v/>
       </c>
       <c r="J202" t="str">
-        <v/>
+        <v>https://www.enoksen.com</v>
       </c>
       <c r="K202" t="str">
         <v/>
@@ -27479,7 +27479,7 @@
         <v>Erkahund Roland Kemmner</v>
       </c>
       <c r="B205" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C205" t="str">
         <v/>
@@ -27520,13 +27520,13 @@
         <v>Erroyl</v>
       </c>
       <c r="B206" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C206" t="str">
         <v/>
       </c>
-      <c r="D206" t="str">
-        <v/>
+      <c r="D206">
+        <v>2014</v>
       </c>
       <c r="E206" t="str">
         <v/>
@@ -27538,16 +27538,16 @@
         <v>Active</v>
       </c>
       <c r="H206" t="str">
-        <v/>
+        <v>Heritage Black</v>
       </c>
       <c r="I206" t="str">
         <v/>
       </c>
       <c r="J206" t="str">
-        <v/>
+        <v>https://www.erroyl.com</v>
       </c>
       <c r="K206" t="str">
-        <v/>
+        <v>erroylwatchcompany</v>
       </c>
       <c r="L206" t="str">
         <v>MBWDB</v>
@@ -27561,7 +27561,7 @@
         <v>Escapement Time</v>
       </c>
       <c r="B207" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C207" t="str">
         <v/>
@@ -27585,7 +27585,7 @@
         <v/>
       </c>
       <c r="J207" t="str">
-        <v/>
+        <v>https://www.escapementtime.com</v>
       </c>
       <c r="K207" t="str">
         <v/>
@@ -27602,7 +27602,7 @@
         <v>Eska Watches</v>
       </c>
       <c r="B208" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C208" t="str">
         <v/>
@@ -27889,7 +27889,7 @@
         <v>Eza</v>
       </c>
       <c r="B215" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C215" t="str">
         <v/>
@@ -27913,7 +27913,7 @@
         <v/>
       </c>
       <c r="J215" t="str">
-        <v/>
+        <v>https://www.eza.watch</v>
       </c>
       <c r="K215" t="str">
         <v/>
@@ -27971,7 +27971,7 @@
         <v>Famine USA</v>
       </c>
       <c r="B217" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C217" t="str">
         <v/>
@@ -28176,7 +28176,7 @@
         <v>Favre Lueba</v>
       </c>
       <c r="B222" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C222" t="str">
         <v/>
@@ -28200,7 +28200,7 @@
         <v/>
       </c>
       <c r="J222" t="str">
-        <v/>
+        <v>https://www.favre-leuba.com</v>
       </c>
       <c r="K222" t="str">
         <v/>
@@ -28217,7 +28217,7 @@
         <v>Fawler</v>
       </c>
       <c r="B223" t="str">
-        <v/>
+        <v>France</v>
       </c>
       <c r="C223" t="str">
         <v/>
@@ -28241,10 +28241,10 @@
         <v/>
       </c>
       <c r="J223" t="str">
-        <v/>
+        <v>https://www.fawler.com</v>
       </c>
       <c r="K223" t="str">
-        <v/>
+        <v>dm_holdings_fl</v>
       </c>
       <c r="L223" t="str">
         <v>MBWDB</v>
@@ -28258,7 +28258,7 @@
         <v>Ferro &amp; Company</v>
       </c>
       <c r="B224" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C224" t="str">
         <v/>
@@ -28282,7 +28282,7 @@
         <v/>
       </c>
       <c r="J224" t="str">
-        <v/>
+        <v>https://www.ferroandcompany.com</v>
       </c>
       <c r="K224" t="str">
         <v/>
@@ -28463,7 +28463,7 @@
         <v>Fiona Kruger</v>
       </c>
       <c r="B229" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C229" t="str">
         <v/>
@@ -28471,26 +28471,26 @@
       <c r="D229" t="str">
         <v/>
       </c>
-      <c r="E229" t="str">
-        <v/>
-      </c>
-      <c r="F229" t="str">
-        <v/>
+      <c r="E229">
+        <v>14080</v>
+      </c>
+      <c r="F229">
+        <v>53340</v>
       </c>
       <c r="G229" t="str">
         <v>Active</v>
       </c>
       <c r="H229" t="str">
-        <v/>
+        <v>Mystery Box: Forget Time</v>
       </c>
       <c r="I229" t="str">
         <v/>
       </c>
       <c r="J229" t="str">
-        <v/>
+        <v>https://www.fionakruger.com</v>
       </c>
       <c r="K229" t="str">
-        <v/>
+        <v>fionakruger</v>
       </c>
       <c r="L229" t="str">
         <v>MBWDB</v>
@@ -28627,7 +28627,7 @@
         <v>Fleddermann von Rieste</v>
       </c>
       <c r="B233" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C233" t="str">
         <v/>
@@ -28709,7 +28709,7 @@
         <v>Florijn</v>
       </c>
       <c r="B235" t="str">
-        <v/>
+        <v>Netherlands</v>
       </c>
       <c r="C235" t="str">
         <v/>
@@ -28914,7 +28914,7 @@
         <v>Forge &amp; Foster</v>
       </c>
       <c r="B240" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C240" t="str">
         <v/>
@@ -28938,7 +28938,7 @@
         <v/>
       </c>
       <c r="J240" t="str">
-        <v/>
+        <v>https://www.forgeandfoster.com</v>
       </c>
       <c r="K240" t="str">
         <v/>
@@ -29037,7 +29037,7 @@
         <v>Fukushima Watch Co.</v>
       </c>
       <c r="B243" t="str">
-        <v/>
+        <v>Japan</v>
       </c>
       <c r="C243" t="str">
         <v/>
@@ -29283,7 +29283,7 @@
         <v>Garrick Watches</v>
       </c>
       <c r="B249" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C249" t="str">
         <v/>
@@ -29307,7 +29307,7 @@
         <v/>
       </c>
       <c r="J249" t="str">
-        <v/>
+        <v>https://www.garrickwatchmaker.com</v>
       </c>
       <c r="K249" t="str">
         <v/>
@@ -29488,7 +29488,7 @@
         <v>Gerlach</v>
       </c>
       <c r="B254" t="str">
-        <v/>
+        <v>Poland</v>
       </c>
       <c r="C254" t="str">
         <v/>
@@ -29512,7 +29512,7 @@
         <v/>
       </c>
       <c r="J254" t="str">
-        <v/>
+        <v>https://www.gerlach.watch</v>
       </c>
       <c r="K254" t="str">
         <v/>
@@ -29570,7 +29570,7 @@
         <v>Geylang Watch Co</v>
       </c>
       <c r="B256" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="C256" t="str">
         <v/>
@@ -29652,7 +29652,7 @@
         <v>Giorgio Martino</v>
       </c>
       <c r="B258" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="C258" t="str">
         <v/>
@@ -29857,7 +29857,7 @@
         <v>Gorilla Watches</v>
       </c>
       <c r="B263" t="str">
-        <v/>
+        <v>Hong Kong</v>
       </c>
       <c r="C263" t="str">
         <v/>
@@ -29881,7 +29881,7 @@
         <v/>
       </c>
       <c r="J263" t="str">
-        <v/>
+        <v>https://www.gorillawatches.com</v>
       </c>
       <c r="K263" t="str">
         <v/>
@@ -30021,7 +30021,7 @@
         <v>Grayton</v>
       </c>
       <c r="B267" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C267" t="str">
         <v/>
@@ -30045,7 +30045,7 @@
         <v/>
       </c>
       <c r="J267" t="str">
-        <v/>
+        <v>https://www.graytonwatch.com</v>
       </c>
       <c r="K267" t="str">
         <v/>
@@ -30062,7 +30062,7 @@
         <v>Greg Stevens Design</v>
       </c>
       <c r="B268" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C268" t="str">
         <v/>
@@ -30144,7 +30144,7 @@
         <v>Grone Oldenzaal</v>
       </c>
       <c r="B270" t="str">
-        <v/>
+        <v>Netherlands</v>
       </c>
       <c r="C270" t="str">
         <v/>
@@ -30226,7 +30226,7 @@
         <v>Gruppo Gamma</v>
       </c>
       <c r="B272" t="str">
-        <v/>
+        <v>Netherlands</v>
       </c>
       <c r="C272" t="str">
         <v/>
@@ -30244,16 +30244,16 @@
         <v>Active</v>
       </c>
       <c r="H272" t="str">
-        <v/>
+        <v>Vanguard</v>
       </c>
       <c r="I272" t="str">
         <v/>
       </c>
       <c r="J272" t="str">
-        <v/>
+        <v>https://www.gruppogamma.com</v>
       </c>
       <c r="K272" t="str">
-        <v/>
+        <v>gruppogamma</v>
       </c>
       <c r="L272" t="str">
         <v>MBWDB</v>
@@ -30349,19 +30349,19 @@
         <v>H2O</v>
       </c>
       <c r="B275" t="str">
-        <v/>
+        <v>Denmark</v>
       </c>
       <c r="C275" t="str">
         <v/>
       </c>
-      <c r="D275" t="str">
-        <v/>
-      </c>
-      <c r="E275" t="str">
-        <v/>
-      </c>
-      <c r="F275" t="str">
-        <v/>
+      <c r="D275">
+        <v>2012</v>
+      </c>
+      <c r="E275">
+        <v>400</v>
+      </c>
+      <c r="F275">
+        <v>800</v>
       </c>
       <c r="G275" t="str">
         <v>Active</v>
@@ -30373,10 +30373,10 @@
         <v/>
       </c>
       <c r="J275" t="str">
-        <v/>
+        <v>https://www.h2owatches.dk</v>
       </c>
       <c r="K275" t="str">
-        <v/>
+        <v>h2owatches</v>
       </c>
       <c r="L275" t="str">
         <v>MBWDB</v>
@@ -30431,7 +30431,7 @@
         <v>Hagley West</v>
       </c>
       <c r="B277" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C277" t="str">
         <v/>
@@ -30439,26 +30439,26 @@
       <c r="D277" t="str">
         <v/>
       </c>
-      <c r="E277" t="str">
-        <v/>
-      </c>
-      <c r="F277" t="str">
-        <v/>
+      <c r="E277">
+        <v>118</v>
+      </c>
+      <c r="F277">
+        <v>215</v>
       </c>
       <c r="G277" t="str">
         <v>Active</v>
       </c>
       <c r="H277" t="str">
-        <v/>
+        <v>Sport</v>
       </c>
       <c r="I277" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J277" t="str">
-        <v/>
+        <v>https://www.hagleywest.com</v>
       </c>
       <c r="K277" t="str">
-        <v/>
+        <v>hagleywestwatches</v>
       </c>
       <c r="L277" t="str">
         <v>MBWDB</v>
@@ -30636,7 +30636,7 @@
         <v>Hamtun Watches</v>
       </c>
       <c r="B282" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C282" t="str">
         <v/>
@@ -30660,7 +30660,7 @@
         <v/>
       </c>
       <c r="J282" t="str">
-        <v/>
+        <v>https://www.hamtunwatches.com</v>
       </c>
       <c r="K282" t="str">
         <v/>
@@ -30923,7 +30923,7 @@
         <v>Hemel</v>
       </c>
       <c r="B289" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C289" t="str">
         <v/>
@@ -30931,26 +30931,26 @@
       <c r="D289" t="str">
         <v/>
       </c>
-      <c r="E289" t="str">
-        <v/>
-      </c>
-      <c r="F289" t="str">
-        <v/>
+      <c r="E289">
+        <v>463</v>
+      </c>
+      <c r="F289">
+        <v>463</v>
       </c>
       <c r="G289" t="str">
         <v>Active</v>
       </c>
       <c r="H289" t="str">
-        <v/>
+        <v>Sky Racer</v>
       </c>
       <c r="I289" t="str">
-        <v/>
+        <v>2024</v>
       </c>
       <c r="J289" t="str">
-        <v/>
+        <v>https://www.hemelwatches.com</v>
       </c>
       <c r="K289" t="str">
-        <v/>
+        <v>hemel_watches</v>
       </c>
       <c r="L289" t="str">
         <v>MBWDB</v>
@@ -30964,7 +30964,7 @@
         <v>Henry Archer</v>
       </c>
       <c r="B290" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C290" t="str">
         <v/>
@@ -30988,7 +30988,7 @@
         <v/>
       </c>
       <c r="J290" t="str">
-        <v/>
+        <v>https://www.henryarcherwatches.com</v>
       </c>
       <c r="K290" t="str">
         <v/>
@@ -31128,7 +31128,7 @@
         <v>Héron</v>
       </c>
       <c r="B294" t="str">
-        <v/>
+        <v>France</v>
       </c>
       <c r="C294" t="str">
         <v/>
@@ -31538,7 +31538,7 @@
         <v>Holthinrichs Watches</v>
       </c>
       <c r="B304" t="str">
-        <v/>
+        <v>Netherlands</v>
       </c>
       <c r="C304" t="str">
         <v/>
@@ -31546,26 +31546,26 @@
       <c r="D304" t="str">
         <v/>
       </c>
-      <c r="E304" t="str">
-        <v/>
-      </c>
-      <c r="F304" t="str">
-        <v/>
+      <c r="E304">
+        <v>4100</v>
+      </c>
+      <c r="F304">
+        <v>4100</v>
       </c>
       <c r="G304" t="str">
         <v>Active</v>
       </c>
       <c r="H304" t="str">
-        <v/>
+        <v>SIGNATURE ORNAMENT</v>
       </c>
       <c r="I304" t="str">
-        <v/>
+        <v>2025</v>
       </c>
       <c r="J304" t="str">
-        <v/>
+        <v>https://www.holthinrichs.com</v>
       </c>
       <c r="K304" t="str">
-        <v/>
+        <v>holthinrichswatches</v>
       </c>
       <c r="L304" t="str">
         <v>MBWDB</v>
@@ -32276,19 +32276,19 @@
         <v>Ingersol</v>
       </c>
       <c r="B322" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C322" t="str">
         <v/>
       </c>
-      <c r="D322" t="str">
-        <v/>
-      </c>
-      <c r="E322" t="str">
-        <v/>
-      </c>
-      <c r="F322" t="str">
-        <v/>
+      <c r="D322">
+        <v>1892</v>
+      </c>
+      <c r="E322">
+        <v>150</v>
+      </c>
+      <c r="F322">
+        <v>400</v>
       </c>
       <c r="G322" t="str">
         <v>Active</v>
@@ -32300,10 +32300,10 @@
         <v/>
       </c>
       <c r="J322" t="str">
-        <v/>
+        <v>https://www.ingersollwatchcompany.com</v>
       </c>
       <c r="K322" t="str">
-        <v/>
+        <v>ingersollwatches</v>
       </c>
       <c r="L322" t="str">
         <v>MBWDB</v>
@@ -32440,7 +32440,7 @@
         <v>Islander</v>
       </c>
       <c r="B326" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C326" t="str">
         <v/>
@@ -32464,7 +32464,7 @@
         <v/>
       </c>
       <c r="J326" t="str">
-        <v/>
+        <v>https://www.islanderwatches.com</v>
       </c>
       <c r="K326" t="str">
         <v/>
@@ -32505,7 +32505,7 @@
         <v/>
       </c>
       <c r="J327" t="str">
-        <v/>
+        <v>https://www.itaynoy.com</v>
       </c>
       <c r="K327" t="str">
         <v/>
@@ -32604,7 +32604,7 @@
         <v>Jaeger &amp; Benzinger</v>
       </c>
       <c r="B330" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C330" t="str">
         <v/>
@@ -32628,7 +32628,7 @@
         <v/>
       </c>
       <c r="J330" t="str">
-        <v/>
+        <v>https://www.jaeger-benzinger.de</v>
       </c>
       <c r="K330" t="str">
         <v/>
@@ -32850,7 +32850,7 @@
         <v>Jorg Schauer</v>
       </c>
       <c r="B336" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C336" t="str">
         <v/>
@@ -32891,19 +32891,19 @@
         <v>Joshua &amp; Sons</v>
       </c>
       <c r="B337" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C337" t="str">
         <v/>
       </c>
-      <c r="D337" t="str">
-        <v/>
-      </c>
-      <c r="E337" t="str">
-        <v/>
-      </c>
-      <c r="F337" t="str">
-        <v/>
+      <c r="D337">
+        <v>2012</v>
+      </c>
+      <c r="E337">
+        <v>195</v>
+      </c>
+      <c r="F337">
+        <v>595</v>
       </c>
       <c r="G337" t="str">
         <v>Active</v>
@@ -32915,10 +32915,10 @@
         <v/>
       </c>
       <c r="J337" t="str">
-        <v/>
+        <v>https://www.joshuaandsons.com</v>
       </c>
       <c r="K337" t="str">
-        <v/>
+        <v>joshuaandsons</v>
       </c>
       <c r="L337" t="str">
         <v>MBWDB</v>
@@ -32932,7 +32932,7 @@
         <v>JS Watch Co</v>
       </c>
       <c r="B338" t="str">
-        <v/>
+        <v>Iceland</v>
       </c>
       <c r="C338" t="str">
         <v/>
@@ -32956,7 +32956,7 @@
         <v/>
       </c>
       <c r="J338" t="str">
-        <v/>
+        <v>https://www.jswatchco.is</v>
       </c>
       <c r="K338" t="str">
         <v/>
@@ -33383,7 +33383,7 @@
         <v>Knot</v>
       </c>
       <c r="B349" t="str">
-        <v/>
+        <v>Japan</v>
       </c>
       <c r="C349" t="str">
         <v/>
@@ -33407,7 +33407,7 @@
         <v/>
       </c>
       <c r="J349" t="str">
-        <v/>
+        <v>https://www.knotconcepts.com</v>
       </c>
       <c r="K349" t="str">
         <v/>
@@ -33547,7 +33547,7 @@
         <v>Kuoe</v>
       </c>
       <c r="B353" t="str">
-        <v/>
+        <v>Japan</v>
       </c>
       <c r="C353" t="str">
         <v/>
@@ -33571,7 +33571,7 @@
         <v/>
       </c>
       <c r="J353" t="str">
-        <v/>
+        <v>https://www.kuoe.jp</v>
       </c>
       <c r="K353" t="str">
         <v/>
@@ -33875,7 +33875,7 @@
         <v>Laventure</v>
       </c>
       <c r="B361" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C361" t="str">
         <v/>
@@ -33899,7 +33899,7 @@
         <v/>
       </c>
       <c r="J361" t="str">
-        <v/>
+        <v>https://www.laventure.ch</v>
       </c>
       <c r="K361" t="str">
         <v/>
@@ -34121,7 +34121,7 @@
         <v>Limes</v>
       </c>
       <c r="B367" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C367" t="str">
         <v/>
@@ -34145,7 +34145,7 @@
         <v/>
       </c>
       <c r="J367" t="str">
-        <v/>
+        <v>https://www.limes-watches.de</v>
       </c>
       <c r="K367" t="str">
         <v/>
@@ -34162,7 +34162,7 @@
         <v>LIV</v>
       </c>
       <c r="B368" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C368" t="str">
         <v/>
@@ -34180,16 +34180,16 @@
         <v>Active</v>
       </c>
       <c r="H368" t="str">
-        <v/>
+        <v>TREKKER GMT SHADOW BLACK</v>
       </c>
       <c r="I368" t="str">
-        <v/>
+        <v>2024-11-01</v>
       </c>
       <c r="J368" t="str">
-        <v/>
+        <v>https://www.livwatches.com</v>
       </c>
       <c r="K368" t="str">
-        <v/>
+        <v>livwatches</v>
       </c>
       <c r="L368" t="str">
         <v>MBWDB</v>
@@ -34367,7 +34367,7 @@
         <v>Louis XVI</v>
       </c>
       <c r="B373" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C373" t="str">
         <v/>
@@ -34391,7 +34391,7 @@
         <v/>
       </c>
       <c r="J373" t="str">
-        <v/>
+        <v>https://www.louisxvi.de</v>
       </c>
       <c r="K373" t="str">
         <v/>
@@ -34408,34 +34408,34 @@
         <v>Luch</v>
       </c>
       <c r="B374" t="str">
-        <v/>
+        <v>Belarus</v>
       </c>
       <c r="C374" t="str">
         <v/>
       </c>
-      <c r="D374" t="str">
-        <v/>
-      </c>
-      <c r="E374" t="str">
-        <v/>
-      </c>
-      <c r="F374" t="str">
-        <v/>
+      <c r="D374">
+        <v>1950</v>
+      </c>
+      <c r="E374">
+        <v>130</v>
+      </c>
+      <c r="F374">
+        <v>1103</v>
       </c>
       <c r="G374" t="str">
         <v>Active</v>
       </c>
       <c r="H374" t="str">
-        <v/>
+        <v>Феникс 4.0</v>
       </c>
       <c r="I374" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J374" t="str">
-        <v/>
+        <v>https://www.luch.by</v>
       </c>
       <c r="K374" t="str">
-        <v/>
+        <v>luch.official</v>
       </c>
       <c r="L374" t="str">
         <v>MBWDB</v>
@@ -34490,7 +34490,7 @@
         <v>Lucleon</v>
       </c>
       <c r="B376" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C376" t="str">
         <v/>
@@ -34498,26 +34498,26 @@
       <c r="D376" t="str">
         <v/>
       </c>
-      <c r="E376" t="str">
-        <v/>
-      </c>
-      <c r="F376" t="str">
-        <v/>
+      <c r="E376">
+        <v>17</v>
+      </c>
+      <c r="F376">
+        <v>100</v>
       </c>
       <c r="G376" t="str">
         <v>Active</v>
       </c>
       <c r="H376" t="str">
-        <v/>
+        <v>Laurens Ternion Stainless Steel Dual Time Watch</v>
       </c>
       <c r="I376" t="str">
-        <v/>
+        <v>2024-04-01</v>
       </c>
       <c r="J376" t="str">
-        <v/>
+        <v>https://www.lucleon.com</v>
       </c>
       <c r="K376" t="str">
-        <v/>
+        <v>trendhim</v>
       </c>
       <c r="L376" t="str">
         <v>MBWDB</v>
@@ -35023,7 +35023,7 @@
         <v>Maker Watch Company</v>
       </c>
       <c r="B389" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C389" t="str">
         <v/>
@@ -35047,7 +35047,7 @@
         <v/>
       </c>
       <c r="J389" t="str">
-        <v/>
+        <v>https://www.makerwatchco.com</v>
       </c>
       <c r="K389" t="str">
         <v/>
@@ -35187,7 +35187,7 @@
         <v>Manufaktur Waldhoff</v>
       </c>
       <c r="B393" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C393" t="str">
         <v/>
@@ -35195,26 +35195,26 @@
       <c r="D393" t="str">
         <v/>
       </c>
-      <c r="E393" t="str">
-        <v/>
-      </c>
-      <c r="F393" t="str">
-        <v/>
+      <c r="E393">
+        <v>424</v>
+      </c>
+      <c r="F393">
+        <v>2331</v>
       </c>
       <c r="G393" t="str">
         <v>Active</v>
       </c>
       <c r="H393" t="str">
-        <v/>
+        <v>Quantum Ti</v>
       </c>
       <c r="I393" t="str">
-        <v/>
+        <v>2024-12-31</v>
       </c>
       <c r="J393" t="str">
-        <v/>
+        <v>https://www.manufaktur-waldhoff.de</v>
       </c>
       <c r="K393" t="str">
-        <v/>
+        <v>waldhoff_watches</v>
       </c>
       <c r="L393" t="str">
         <v>MBWDB</v>
@@ -35228,7 +35228,7 @@
         <v>Maranez</v>
       </c>
       <c r="B394" t="str">
-        <v/>
+        <v>Thailand</v>
       </c>
       <c r="C394" t="str">
         <v/>
@@ -35236,23 +35236,23 @@
       <c r="D394" t="str">
         <v/>
       </c>
-      <c r="E394" t="str">
-        <v/>
-      </c>
-      <c r="F394" t="str">
-        <v/>
+      <c r="E394">
+        <v>329</v>
+      </c>
+      <c r="F394">
+        <v>399</v>
       </c>
       <c r="G394" t="str">
         <v>Active</v>
       </c>
       <c r="H394" t="str">
-        <v/>
+        <v>Samui vintage titanium</v>
       </c>
       <c r="I394" t="str">
         <v/>
       </c>
       <c r="J394" t="str">
-        <v/>
+        <v>https://www.maranez.com</v>
       </c>
       <c r="K394" t="str">
         <v/>
@@ -35269,7 +35269,7 @@
         <v>Marcello C</v>
       </c>
       <c r="B395" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C395" t="str">
         <v/>
@@ -35293,7 +35293,7 @@
         <v/>
       </c>
       <c r="J395" t="str">
-        <v/>
+        <v>https://www.marcelloc.com</v>
       </c>
       <c r="K395" t="str">
         <v/>
@@ -35925,7 +35925,7 @@
         <v>McGonigle</v>
       </c>
       <c r="B411" t="str">
-        <v/>
+        <v>Ireland</v>
       </c>
       <c r="C411" t="str">
         <v/>
@@ -35949,7 +35949,7 @@
         <v/>
       </c>
       <c r="J411" t="str">
-        <v/>
+        <v>https://www.mcgonigle.ie</v>
       </c>
       <c r="K411" t="str">
         <v/>
@@ -36622,7 +36622,7 @@
         <v>Mini Focus</v>
       </c>
       <c r="B428" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C428" t="str">
         <v/>
@@ -36704,16 +36704,16 @@
         <v>Minuteman</v>
       </c>
       <c r="B430" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C430" t="str">
         <v/>
       </c>
-      <c r="D430" t="str">
-        <v/>
-      </c>
-      <c r="E430" t="str">
-        <v/>
+      <c r="D430">
+        <v>2017</v>
+      </c>
+      <c r="E430">
+        <v>369</v>
       </c>
       <c r="F430" t="str">
         <v/>
@@ -36722,16 +36722,16 @@
         <v>Active</v>
       </c>
       <c r="H430" t="str">
-        <v/>
+        <v>Parker Chronograph</v>
       </c>
       <c r="I430" t="str">
-        <v/>
+        <v>2020-01-20</v>
       </c>
       <c r="J430" t="str">
-        <v/>
+        <v>https://www.minutemanwatches.com</v>
       </c>
       <c r="K430" t="str">
-        <v/>
+        <v>minutemanwatches</v>
       </c>
       <c r="L430" t="str">
         <v>MBWDB</v>
@@ -38098,19 +38098,19 @@
         <v>Naviforce</v>
       </c>
       <c r="B464" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C464" t="str">
         <v/>
       </c>
-      <c r="D464" t="str">
-        <v/>
-      </c>
-      <c r="E464" t="str">
-        <v/>
-      </c>
-      <c r="F464" t="str">
-        <v/>
+      <c r="D464">
+        <v>2013</v>
+      </c>
+      <c r="E464">
+        <v>25</v>
+      </c>
+      <c r="F464">
+        <v>150</v>
       </c>
       <c r="G464" t="str">
         <v>Active</v>
@@ -38122,10 +38122,10 @@
         <v/>
       </c>
       <c r="J464" t="str">
-        <v/>
+        <v>https://www.naviforce.com</v>
       </c>
       <c r="K464" t="str">
-        <v/>
+        <v>naviforce_official</v>
       </c>
       <c r="L464" t="str">
         <v>MBWDB</v>
@@ -38672,7 +38672,7 @@
         <v>Nite</v>
       </c>
       <c r="B478" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C478" t="str">
         <v/>
@@ -38690,16 +38690,16 @@
         <v>Active</v>
       </c>
       <c r="H478" t="str">
-        <v/>
+        <v>MX10</v>
       </c>
       <c r="I478" t="str">
-        <v/>
+        <v>2024-12-31</v>
       </c>
       <c r="J478" t="str">
-        <v/>
+        <v>https://www.nitewatches.com</v>
       </c>
       <c r="K478" t="str">
-        <v/>
+        <v>nitewatches</v>
       </c>
       <c r="L478" t="str">
         <v>MBWDB</v>
@@ -39000,7 +39000,7 @@
         <v>Norquain</v>
       </c>
       <c r="B486" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C486" t="str">
         <v/>
@@ -39008,26 +39008,26 @@
       <c r="D486" t="str">
         <v/>
       </c>
-      <c r="E486" t="str">
-        <v/>
-      </c>
-      <c r="F486" t="str">
-        <v/>
+      <c r="E486">
+        <v>2800</v>
+      </c>
+      <c r="F486">
+        <v>17000</v>
       </c>
       <c r="G486" t="str">
         <v>Active</v>
       </c>
       <c r="H486" t="str">
-        <v/>
+        <v>Wild ONE of 1</v>
       </c>
       <c r="I486" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J486" t="str">
-        <v/>
+        <v>https://www.norquain.com</v>
       </c>
       <c r="K486" t="str">
-        <v/>
+        <v>norqain</v>
       </c>
       <c r="L486" t="str">
         <v>MBWDB</v>
@@ -39410,7 +39410,7 @@
         <v>Objest</v>
       </c>
       <c r="B496" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C496" t="str">
         <v/>
@@ -39431,13 +39431,13 @@
         <v/>
       </c>
       <c r="I496" t="str">
-        <v/>
+        <v>2021-01-01</v>
       </c>
       <c r="J496" t="str">
-        <v/>
+        <v>https://www.objest.com</v>
       </c>
       <c r="K496" t="str">
-        <v/>
+        <v>ObjestStyle</v>
       </c>
       <c r="L496" t="str">
         <v>MBWDB</v>
@@ -39451,7 +39451,7 @@
         <v>Obris Morgan</v>
       </c>
       <c r="B497" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C497" t="str">
         <v/>
@@ -39459,26 +39459,26 @@
       <c r="D497" t="str">
         <v/>
       </c>
-      <c r="E497" t="str">
-        <v/>
-      </c>
-      <c r="F497" t="str">
-        <v/>
+      <c r="E497">
+        <v>319</v>
+      </c>
+      <c r="F497">
+        <v>379</v>
       </c>
       <c r="G497" t="str">
         <v>Active</v>
       </c>
       <c r="H497" t="str">
-        <v/>
+        <v>Port</v>
       </c>
       <c r="I497" t="str">
         <v/>
       </c>
       <c r="J497" t="str">
-        <v/>
+        <v>https://www.obrismorgan.com</v>
       </c>
       <c r="K497" t="str">
-        <v/>
+        <v>obris_morgan</v>
       </c>
       <c r="L497" t="str">
         <v>MBWDB</v>
@@ -39533,7 +39533,7 @@
         <v>Ocean7</v>
       </c>
       <c r="B499" t="str">
-        <v/>
+        <v>Canada</v>
       </c>
       <c r="C499" t="str">
         <v/>
@@ -39557,7 +39557,7 @@
         <v/>
       </c>
       <c r="J499" t="str">
-        <v/>
+        <v>https://www.ocean7watches.com</v>
       </c>
       <c r="K499" t="str">
         <v/>
@@ -39743,29 +39743,29 @@
       <c r="C504" t="str">
         <v>Tel Aviv, Israel</v>
       </c>
-      <c r="D504" t="str">
-        <v/>
-      </c>
-      <c r="E504" t="str">
-        <v/>
-      </c>
-      <c r="F504" t="str">
-        <v/>
+      <c r="D504">
+        <v>1957</v>
+      </c>
+      <c r="E504">
+        <v>1650</v>
+      </c>
+      <c r="F504">
+        <v>3050</v>
       </c>
       <c r="G504" t="str">
         <v>Active</v>
       </c>
       <c r="H504" t="str">
-        <v/>
+        <v>OW 8001 TUNDRA</v>
       </c>
       <c r="I504" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J504" t="str">
         <v>https://www.ow-watch.com</v>
       </c>
       <c r="K504" t="str">
-        <v/>
+        <v>ollechandwajs</v>
       </c>
       <c r="L504" t="str">
         <v>existing-db</v>
@@ -39820,7 +39820,7 @@
         <v>Olto-8</v>
       </c>
       <c r="B506" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="C506" t="str">
         <v/>
@@ -39844,7 +39844,7 @@
         <v/>
       </c>
       <c r="J506" t="str">
-        <v/>
+        <v>https://www.olto8.com</v>
       </c>
       <c r="K506" t="str">
         <v/>
@@ -39943,7 +39943,7 @@
         <v>OOO – Out of Order</v>
       </c>
       <c r="B509" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="C509" t="str">
         <v/>
@@ -39967,7 +39967,7 @@
         <v/>
       </c>
       <c r="J509" t="str">
-        <v/>
+        <v>https://www.outoforder.cc</v>
       </c>
       <c r="K509" t="str">
         <v/>
@@ -40263,7 +40263,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M516" t="str">
-        <v/>
+        <v>Insufficient training data available for P.H. Watches. Brand identity and details cannot be reliably confirmed.</v>
       </c>
     </row>
     <row r="517">
@@ -40558,7 +40558,7 @@
         <v>Paulin</v>
       </c>
       <c r="B524" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C524" t="str">
         <v/>
@@ -40566,26 +40566,26 @@
       <c r="D524" t="str">
         <v/>
       </c>
-      <c r="E524" t="str">
-        <v/>
-      </c>
-      <c r="F524" t="str">
-        <v/>
+      <c r="E524">
+        <v>24</v>
+      </c>
+      <c r="F524">
+        <v>1110</v>
       </c>
       <c r="G524" t="str">
         <v>Active</v>
       </c>
       <c r="H524" t="str">
-        <v/>
+        <v>Neo Collection</v>
       </c>
       <c r="I524" t="str">
-        <v/>
+        <v>2026-03-23</v>
       </c>
       <c r="J524" t="str">
-        <v/>
+        <v>https://www.paulinwatches.com</v>
       </c>
       <c r="K524" t="str">
-        <v/>
+        <v>paulin_watches</v>
       </c>
       <c r="L524" t="str">
         <v>MBWDB</v>
@@ -41055,8 +41055,8 @@
       <c r="C536" t="str">
         <v/>
       </c>
-      <c r="D536" t="str">
-        <v/>
+      <c r="D536">
+        <v>1930</v>
       </c>
       <c r="E536" t="str">
         <v/>
@@ -41296,7 +41296,7 @@
         <v>Projects Watches</v>
       </c>
       <c r="B542" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C542" t="str">
         <v/>
@@ -41320,7 +41320,7 @@
         <v/>
       </c>
       <c r="J542" t="str">
-        <v/>
+        <v>https://www.projectswatches.com</v>
       </c>
       <c r="K542" t="str">
         <v/>
@@ -41378,7 +41378,7 @@
         <v>ProTek</v>
       </c>
       <c r="B544" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C544" t="str">
         <v/>
@@ -41402,7 +41402,7 @@
         <v/>
       </c>
       <c r="J544" t="str">
-        <v/>
+        <v>https://www.protekwatches.com</v>
       </c>
       <c r="K544" t="str">
         <v/>
@@ -41752,29 +41752,29 @@
       <c r="C553" t="str">
         <v>Peterhof, Russia</v>
       </c>
-      <c r="D553" t="str">
-        <v/>
-      </c>
-      <c r="E553" t="str">
-        <v/>
-      </c>
-      <c r="F553" t="str">
-        <v/>
+      <c r="D553">
+        <v>1895</v>
+      </c>
+      <c r="E553">
+        <v>625</v>
+      </c>
+      <c r="F553">
+        <v>5400</v>
       </c>
       <c r="G553" t="str">
         <v>Active</v>
       </c>
       <c r="H553" t="str">
-        <v/>
+        <v>Malevich Triptych</v>
       </c>
       <c r="I553" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J553" t="str">
         <v>https://www.raketa.com</v>
       </c>
       <c r="K553" t="str">
-        <v/>
+        <v>raketawatches</v>
       </c>
       <c r="L553" t="str">
         <v>existing-db</v>
@@ -41788,7 +41788,7 @@
         <v>Ratio Watches</v>
       </c>
       <c r="B554" t="str">
-        <v/>
+        <v>Hong Kong</v>
       </c>
       <c r="C554" t="str">
         <v/>
@@ -41796,26 +41796,26 @@
       <c r="D554" t="str">
         <v/>
       </c>
-      <c r="E554" t="str">
-        <v/>
-      </c>
-      <c r="F554" t="str">
-        <v/>
+      <c r="E554">
+        <v>87</v>
+      </c>
+      <c r="F554">
+        <v>495</v>
       </c>
       <c r="G554" t="str">
         <v>Active</v>
       </c>
       <c r="H554" t="str">
-        <v/>
+        <v>Ratio Street Racer Chronograph</v>
       </c>
       <c r="I554" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J554" t="str">
-        <v/>
+        <v>https://www.ratiowatches.com</v>
       </c>
       <c r="K554" t="str">
-        <v/>
+        <v>ratiowatches</v>
       </c>
       <c r="L554" t="str">
         <v>MBWDB</v>
@@ -41829,7 +41829,7 @@
         <v>Raven</v>
       </c>
       <c r="B555" t="str">
-        <v/>
+        <v>Canada</v>
       </c>
       <c r="C555" t="str">
         <v/>
@@ -41853,7 +41853,7 @@
         <v/>
       </c>
       <c r="J555" t="str">
-        <v/>
+        <v>https://www.ravenwatchco.com</v>
       </c>
       <c r="K555" t="str">
         <v/>
@@ -41870,7 +41870,7 @@
         <v>Rdunae</v>
       </c>
       <c r="B556" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C556" t="str">
         <v/>
@@ -41878,23 +41878,23 @@
       <c r="D556" t="str">
         <v/>
       </c>
-      <c r="E556" t="str">
-        <v/>
-      </c>
-      <c r="F556" t="str">
-        <v/>
+      <c r="E556">
+        <v>29</v>
+      </c>
+      <c r="F556">
+        <v>189</v>
       </c>
       <c r="G556" t="str">
         <v>Active</v>
       </c>
       <c r="H556" t="str">
-        <v/>
+        <v>Rdunae R2X Turtle 6105-8110</v>
       </c>
       <c r="I556" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J556" t="str">
-        <v/>
+        <v>https://www.rdunae.com</v>
       </c>
       <c r="K556" t="str">
         <v/>
@@ -41911,34 +41911,34 @@
         <v>Reactor</v>
       </c>
       <c r="B557" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C557" t="str">
         <v/>
       </c>
-      <c r="D557" t="str">
-        <v/>
-      </c>
-      <c r="E557" t="str">
-        <v/>
-      </c>
-      <c r="F557" t="str">
-        <v/>
+      <c r="D557">
+        <v>2017</v>
+      </c>
+      <c r="E557">
+        <v>149</v>
+      </c>
+      <c r="F557">
+        <v>480</v>
       </c>
       <c r="G557" t="str">
         <v>Active</v>
       </c>
       <c r="H557" t="str">
-        <v/>
+        <v>Crystal 2</v>
       </c>
       <c r="I557" t="str">
-        <v/>
+        <v>2024-05-05</v>
       </c>
       <c r="J557" t="str">
-        <v/>
+        <v>https://www.reactorwatch.com</v>
       </c>
       <c r="K557" t="str">
-        <v/>
+        <v>reactorwatchlp</v>
       </c>
       <c r="L557" t="str">
         <v>MBWDB</v>
@@ -41993,7 +41993,7 @@
         <v>RED BALLOON</v>
       </c>
       <c r="B559" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="C559" t="str">
         <v/>
@@ -42017,7 +42017,7 @@
         <v/>
       </c>
       <c r="J559" t="str">
-        <v/>
+        <v>https://www.redballoonwatch.com</v>
       </c>
       <c r="K559" t="str">
         <v/>
@@ -42034,7 +42034,7 @@
         <v>Redux</v>
       </c>
       <c r="B560" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C560" t="str">
         <v/>
@@ -42058,7 +42058,7 @@
         <v/>
       </c>
       <c r="J560" t="str">
-        <v/>
+        <v>https://www.reduxwatches.com</v>
       </c>
       <c r="K560" t="str">
         <v/>
@@ -42075,34 +42075,34 @@
         <v>Redwood Watches</v>
       </c>
       <c r="B561" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C561" t="str">
         <v/>
       </c>
-      <c r="D561" t="str">
-        <v/>
-      </c>
-      <c r="E561" t="str">
-        <v/>
-      </c>
-      <c r="F561" t="str">
-        <v/>
+      <c r="D561">
+        <v>2014</v>
+      </c>
+      <c r="E561">
+        <v>194</v>
+      </c>
+      <c r="F561">
+        <v>388</v>
       </c>
       <c r="G561" t="str">
         <v>Active</v>
       </c>
       <c r="H561" t="str">
-        <v/>
+        <v>Recon - C-47 Pathfinder (Full-Lume)</v>
       </c>
       <c r="I561" t="str">
-        <v/>
+        <v>2024-11-01</v>
       </c>
       <c r="J561" t="str">
-        <v/>
+        <v>https://www.redwoodwatches.com</v>
       </c>
       <c r="K561" t="str">
-        <v/>
+        <v>redwoodwatches</v>
       </c>
       <c r="L561" t="str">
         <v>MBWDB</v>
@@ -42157,7 +42157,7 @@
         <v>Reign</v>
       </c>
       <c r="B563" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C563" t="str">
         <v/>
@@ -42165,26 +42165,26 @@
       <c r="D563" t="str">
         <v/>
       </c>
-      <c r="E563" t="str">
-        <v/>
-      </c>
-      <c r="F563" t="str">
-        <v/>
+      <c r="E563">
+        <v>430</v>
+      </c>
+      <c r="F563">
+        <v>1595</v>
       </c>
       <c r="G563" t="str">
         <v>Active</v>
       </c>
       <c r="H563" t="str">
-        <v/>
+        <v>Olympia</v>
       </c>
       <c r="I563" t="str">
-        <v/>
+        <v>2024-12-31</v>
       </c>
       <c r="J563" t="str">
-        <v/>
+        <v>https://www.reignwatches.com</v>
       </c>
       <c r="K563" t="str">
-        <v/>
+        <v>reignwatches</v>
       </c>
       <c r="L563" t="str">
         <v>MBWDB</v>
@@ -42280,7 +42280,7 @@
         <v>Relax</v>
       </c>
       <c r="B566" t="str">
-        <v/>
+        <v>Japan</v>
       </c>
       <c r="C566" t="str">
         <v/>
@@ -42321,19 +42321,19 @@
         <v>Relic</v>
       </c>
       <c r="B567" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C567" t="str">
         <v/>
       </c>
-      <c r="D567" t="str">
-        <v/>
-      </c>
-      <c r="E567" t="str">
-        <v/>
-      </c>
-      <c r="F567" t="str">
-        <v/>
+      <c r="D567">
+        <v>1984</v>
+      </c>
+      <c r="E567">
+        <v>50</v>
+      </c>
+      <c r="F567">
+        <v>150</v>
       </c>
       <c r="G567" t="str">
         <v>Active</v>
@@ -42345,10 +42345,10 @@
         <v/>
       </c>
       <c r="J567" t="str">
-        <v/>
+        <v>https://www.relicwatches.com</v>
       </c>
       <c r="K567" t="str">
-        <v/>
+        <v>relicwatches</v>
       </c>
       <c r="L567" t="str">
         <v>MBWDB</v>
@@ -42403,7 +42403,7 @@
         <v>Renato</v>
       </c>
       <c r="B569" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C569" t="str">
         <v/>
@@ -42427,7 +42427,7 @@
         <v/>
       </c>
       <c r="J569" t="str">
-        <v/>
+        <v>https://www.renatowatches.com</v>
       </c>
       <c r="K569" t="str">
         <v/>
@@ -42444,7 +42444,7 @@
         <v>Resco</v>
       </c>
       <c r="B570" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C570" t="str">
         <v/>
@@ -42468,7 +42468,7 @@
         <v/>
       </c>
       <c r="J570" t="str">
-        <v/>
+        <v>https://www.rescowatches.com</v>
       </c>
       <c r="K570" t="str">
         <v/>
@@ -42567,34 +42567,34 @@
         <v>Reverie</v>
       </c>
       <c r="B573" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="C573" t="str">
         <v/>
       </c>
-      <c r="D573" t="str">
-        <v/>
-      </c>
-      <c r="E573" t="str">
-        <v/>
-      </c>
-      <c r="F573" t="str">
-        <v/>
+      <c r="D573">
+        <v>2014</v>
+      </c>
+      <c r="E573">
+        <v>225</v>
+      </c>
+      <c r="F573">
+        <v>550</v>
       </c>
       <c r="G573" t="str">
         <v>Active</v>
       </c>
       <c r="H573" t="str">
-        <v/>
+        <v>Diver</v>
       </c>
       <c r="I573" t="str">
         <v/>
       </c>
       <c r="J573" t="str">
-        <v/>
+        <v>https://www.reveriewatches.com</v>
       </c>
       <c r="K573" t="str">
-        <v/>
+        <v>reveriewatches</v>
       </c>
       <c r="L573" t="str">
         <v>MBWDB</v>
@@ -42649,7 +42649,7 @@
         <v>RGMT</v>
       </c>
       <c r="B575" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C575" t="str">
         <v/>
@@ -42673,7 +42673,7 @@
         <v/>
       </c>
       <c r="J575" t="str">
-        <v/>
+        <v>https://www.rgmtwatches.com</v>
       </c>
       <c r="K575" t="str">
         <v/>
@@ -42731,7 +42731,7 @@
         <v>Rhyno</v>
       </c>
       <c r="B577" t="str">
-        <v/>
+        <v>South Africa</v>
       </c>
       <c r="C577" t="str">
         <v/>
@@ -42755,7 +42755,7 @@
         <v/>
       </c>
       <c r="J577" t="str">
-        <v/>
+        <v>https://www.rhynowatches.com</v>
       </c>
       <c r="K577" t="str">
         <v/>
@@ -42813,7 +42813,7 @@
         <v>Richardt &amp; Mejer</v>
       </c>
       <c r="B579" t="str">
-        <v/>
+        <v>Denmark</v>
       </c>
       <c r="C579" t="str">
         <v/>
@@ -42837,7 +42837,7 @@
         <v/>
       </c>
       <c r="J579" t="str">
-        <v/>
+        <v>https://www.richardtmejer.com</v>
       </c>
       <c r="K579" t="str">
         <v/>
@@ -42936,7 +42936,7 @@
         <v>Riskers</v>
       </c>
       <c r="B582" t="str">
-        <v/>
+        <v>Spain</v>
       </c>
       <c r="C582" t="str">
         <v/>
@@ -42960,7 +42960,7 @@
         <v/>
       </c>
       <c r="J582" t="str">
-        <v/>
+        <v>https://www.riskers.co</v>
       </c>
       <c r="K582" t="str">
         <v/>
@@ -42977,7 +42977,7 @@
         <v>Ristola</v>
       </c>
       <c r="B583" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C583" t="str">
         <v/>
@@ -43001,7 +43001,7 @@
         <v/>
       </c>
       <c r="J583" t="str">
-        <v/>
+        <v>https://www.ristola.com</v>
       </c>
       <c r="K583" t="str">
         <v/>
@@ -43256,7 +43256,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M589" t="str">
-        <v/>
+        <v>Rössling &amp; Co is a watch brand with limited publicly available information in training data. Insufficient verified details available to confirm current status, pricing, or product specifications.</v>
       </c>
     </row>
     <row r="590">
@@ -43305,7 +43305,7 @@
         <v>Roue</v>
       </c>
       <c r="B591" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="C591" t="str">
         <v/>
@@ -43329,7 +43329,7 @@
         <v/>
       </c>
       <c r="J591" t="str">
-        <v/>
+        <v>https://www.rouewatches.com</v>
       </c>
       <c r="K591" t="str">
         <v/>
@@ -43428,7 +43428,7 @@
         <v>Ruckfield</v>
       </c>
       <c r="B594" t="str">
-        <v/>
+        <v>France</v>
       </c>
       <c r="C594" t="str">
         <v/>
@@ -43449,13 +43449,13 @@
         <v/>
       </c>
       <c r="I594" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J594" t="str">
-        <v/>
+        <v>https://www.ruckfield.com</v>
       </c>
       <c r="K594" t="str">
-        <v/>
+        <v>ruckfield</v>
       </c>
       <c r="L594" t="str">
         <v>MBWDB</v>
@@ -43469,7 +43469,7 @@
         <v>Rudiger</v>
       </c>
       <c r="B595" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C595" t="str">
         <v/>
@@ -43493,7 +43493,7 @@
         <v/>
       </c>
       <c r="J595" t="str">
-        <v/>
+        <v>https://www.rudigerwatches.com</v>
       </c>
       <c r="K595" t="str">
         <v/>
@@ -43510,7 +43510,7 @@
         <v>RUF</v>
       </c>
       <c r="B596" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C596" t="str">
         <v/>
@@ -43534,7 +43534,7 @@
         <v/>
       </c>
       <c r="J596" t="str">
-        <v/>
+        <v>https://www.ruf-watches.com</v>
       </c>
       <c r="K596" t="str">
         <v/>
@@ -43633,13 +43633,13 @@
         <v>RZE (Reise Watches)</v>
       </c>
       <c r="B599" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="C599" t="str">
         <v/>
       </c>
-      <c r="D599" t="str">
-        <v/>
+      <c r="D599">
+        <v>2020</v>
       </c>
       <c r="E599" t="str">
         <v/>
@@ -43651,16 +43651,16 @@
         <v>Active</v>
       </c>
       <c r="H599" t="str">
-        <v/>
+        <v>RESOLUTE UTD-8000</v>
       </c>
       <c r="I599" t="str">
-        <v/>
+        <v>2026-04-02</v>
       </c>
       <c r="J599" t="str">
-        <v/>
+        <v>https://www.rzewatches.com</v>
       </c>
       <c r="K599" t="str">
-        <v/>
+        <v>rzewatches</v>
       </c>
       <c r="L599" t="str">
         <v>MBWDB</v>
@@ -43797,7 +43797,7 @@
         <v>Salt</v>
       </c>
       <c r="B603" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C603" t="str">
         <v/>
@@ -43821,7 +43821,7 @@
         <v/>
       </c>
       <c r="J603" t="str">
-        <v/>
+        <v>https://www.saltwatches.com</v>
       </c>
       <c r="K603" t="str">
         <v/>
@@ -43879,7 +43879,7 @@
         <v>Sangin Instruments</v>
       </c>
       <c r="B605" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C605" t="str">
         <v/>
@@ -43903,7 +43903,7 @@
         <v/>
       </c>
       <c r="J605" t="str">
-        <v/>
+        <v>https://www.sangin-instruments.com</v>
       </c>
       <c r="K605" t="str">
         <v/>
@@ -44248,7 +44248,7 @@
         <v>Seaholm</v>
       </c>
       <c r="B614" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C614" t="str">
         <v/>
@@ -44272,7 +44272,7 @@
         <v/>
       </c>
       <c r="J614" t="str">
-        <v/>
+        <v>https://www.seaholmwatches.com</v>
       </c>
       <c r="K614" t="str">
         <v/>
@@ -44330,7 +44330,7 @@
         <v>Seapro</v>
       </c>
       <c r="B616" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C616" t="str">
         <v/>
@@ -44338,26 +44338,26 @@
       <c r="D616" t="str">
         <v/>
       </c>
-      <c r="E616" t="str">
-        <v/>
-      </c>
-      <c r="F616" t="str">
-        <v/>
+      <c r="E616">
+        <v>40</v>
+      </c>
+      <c r="F616">
+        <v>424</v>
       </c>
       <c r="G616" t="str">
         <v>Active</v>
       </c>
       <c r="H616" t="str">
-        <v/>
+        <v>Scuba Dragon Diver Limited Edition 1000 Meters</v>
       </c>
       <c r="I616" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J616" t="str">
-        <v/>
+        <v>https://www.seaprowatches.com</v>
       </c>
       <c r="K616" t="str">
-        <v/>
+        <v>seapro_watches</v>
       </c>
       <c r="L616" t="str">
         <v>MBWDB</v>
@@ -44494,7 +44494,7 @@
         <v>Seizmont</v>
       </c>
       <c r="B620" t="str">
-        <v/>
+        <v>Denmark</v>
       </c>
       <c r="C620" t="str">
         <v/>
@@ -44502,26 +44502,26 @@
       <c r="D620" t="str">
         <v/>
       </c>
-      <c r="E620" t="str">
-        <v/>
-      </c>
-      <c r="F620" t="str">
-        <v/>
+      <c r="E620">
+        <v>5</v>
+      </c>
+      <c r="F620">
+        <v>246</v>
       </c>
       <c r="G620" t="str">
         <v>Active</v>
       </c>
       <c r="H620" t="str">
-        <v/>
+        <v>Dante II</v>
       </c>
       <c r="I620" t="str">
-        <v/>
+        <v>2024-04-01</v>
       </c>
       <c r="J620" t="str">
-        <v/>
+        <v>https://www.seizmont.com</v>
       </c>
       <c r="K620" t="str">
-        <v/>
+        <v>trendhim</v>
       </c>
       <c r="L620" t="str">
         <v>MBWDB</v>
@@ -44740,7 +44740,7 @@
         <v>Sewills</v>
       </c>
       <c r="B626" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C626" t="str">
         <v/>
@@ -44764,7 +44764,7 @@
         <v/>
       </c>
       <c r="J626" t="str">
-        <v/>
+        <v>https://www.sewills.co.uk</v>
       </c>
       <c r="K626" t="str">
         <v/>
@@ -44863,7 +44863,7 @@
         <v>Shelby Watch Company</v>
       </c>
       <c r="B629" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C629" t="str">
         <v/>
@@ -45314,7 +45314,7 @@
         <v>SISU</v>
       </c>
       <c r="B640" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C640" t="str">
         <v/>
@@ -45322,26 +45322,26 @@
       <c r="D640" t="str">
         <v/>
       </c>
-      <c r="E640" t="str">
-        <v/>
-      </c>
-      <c r="F640" t="str">
-        <v/>
+      <c r="E640">
+        <v>308</v>
+      </c>
+      <c r="F640">
+        <v>1538</v>
       </c>
       <c r="G640" t="str">
         <v>Active</v>
       </c>
       <c r="H640" t="str">
-        <v/>
+        <v>BRAVADO CROSS</v>
       </c>
       <c r="I640" t="str">
         <v/>
       </c>
       <c r="J640" t="str">
-        <v/>
+        <v>https://www.sisuwatches.com</v>
       </c>
       <c r="K640" t="str">
-        <v/>
+        <v>sisuwatches</v>
       </c>
       <c r="L640" t="str">
         <v>MBWDB</v>
@@ -45396,7 +45396,7 @@
         <v>Smith Bradley</v>
       </c>
       <c r="B642" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C642" t="str">
         <v/>
@@ -45420,7 +45420,7 @@
         <v/>
       </c>
       <c r="J642" t="str">
-        <v/>
+        <v>https://www.smithbradley.com</v>
       </c>
       <c r="K642" t="str">
         <v/>
@@ -45437,7 +45437,7 @@
         <v>SNGLRTY Watch</v>
       </c>
       <c r="B643" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C643" t="str">
         <v/>
@@ -45461,7 +45461,7 @@
         <v/>
       </c>
       <c r="J643" t="str">
-        <v/>
+        <v>https://www.snglrty.com</v>
       </c>
       <c r="K643" t="str">
         <v/>
@@ -45560,7 +45560,7 @@
         <v>Söner Watches (Soner)</v>
       </c>
       <c r="B646" t="str">
-        <v/>
+        <v>Sweden</v>
       </c>
       <c r="C646" t="str">
         <v/>
@@ -45568,26 +45568,26 @@
       <c r="D646" t="str">
         <v/>
       </c>
-      <c r="E646" t="str">
-        <v/>
-      </c>
-      <c r="F646" t="str">
-        <v/>
+      <c r="E646">
+        <v>375</v>
+      </c>
+      <c r="F646">
+        <v>625</v>
       </c>
       <c r="G646" t="str">
         <v>Active</v>
       </c>
       <c r="H646" t="str">
-        <v/>
+        <v>Amorous</v>
       </c>
       <c r="I646" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J646" t="str">
-        <v/>
+        <v>https://www.sonerwatches.com</v>
       </c>
       <c r="K646" t="str">
-        <v/>
+        <v>sonerwatches</v>
       </c>
       <c r="L646" t="str">
         <v>MBWDB</v>
@@ -45642,7 +45642,7 @@
         <v>Sottomarino</v>
       </c>
       <c r="B648" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="C648" t="str">
         <v/>
@@ -45666,7 +45666,7 @@
         <v/>
       </c>
       <c r="J648" t="str">
-        <v/>
+        <v>https://www.sottomarinowatches.com</v>
       </c>
       <c r="K648" t="str">
         <v/>
@@ -45896,20 +45896,20 @@
       <c r="D654" t="str">
         <v/>
       </c>
-      <c r="E654" t="str">
-        <v/>
-      </c>
-      <c r="F654" t="str">
-        <v/>
+      <c r="E654">
+        <v>3900</v>
+      </c>
+      <c r="F654">
+        <v>6800</v>
       </c>
       <c r="G654" t="str">
         <v>Active</v>
       </c>
       <c r="H654" t="str">
-        <v/>
+        <v>ST02</v>
       </c>
       <c r="I654" t="str">
-        <v/>
+        <v>2024</v>
       </c>
       <c r="J654" t="str">
         <v>https://www.staterawatch.co</v>
@@ -46011,7 +46011,7 @@
         <v>Stewart Dawson</v>
       </c>
       <c r="B657" t="str">
-        <v/>
+        <v>New Zealand</v>
       </c>
       <c r="C657" t="str">
         <v/>
@@ -46216,7 +46216,7 @@
         <v>Straton Watch Co.</v>
       </c>
       <c r="B662" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C662" t="str">
         <v/>
@@ -46240,7 +46240,7 @@
         <v/>
       </c>
       <c r="J662" t="str">
-        <v/>
+        <v>https://www.stratonwatchco.com</v>
       </c>
       <c r="K662" t="str">
         <v/>
@@ -46257,7 +46257,7 @@
         <v>Straum</v>
       </c>
       <c r="B663" t="str">
-        <v/>
+        <v>Norway</v>
       </c>
       <c r="C663" t="str">
         <v/>
@@ -46281,7 +46281,7 @@
         <v/>
       </c>
       <c r="J663" t="str">
-        <v/>
+        <v>https://straumwatches.com</v>
       </c>
       <c r="K663" t="str">
         <v/>
@@ -46380,7 +46380,7 @@
         <v>Studio Underd0g Watches</v>
       </c>
       <c r="B666" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C666" t="str">
         <v/>
@@ -46404,7 +46404,7 @@
         <v/>
       </c>
       <c r="J666" t="str">
-        <v/>
+        <v>https://www.studiounderd0g.com</v>
       </c>
       <c r="K666" t="str">
         <v/>
@@ -46626,7 +46626,7 @@
         <v>Tactical Frog</v>
       </c>
       <c r="B672" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C672" t="str">
         <v/>
@@ -46708,7 +46708,7 @@
         <v>Tandorio</v>
       </c>
       <c r="B674" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C674" t="str">
         <v/>
@@ -46732,7 +46732,7 @@
         <v/>
       </c>
       <c r="J674" t="str">
-        <v/>
+        <v>https://www.tandorio.com</v>
       </c>
       <c r="K674" t="str">
         <v/>
@@ -46872,7 +46872,7 @@
         <v>Tecnotempo</v>
       </c>
       <c r="B678" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="C678" t="str">
         <v/>
@@ -47077,7 +47077,7 @@
         <v>The Abingdon Co.</v>
       </c>
       <c r="B683" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C683" t="str">
         <v/>
@@ -47085,26 +47085,26 @@
       <c r="D683" t="str">
         <v/>
       </c>
-      <c r="E683" t="str">
-        <v/>
-      </c>
-      <c r="F683" t="str">
-        <v/>
+      <c r="E683">
+        <v>29</v>
+      </c>
+      <c r="F683">
+        <v>1075</v>
       </c>
       <c r="G683" t="str">
         <v>Active</v>
       </c>
       <c r="H683" t="str">
-        <v/>
+        <v>Bonneville Blue</v>
       </c>
       <c r="I683" t="str">
-        <v/>
+        <v>2024-12-31</v>
       </c>
       <c r="J683" t="str">
-        <v/>
+        <v>https://www.theabingdonco.com</v>
       </c>
       <c r="K683" t="str">
-        <v/>
+        <v>theabingdonco</v>
       </c>
       <c r="L683" t="str">
         <v>MBWDB</v>
@@ -47118,7 +47118,7 @@
         <v>Theorema</v>
       </c>
       <c r="B684" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C684" t="str">
         <v/>
@@ -47323,7 +47323,7 @@
         <v>Timeless Swiss Watch</v>
       </c>
       <c r="B689" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C689" t="str">
         <v/>
@@ -47405,7 +47405,7 @@
         <v>Titus Watches</v>
       </c>
       <c r="B691" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C691" t="str">
         <v/>
@@ -47733,7 +47733,7 @@
         <v>Tourby Watches</v>
       </c>
       <c r="B699" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C699" t="str">
         <v/>
@@ -47757,7 +47757,7 @@
         <v/>
       </c>
       <c r="J699" t="str">
-        <v/>
+        <v>https://www.tourby.de</v>
       </c>
       <c r="K699" t="str">
         <v/>
@@ -47979,7 +47979,7 @@
         <v>Tsao Baltimore</v>
       </c>
       <c r="B705" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C705" t="str">
         <v/>
@@ -47997,16 +47997,16 @@
         <v>Active</v>
       </c>
       <c r="H705" t="str">
-        <v/>
+        <v>Torsk GMT 39</v>
       </c>
       <c r="I705" t="str">
         <v/>
       </c>
       <c r="J705" t="str">
-        <v/>
+        <v>https://www.tsaobaltimore.com</v>
       </c>
       <c r="K705" t="str">
-        <v/>
+        <v>tsaobaltimore</v>
       </c>
       <c r="L705" t="str">
         <v>MBWDB</v>
@@ -48020,7 +48020,7 @@
         <v>TSAR BOMBA</v>
       </c>
       <c r="B706" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C706" t="str">
         <v/>
@@ -48028,26 +48028,26 @@
       <c r="D706" t="str">
         <v/>
       </c>
-      <c r="E706" t="str">
-        <v/>
-      </c>
-      <c r="F706" t="str">
-        <v/>
+      <c r="E706">
+        <v>215</v>
+      </c>
+      <c r="F706">
+        <v>4870</v>
       </c>
       <c r="G706" t="str">
         <v>Active</v>
       </c>
       <c r="H706" t="str">
-        <v/>
+        <v>Dark Matter-Rafael Márquez Collaboration Limited Edition</v>
       </c>
       <c r="I706" t="str">
         <v/>
       </c>
       <c r="J706" t="str">
-        <v/>
+        <v>https://www.tsarbombawatch.com</v>
       </c>
       <c r="K706" t="str">
-        <v/>
+        <v>tsarbomba_watch</v>
       </c>
       <c r="L706" t="str">
         <v>MBWDB</v>
@@ -48102,34 +48102,34 @@
         <v>Tuseno</v>
       </c>
       <c r="B708" t="str">
-        <v/>
+        <v>Sweden</v>
       </c>
       <c r="C708" t="str">
         <v/>
       </c>
-      <c r="D708" t="str">
-        <v/>
-      </c>
-      <c r="E708" t="str">
-        <v/>
-      </c>
-      <c r="F708" t="str">
-        <v/>
+      <c r="D708">
+        <v>2015</v>
+      </c>
+      <c r="E708">
+        <v>549</v>
+      </c>
+      <c r="F708">
+        <v>1199</v>
       </c>
       <c r="G708" t="str">
         <v>Active</v>
       </c>
       <c r="H708" t="str">
-        <v/>
+        <v>Shellback V2</v>
       </c>
       <c r="I708" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J708" t="str">
-        <v/>
+        <v>https://www.tuseno.com</v>
       </c>
       <c r="K708" t="str">
-        <v/>
+        <v>tusenowatches</v>
       </c>
       <c r="L708" t="str">
         <v>MBWDB</v>
@@ -48184,7 +48184,7 @@
         <v>TWCO</v>
       </c>
       <c r="B710" t="str">
-        <v/>
+        <v>Australia</v>
       </c>
       <c r="C710" t="str">
         <v/>
@@ -48208,7 +48208,7 @@
         <v/>
       </c>
       <c r="J710" t="str">
-        <v/>
+        <v>https://www.twco.com.au</v>
       </c>
       <c r="K710" t="str">
         <v/>
@@ -48430,7 +48430,7 @@
         <v>UTS</v>
       </c>
       <c r="B716" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C716" t="str">
         <v/>
@@ -48448,13 +48448,13 @@
         <v>Active</v>
       </c>
       <c r="H716" t="str">
-        <v/>
+        <v>UTS Professional Diver/GMT Serie</v>
       </c>
       <c r="I716" t="str">
-        <v/>
+        <v>2012-12-31</v>
       </c>
       <c r="J716" t="str">
-        <v/>
+        <v>https://www.uts-watches.de</v>
       </c>
       <c r="K716" t="str">
         <v/>
@@ -48635,13 +48635,13 @@
         <v>Vario</v>
       </c>
       <c r="B721" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="C721" t="str">
         <v/>
       </c>
-      <c r="D721" t="str">
-        <v/>
+      <c r="D721">
+        <v>2014</v>
       </c>
       <c r="E721" t="str">
         <v/>
@@ -48653,16 +48653,16 @@
         <v>Active</v>
       </c>
       <c r="H721" t="str">
-        <v/>
+        <v>1918 Trench &amp; Medic</v>
       </c>
       <c r="I721" t="str">
         <v/>
       </c>
       <c r="J721" t="str">
-        <v/>
+        <v>https://www.vario.sg</v>
       </c>
       <c r="K721" t="str">
-        <v/>
+        <v>varioeveryday</v>
       </c>
       <c r="L721" t="str">
         <v>MBWDB</v>
@@ -48799,7 +48799,7 @@
         <v>Ventura Watches</v>
       </c>
       <c r="B725" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C725" t="str">
         <v/>
@@ -48823,7 +48823,7 @@
         <v/>
       </c>
       <c r="J725" t="str">
-        <v/>
+        <v>https://www.ventura-watches.com</v>
       </c>
       <c r="K725" t="str">
         <v/>
@@ -49127,7 +49127,7 @@
         <v>Vincenterra</v>
       </c>
       <c r="B733" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C733" t="str">
         <v/>
@@ -49151,7 +49151,7 @@
         <v/>
       </c>
       <c r="J733" t="str">
-        <v/>
+        <v>https://www.vincenterra.com</v>
       </c>
       <c r="K733" t="str">
         <v/>
@@ -49419,29 +49419,29 @@
       <c r="C740" t="str">
         <v/>
       </c>
-      <c r="D740" t="str">
-        <v/>
-      </c>
-      <c r="E740" t="str">
-        <v/>
-      </c>
-      <c r="F740" t="str">
-        <v/>
+      <c r="D740">
+        <v>1942</v>
+      </c>
+      <c r="E740">
+        <v>80</v>
+      </c>
+      <c r="F740">
+        <v>400</v>
       </c>
       <c r="G740" t="str">
         <v>Active</v>
       </c>
       <c r="H740" t="str">
-        <v/>
+        <v>Amphibia</v>
       </c>
       <c r="I740" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J740" t="str">
-        <v/>
+        <v>https://www.vostok.ru</v>
       </c>
       <c r="K740" t="str">
-        <v/>
+        <v>vostok_watches</v>
       </c>
       <c r="L740" t="str">
         <v>MBWDB</v>
@@ -49460,8 +49460,8 @@
       <c r="C741" t="str">
         <v/>
       </c>
-      <c r="D741" t="str">
-        <v/>
+      <c r="D741">
+        <v>2003</v>
       </c>
       <c r="E741" t="str">
         <v/>
@@ -49473,16 +49473,16 @@
         <v>Active</v>
       </c>
       <c r="H741" t="str">
-        <v/>
+        <v>Vilnelė</v>
       </c>
       <c r="I741" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J741" t="str">
-        <v/>
+        <v>https://www.vostok-europe.com</v>
       </c>
       <c r="K741" t="str">
-        <v/>
+        <v>vostok.europe.official</v>
       </c>
       <c r="L741" t="str">
         <v>MBWDB</v>
@@ -49701,7 +49701,7 @@
         <v>Waldan</v>
       </c>
       <c r="B747" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C747" t="str">
         <v/>
@@ -49824,7 +49824,7 @@
         <v>Welly Merck</v>
       </c>
       <c r="B750" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C750" t="str">
         <v/>
@@ -49832,26 +49832,26 @@
       <c r="D750" t="str">
         <v/>
       </c>
-      <c r="E750" t="str">
-        <v/>
-      </c>
-      <c r="F750" t="str">
-        <v/>
+      <c r="E750">
+        <v>144</v>
+      </c>
+      <c r="F750">
+        <v>277</v>
       </c>
       <c r="G750" t="str">
         <v>Active</v>
       </c>
       <c r="H750" t="str">
-        <v/>
+        <v>WM225</v>
       </c>
       <c r="I750" t="str">
-        <v/>
+        <v>2025-01-15</v>
       </c>
       <c r="J750" t="str">
-        <v/>
+        <v>https://www.wellymerck.com</v>
       </c>
       <c r="K750" t="str">
-        <v/>
+        <v>wm_watch</v>
       </c>
       <c r="L750" t="str">
         <v>MBWDB</v>
@@ -49865,7 +49865,7 @@
         <v>Werenbach</v>
       </c>
       <c r="B751" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C751" t="str">
         <v/>
@@ -49889,7 +49889,7 @@
         <v/>
       </c>
       <c r="J751" t="str">
-        <v/>
+        <v>https://www.werenbach.com</v>
       </c>
       <c r="K751" t="str">
         <v/>
@@ -49906,7 +49906,7 @@
         <v>West End Watch Co</v>
       </c>
       <c r="B752" t="str">
-        <v/>
+        <v>Switzerland</v>
       </c>
       <c r="C752" t="str">
         <v/>
@@ -49930,7 +49930,7 @@
         <v/>
       </c>
       <c r="J752" t="str">
-        <v/>
+        <v>https://www.westendwatch.com</v>
       </c>
       <c r="K752" t="str">
         <v/>
@@ -50070,13 +50070,13 @@
         <v>William L</v>
       </c>
       <c r="B756" t="str">
-        <v/>
+        <v>France</v>
       </c>
       <c r="C756" t="str">
         <v/>
       </c>
-      <c r="D756" t="str">
-        <v/>
+      <c r="D756">
+        <v>1985</v>
       </c>
       <c r="E756" t="str">
         <v/>
@@ -50094,10 +50094,10 @@
         <v/>
       </c>
       <c r="J756" t="str">
-        <v/>
+        <v>https://www.williaml1985.com</v>
       </c>
       <c r="K756" t="str">
-        <v/>
+        <v>williaml1985</v>
       </c>
       <c r="L756" t="str">
         <v>MBWDB</v>
@@ -50111,7 +50111,7 @@
         <v>William Wood</v>
       </c>
       <c r="B757" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C757" t="str">
         <v/>
@@ -50119,26 +50119,26 @@
       <c r="D757" t="str">
         <v/>
       </c>
-      <c r="E757" t="str">
-        <v/>
-      </c>
-      <c r="F757" t="str">
-        <v/>
+      <c r="E757">
+        <v>595</v>
+      </c>
+      <c r="F757">
+        <v>4795</v>
       </c>
       <c r="G757" t="str">
         <v>Active</v>
       </c>
       <c r="H757" t="str">
-        <v/>
+        <v>Dunkirk Watch</v>
       </c>
       <c r="I757" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J757" t="str">
-        <v/>
+        <v>https://www.williamwoodwatches.com</v>
       </c>
       <c r="K757" t="str">
-        <v/>
+        <v>williamwoodwatches</v>
       </c>
       <c r="L757" t="str">
         <v>MBWDB</v>
@@ -50193,7 +50193,7 @@
         <v>Winner</v>
       </c>
       <c r="B759" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C759" t="str">
         <v/>
@@ -50316,7 +50316,7 @@
         <v>WMT</v>
       </c>
       <c r="B762" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C762" t="str">
         <v/>
@@ -50324,26 +50324,26 @@
       <c r="D762" t="str">
         <v/>
       </c>
-      <c r="E762" t="str">
-        <v/>
-      </c>
-      <c r="F762" t="str">
-        <v/>
+      <c r="E762">
+        <v>335</v>
+      </c>
+      <c r="F762">
+        <v>690</v>
       </c>
       <c r="G762" t="str">
         <v>Active</v>
       </c>
       <c r="H762" t="str">
-        <v/>
+        <v>Cushion / Zheng He Voyages</v>
       </c>
       <c r="I762" t="str">
-        <v/>
+        <v>2026-02-12</v>
       </c>
       <c r="J762" t="str">
-        <v/>
+        <v>https://www.wmtwatches.com</v>
       </c>
       <c r="K762" t="str">
-        <v/>
+        <v>wmtwatches</v>
       </c>
       <c r="L762" t="str">
         <v>MBWDB</v>
@@ -50357,7 +50357,7 @@
         <v>Wolfpoint</v>
       </c>
       <c r="B763" t="str">
-        <v/>
+        <v>United States</v>
       </c>
       <c r="C763" t="str">
         <v/>
@@ -50381,7 +50381,7 @@
         <v/>
       </c>
       <c r="J763" t="str">
-        <v/>
+        <v>https://www.wolfpointwatches.com</v>
       </c>
       <c r="K763" t="str">
         <v/>
@@ -50422,7 +50422,7 @@
         <v/>
       </c>
       <c r="J764" t="str">
-        <v/>
+        <v>https://www.wolkov.com</v>
       </c>
       <c r="K764" t="str">
         <v/>
@@ -50726,7 +50726,7 @@
         <v>Yazole</v>
       </c>
       <c r="B772" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C772" t="str">
         <v/>
@@ -50734,11 +50734,11 @@
       <c r="D772" t="str">
         <v/>
       </c>
-      <c r="E772" t="str">
-        <v/>
-      </c>
-      <c r="F772" t="str">
-        <v/>
+      <c r="E772">
+        <v>15</v>
+      </c>
+      <c r="F772">
+        <v>50</v>
       </c>
       <c r="G772" t="str">
         <v>Active</v>
@@ -50808,7 +50808,7 @@
         <v>Yoshino</v>
       </c>
       <c r="B774" t="str">
-        <v/>
+        <v>United Kingdom</v>
       </c>
       <c r="C774" t="str">
         <v/>
@@ -50832,7 +50832,7 @@
         <v/>
       </c>
       <c r="J774" t="str">
-        <v/>
+        <v>https://www.yoshinowatches.com</v>
       </c>
       <c r="K774" t="str">
         <v/>
@@ -50931,7 +50931,7 @@
         <v>Zealandic</v>
       </c>
       <c r="B777" t="str">
-        <v/>
+        <v>New Zealand</v>
       </c>
       <c r="C777" t="str">
         <v/>
@@ -50955,7 +50955,7 @@
         <v/>
       </c>
       <c r="J777" t="str">
-        <v/>
+        <v>https://www.zealandic.com</v>
       </c>
       <c r="K777" t="str">
         <v/>
@@ -51013,7 +51013,7 @@
         <v>Zeitwinkel</v>
       </c>
       <c r="B779" t="str">
-        <v/>
+        <v>Germany</v>
       </c>
       <c r="C779" t="str">
         <v/>
@@ -51037,7 +51037,7 @@
         <v/>
       </c>
       <c r="J779" t="str">
-        <v/>
+        <v>https://www.zeitwinkel.com</v>
       </c>
       <c r="K779" t="str">
         <v/>
@@ -51406,7 +51406,7 @@
         <v/>
       </c>
       <c r="J788" t="str">
-        <v/>
+        <v>https://www.zlatoust.com</v>
       </c>
       <c r="K788" t="str">
         <v/>
@@ -51550,7 +51550,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B63"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -51649,7 +51649,7 @@
         <v>Australia</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -51657,44 +51657,44 @@
         <v>Austria</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Belgium</v>
+        <v>Belarus</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Canada</v>
+        <v>Belgium</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>China</v>
+        <v>Canada</v>
       </c>
       <c r="B16">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Croatia</v>
+        <v>China</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Cuba</v>
+        <v>Croatia</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -51702,7 +51702,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Czech Republic</v>
+        <v>Cuba</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -51710,55 +51710,55 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Denmark</v>
+        <v>Czech Republic</v>
       </c>
       <c r="B20">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>France</v>
+        <v>Denmark</v>
       </c>
       <c r="B21">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Germany</v>
+        <v>France</v>
       </c>
       <c r="B22">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Greece</v>
+        <v>Germany</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Hong Kong</v>
+        <v>Greece</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Hungary</v>
+        <v>Hong Kong</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Iceland</v>
+        <v>Hungary</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -51766,151 +51766,151 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>India</v>
+        <v>Iceland</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ireland</v>
+        <v>India</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Israel</v>
+        <v>Indonesia</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Italy</v>
+        <v>Ireland</v>
       </c>
       <c r="B30">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Japan</v>
+        <v>Israel</v>
       </c>
       <c r="B31">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lithuania</v>
+        <v>Italy</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Malaysia</v>
+        <v>Japan</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Netherlands</v>
+        <v>Lithuania</v>
       </c>
       <c r="B34">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Norway</v>
+        <v>Malaysia</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>null</v>
+        <v>Netherlands</v>
       </c>
       <c r="B36">
-        <v>775</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Romania</v>
+        <v>New Zealand</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Russia</v>
+        <v>Norway</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Singapore</v>
+        <v>null</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>594</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Slovakia</v>
+        <v>Poland</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>South Korea</v>
+        <v>Romania</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Spain</v>
+        <v>Russia</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Sweden</v>
+        <v>Singapore</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Switzerland</v>
+        <v>Slovakia</v>
       </c>
       <c r="B44">
-        <v>78</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Taiwan</v>
+        <v>South Africa</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -51918,47 +51918,47 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ukraine</v>
+        <v>South Korea</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>United Kingdom</v>
+        <v>Spain</v>
       </c>
       <c r="B47">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>United States</v>
+        <v>Sweden</v>
       </c>
       <c r="B48">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Unknown</v>
+        <v>Switzerland</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>USA</v>
+        <v>Taiwan</v>
       </c>
       <c r="B50">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Vietnam</v>
+        <v>Thailand</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -51966,47 +51966,103 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
-      </c>
-      <c r="B52" t="str">
-        <v/>
+        <v>Turkey</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Status</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Count</v>
+        <v>Ukraine</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Active</v>
+        <v>United Kingdom</v>
       </c>
       <c r="B54">
-        <v>1240</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Dormant</v>
+        <v>United States</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>USA</v>
+      </c>
+      <c r="B57">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Vietnam</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Status</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Count</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B61">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Dormant</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
         <v>Defunct</v>
       </c>
-      <c r="B56">
+      <c r="B63">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B63"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/watch-microbrand-database.xlsx
+++ b/watch-microbrand-database.xlsx
@@ -652,7 +652,7 @@
         <v>2025-12-09</v>
       </c>
       <c r="J6" t="str">
-        <v>https://adriatica.hr</v>
+        <v>https://adriaticawatches.ch/en/</v>
       </c>
       <c r="K6" t="str">
         <v>adriatica_official</v>
@@ -1226,7 +1226,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>https://aquastar.ch/</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1595,7 +1595,7 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>https://augustberg.com/</v>
       </c>
       <c r="K29" t="str">
         <v/>
@@ -1923,7 +1923,7 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>https://ballast-watch.de</v>
+        <v>https://www.ballast1903.com/</v>
       </c>
       <c r="K37" t="str">
         <v/>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>https://www.batavi-watches.com/</v>
       </c>
       <c r="K42" t="str">
         <v/>
@@ -2210,7 +2210,7 @@
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>https://bausele.de</v>
+        <v>https://www.bausele.com/</v>
       </c>
       <c r="K44" t="str">
         <v>bausele_watches</v>
@@ -3768,7 +3768,7 @@
         <v/>
       </c>
       <c r="J82" t="str">
-        <v/>
+        <v>https://dingemansmechanischehorloges.nl/</v>
       </c>
       <c r="K82" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v/>
       </c>
       <c r="J89" t="str">
-        <v/>
+        <v>https://www.delftwatchworks.com/en/</v>
       </c>
       <c r="K89" t="str">
         <v/>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="J91" t="str">
-        <v/>
+        <v>https://dennisonwatch.com/</v>
       </c>
       <c r="K91" t="str">
         <v/>
@@ -4588,7 +4588,7 @@
         <v/>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://draytonwatches.com/</v>
       </c>
       <c r="K102" t="str">
         <v/>
@@ -5080,7 +5080,7 @@
         <v/>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>http://www.enicar.com/</v>
       </c>
       <c r="K114" t="str">
         <v/>
@@ -5695,7 +5695,7 @@
         <v/>
       </c>
       <c r="J129" t="str">
-        <v/>
+        <v>https://www.guinand-uhren.de/home-en.html</v>
       </c>
       <c r="K129" t="str">
         <v/>
@@ -6228,7 +6228,7 @@
         <v/>
       </c>
       <c r="J142" t="str">
-        <v/>
+        <v>https://www.humbert-droz.fr/en/</v>
       </c>
       <c r="K142" t="str">
         <v/>
@@ -6597,7 +6597,7 @@
         <v/>
       </c>
       <c r="J151" t="str">
-        <v/>
+        <v>https://mccabewatches.com/</v>
       </c>
       <c r="K151" t="str">
         <v/>
@@ -6925,7 +6925,7 @@
         <v/>
       </c>
       <c r="J159" t="str">
-        <v/>
+        <v>https://www.karlskronawatch.com/</v>
       </c>
       <c r="K159" t="str">
         <v/>
@@ -7458,7 +7458,7 @@
         <v/>
       </c>
       <c r="J172" t="str">
-        <v/>
+        <v>https://www.lang-und-heyne.de/en/collection/</v>
       </c>
       <c r="K172" t="str">
         <v/>
@@ -7499,7 +7499,7 @@
         <v/>
       </c>
       <c r="J173" t="str">
-        <v/>
+        <v>https://apelvikenwatches.com/pages/about</v>
       </c>
       <c r="K173" t="str">
         <v/>
@@ -8196,7 +8196,7 @@
         <v/>
       </c>
       <c r="J190" t="str">
-        <v/>
+        <v>https://marketplace.watchcharts.com/listings/brand/manchester+watch+works</v>
       </c>
       <c r="K190" t="str">
         <v/>
@@ -8278,7 +8278,7 @@
         <v/>
       </c>
       <c r="J192" t="str">
-        <v/>
+        <v>https://www.marcdarno.com</v>
       </c>
       <c r="K192" t="str">
         <v/>
@@ -8770,7 +8770,7 @@
         <v/>
       </c>
       <c r="J204" t="str">
-        <v/>
+        <v>https://www.merkurwatch.com/</v>
       </c>
       <c r="K204" t="str">
         <v/>
@@ -8811,7 +8811,7 @@
         <v/>
       </c>
       <c r="J205" t="str">
-        <v/>
+        <v>https://miangcopenhagen.com/pages/about-us</v>
       </c>
       <c r="K205" t="str">
         <v/>
@@ -8934,7 +8934,7 @@
         <v/>
       </c>
       <c r="J208" t="str">
-        <v/>
+        <v>https://bulangandsons.com/collections/minerva</v>
       </c>
       <c r="K208" t="str">
         <v/>
@@ -9344,7 +9344,7 @@
         <v/>
       </c>
       <c r="J218" t="str">
-        <v>https://www.nordgreen.io</v>
+        <v>https://nordgreen.com/en-us</v>
       </c>
       <c r="K218" t="str">
         <v>nordgreenofficial</v>
@@ -9590,7 +9590,7 @@
         <v/>
       </c>
       <c r="J224" t="str">
-        <v/>
+        <v>https://www.orologicalamai.com/</v>
       </c>
       <c r="K224" t="str">
         <v/>
@@ -9754,7 +9754,7 @@
         <v/>
       </c>
       <c r="J228" t="str">
-        <v/>
+        <v>https://pinet-montrivel.com/en/1729-2/</v>
       </c>
       <c r="K228" t="str">
         <v/>
@@ -10123,7 +10123,7 @@
         <v/>
       </c>
       <c r="J237" t="str">
-        <v/>
+        <v>https://radiuminstruments.no/</v>
       </c>
       <c r="K237" t="str">
         <v/>
@@ -11025,7 +11025,7 @@
         <v>2024-09-15</v>
       </c>
       <c r="J259" t="str">
-        <v>https://www.serica.watches</v>
+        <v>https://serica-watches.com/en</v>
       </c>
       <c r="K259" t="str">
         <v>serica_watches</v>
@@ -11394,7 +11394,7 @@
         <v/>
       </c>
       <c r="J268" t="str">
-        <v/>
+        <v>https://www.stefanobragawatches.com/products/selene-dlc</v>
       </c>
       <c r="K268" t="str">
         <v/>
@@ -11927,7 +11927,7 @@
         <v/>
       </c>
       <c r="J281" t="str">
-        <v/>
+        <v>http://www.tmfwatches.com/en/</v>
       </c>
       <c r="K281" t="str">
         <v/>
@@ -12091,7 +12091,7 @@
         <v/>
       </c>
       <c r="J285" t="str">
-        <v>https://www.tufina.de</v>
+        <v>https://tufinawatches.com/</v>
       </c>
       <c r="K285" t="str">
         <v/>
@@ -12296,7 +12296,7 @@
         <v/>
       </c>
       <c r="J290" t="str">
-        <v/>
+        <v>https://ugolinimeccanicawatches.com/</v>
       </c>
       <c r="K290" t="str">
         <v/>
@@ -12419,7 +12419,7 @@
         <v/>
       </c>
       <c r="J293" t="str">
-        <v/>
+        <v>https://www.valhallaofnorway.no/</v>
       </c>
       <c r="K293" t="str">
         <v/>
@@ -15028,7 +15028,7 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>https://grandeur-usa.com/</v>
       </c>
       <c r="K46" t="str">
         <v/>
@@ -16340,7 +16340,7 @@
         <v/>
       </c>
       <c r="J78" t="str">
-        <v/>
+        <v>https://rarebirds.de/</v>
       </c>
       <c r="K78" t="str">
         <v/>
@@ -17760,7 +17760,7 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>https://bureiwatches.com/</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -17842,7 +17842,7 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>https://linkandtag.com/2025/10/18/ckl-watches/</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -17883,7 +17883,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>https://corgeutwatchco.com/</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -17924,7 +17924,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>https://crrju.com/</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -18047,7 +18047,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>https://guanqin-watch.com/</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -18211,7 +18211,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>https://jaipur.watch/en-us</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -18252,7 +18252,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>https://www.kentex.jp</v>
+        <v>http://www.kentexwatch.com/</v>
       </c>
       <c r="K21" t="str">
         <v>kentex_official</v>
@@ -18293,7 +18293,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>https://kiwametokyo.com/en/collections/watches</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -18703,7 +18703,7 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>https://www.pitzmann.com/</v>
       </c>
       <c r="K32" t="str">
         <v/>
@@ -18744,7 +18744,7 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v/>
+        <v>https://sugesswatch.com/</v>
       </c>
       <c r="K33" t="str">
         <v/>
@@ -18867,7 +18867,7 @@
         <v/>
       </c>
       <c r="J36" t="str">
-        <v/>
+        <v>https://solvil-et-titus.sg/</v>
       </c>
       <c r="K36" t="str">
         <v/>
@@ -18908,7 +18908,7 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v/>
+        <v>https://wancherwatch.com/</v>
       </c>
       <c r="K37" t="str">
         <v/>
@@ -24346,7 +24346,7 @@
         <v/>
       </c>
       <c r="J128" t="str">
-        <v/>
+        <v>https://poshmark.com/brand/charles%20Delon-Women-Accessories-Watches</v>
       </c>
       <c r="K128" t="str">
         <v/>
@@ -25863,7 +25863,7 @@
         <v/>
       </c>
       <c r="J165" t="str">
-        <v>https://diakka.co/</v>
+        <v>https://shop.simon.com/collections/curated-watches-and-sunglasses?Brand=Diakka</v>
       </c>
       <c r="K165" t="str">
         <v/>
@@ -27913,7 +27913,7 @@
         <v/>
       </c>
       <c r="J215" t="str">
-        <v>https://www.eza.watch</v>
+        <v>https://ezawatches.com/</v>
       </c>
       <c r="K215" t="str">
         <v/>
@@ -29512,7 +29512,7 @@
         <v/>
       </c>
       <c r="J254" t="str">
-        <v>https://www.gerlach.watch</v>
+        <v>https://www.gerlach.org.pl/en/g-gerlach/</v>
       </c>
       <c r="K254" t="str">
         <v/>
@@ -30373,7 +30373,7 @@
         <v/>
       </c>
       <c r="J275" t="str">
-        <v>https://www.h2owatches.dk</v>
+        <v>https://www.h2o-watch.com/</v>
       </c>
       <c r="K275" t="str">
         <v>h2owatches</v>
@@ -32956,7 +32956,7 @@
         <v/>
       </c>
       <c r="J338" t="str">
-        <v>https://www.jswatchco.is</v>
+        <v>https://www.jswatch.com</v>
       </c>
       <c r="K338" t="str">
         <v/>
@@ -33571,7 +33571,7 @@
         <v/>
       </c>
       <c r="J353" t="str">
-        <v>https://www.kuoe.jp</v>
+        <v>https://www.kuoe-en.com/</v>
       </c>
       <c r="K353" t="str">
         <v/>
@@ -42960,7 +42960,7 @@
         <v/>
       </c>
       <c r="J582" t="str">
-        <v>https://www.riskers.co</v>
+        <v>https://riskers-watches.com/</v>
       </c>
       <c r="K582" t="str">
         <v/>

--- a/watch-microbrand-database.xlsx
+++ b/watch-microbrand-database.xlsx
@@ -608,7 +608,7 @@
         <v>NIMROD</v>
       </c>
       <c r="I5" t="str">
-        <v>2025-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J5" t="str">
         <v>https://www.abingerwatches.com</v>
@@ -895,7 +895,7 @@
         <v>Thyïlea GMT</v>
       </c>
       <c r="I12" t="str">
-        <v>2026-03-30</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J12" t="str">
         <v>https://www.aevig.com</v>
@@ -977,7 +977,7 @@
         <v>Type 20 70 ANS</v>
       </c>
       <c r="I14" t="str">
-        <v>2025-10-23</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J14" t="str">
         <v>https://www.airain.com</v>
@@ -1182,7 +1182,7 @@
         <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J19" t="str">
         <v>https://www.alato.se/en</v>
@@ -1264,7 +1264,7 @@
         <v>A3 Omen II</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J21" t="str">
         <v>https://alexanderjameswatches.com/</v>
@@ -1305,7 +1305,7 @@
         <v>Kandy Fantasy</v>
       </c>
       <c r="I22" t="str">
-        <v>2025-12-16</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J22" t="str">
         <v>https://www.alexander-shorokhoff.com</v>
@@ -1387,7 +1387,7 @@
         <v>Model Three Diver</v>
       </c>
       <c r="I24" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J24" t="str">
         <v>https://alkinwatches.com/</v>
@@ -1551,7 +1551,7 @@
         <v>Nautilo Vintage Green</v>
       </c>
       <c r="I28" t="str">
-        <v>2022-11-14</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J28" t="str">
         <v>https://www.anonimo.com</v>
@@ -1592,7 +1592,7 @@
         <v>Model 2 Porcelain</v>
       </c>
       <c r="I29" t="str">
-        <v>2025-05-29</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J29" t="str">
         <v>https://anordain.com</v>
@@ -1879,7 +1879,7 @@
         <v>Klassik 200</v>
       </c>
       <c r="I36" t="str">
-        <v>2024-12-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J36" t="str">
         <v>https://www.archimede-watches.com</v>
@@ -1920,7 +1920,7 @@
         <v>Aquaristo Automatic 4H98294 (Klassik Diver series)</v>
       </c>
       <c r="I37" t="str">
-        <v>2026-02-23</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J37" t="str">
         <v>https://www.aristo.de</v>
@@ -2084,7 +2084,7 @@
         <v>FL 1889</v>
       </c>
       <c r="I41" t="str">
-        <v>2025-11-04</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J41" t="str">
         <v>https://www.ateliercaradant.com</v>
@@ -2576,7 +2576,7 @@
         <v>Chapter 8</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J53" t="str">
         <v>https://www.ba111od.com</v>
@@ -2781,7 +2781,7 @@
         <v>Aquascaphe</v>
       </c>
       <c r="I58" t="str">
-        <v>2024-10-15</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J58" t="str">
         <v>https://www.balticwatches.com</v>
@@ -2986,7 +2986,7 @@
         <v/>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J63" t="str">
         <v>https://www.bausele.com/</v>
@@ -3027,7 +3027,7 @@
         <v/>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J64" t="str">
         <v>https://www.beaubleu.fr</v>
@@ -3068,7 +3068,7 @@
         <v>Element 39.5mm</v>
       </c>
       <c r="I65" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J65" t="str">
         <v>https://beaucroftwatches.com/</v>
@@ -3150,7 +3150,7 @@
         <v>Rotary (2025)</v>
       </c>
       <c r="I67" t="str">
-        <v>2025-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J67" t="str">
         <v>https://www.behrenswatches.com</v>
@@ -3970,7 +3970,7 @@
         <v/>
       </c>
       <c r="I87" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J87" t="str">
         <v>https://www.bravur.com</v>
@@ -4052,7 +4052,7 @@
         <v>Terra Nova Jumping Hour</v>
       </c>
       <c r="I89" t="str">
-        <v>2024-10-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J89" t="str">
         <v>https://www.bremont.com</v>
@@ -4339,7 +4339,7 @@
         <v/>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J96" t="str">
         <v>https://www.bruvik.com</v>
@@ -4626,7 +4626,7 @@
         <v/>
       </c>
       <c r="I103" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J103" t="str">
         <v>https://www.cadola.ch</v>
@@ -5036,7 +5036,7 @@
         <v>C60 Trident Pro</v>
       </c>
       <c r="I113" t="str">
-        <v>2024-10-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J113" t="str">
         <v>https://www.christopherward.com</v>
@@ -5200,7 +5200,7 @@
         <v/>
       </c>
       <c r="I117" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J117" t="str">
         <v>https://www.circula.com</v>
@@ -5282,7 +5282,7 @@
         <v>Photic MKII</v>
       </c>
       <c r="I119" t="str">
-        <v>2024-12-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J119" t="str">
         <v>https://www.clemencewatches.com/</v>
@@ -5364,7 +5364,7 @@
         <v/>
       </c>
       <c r="I121" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J121" t="str">
         <v>https://www.code41.com</v>
@@ -5979,7 +5979,7 @@
         <v>DA47</v>
       </c>
       <c r="I136" t="str">
-        <v>2024-10-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J136" t="str">
         <v>https://www.damasko.de</v>
@@ -6061,7 +6061,7 @@
         <v>Argonautic World Traveller</v>
       </c>
       <c r="I138" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J138" t="str">
         <v>https://www.davosa.com</v>
@@ -6225,7 +6225,7 @@
         <v>DEKLA Pilot Watch 40mm Type B Bronze CuSn8</v>
       </c>
       <c r="I142" t="str">
-        <v>2024-12-31</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J142" t="str">
         <v>https://deklawatches.com/en</v>
@@ -6389,7 +6389,7 @@
         <v/>
       </c>
       <c r="I146" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J146" t="str">
         <v>https://dennisonwatch.com/</v>
@@ -6471,7 +6471,7 @@
         <v/>
       </c>
       <c r="I148" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J148" t="str">
         <v>https://www.depancel.com</v>
@@ -7004,7 +7004,7 @@
         <v/>
       </c>
       <c r="I161" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J161" t="str">
         <v>https://www.doxawatch.com</v>
@@ -7250,7 +7250,7 @@
         <v/>
       </c>
       <c r="I167" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J167" t="str">
         <v>https://www.dufa.com</v>
@@ -7414,7 +7414,7 @@
         <v>Rivanera</v>
       </c>
       <c r="I171" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J171" t="str">
         <v>https://www.echoneutra.com</v>
@@ -7701,7 +7701,7 @@
         <v>Arinis</v>
       </c>
       <c r="I178" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J178" t="str">
         <v>https://www.elkawatch.ch/</v>
@@ -8111,7 +8111,7 @@
         <v>Light Racing Range</v>
       </c>
       <c r="I188" t="str">
-        <v>2026-01-21</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J188" t="str">
         <v>https://www.eskawatches.com/en</v>
@@ -8193,7 +8193,7 @@
         <v/>
       </c>
       <c r="I190" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J190" t="str">
         <v>https://ezawatches.com/</v>
@@ -8234,7 +8234,7 @@
         <v>35mm Cushion Case Collection</v>
       </c>
       <c r="I191" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J191" t="str">
         <v>https://www.farer.co.uk</v>
@@ -8275,7 +8275,7 @@
         <v>Nexus</v>
       </c>
       <c r="I192" t="str">
-        <v>2024-12-19</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J192" t="str">
         <v>https://fatherswatches.com/en</v>
@@ -8398,7 +8398,7 @@
         <v>Brunswick</v>
       </c>
       <c r="I195" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J195" t="str">
         <v>https://www.fearswatches.com</v>
@@ -8439,7 +8439,7 @@
         <v>NAUTICMASTER FIELD DIVER</v>
       </c>
       <c r="I196" t="str">
-        <v>2025-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J196" t="str">
         <v>https://www.findeisen-uhren.com/en</v>
@@ -8644,7 +8644,7 @@
         <v>Essence Ceramica GT</v>
       </c>
       <c r="I201" t="str">
-        <v>2024-12-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J201" t="str">
         <v>https://www.formexwatch.com</v>
@@ -8685,7 +8685,7 @@
         <v>Abyss</v>
       </c>
       <c r="I202" t="str">
-        <v>2024-10-15</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J202" t="str">
         <v>https://www.fortis-watches.com</v>
@@ -8808,7 +8808,7 @@
         <v>Disco Onyx Diamonds</v>
       </c>
       <c r="I205" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J205" t="str">
         <v>https://www.furlanmarri.com</v>
@@ -9013,7 +9013,7 @@
         <v>Pioneer</v>
       </c>
       <c r="I210" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J210" t="str">
         <v>https://www.geckota.com</v>
@@ -9300,7 +9300,7 @@
         <v>Aquareef 40</v>
       </c>
       <c r="I217" t="str">
-        <v>2025-09-15</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J217" t="str">
         <v>https://www.golbywatches.co.uk</v>
@@ -9874,7 +9874,7 @@
         <v>Sport</v>
       </c>
       <c r="I231" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J231" t="str">
         <v>https://www.hagleywest.com</v>
@@ -10161,7 +10161,7 @@
         <v>Radiance</v>
       </c>
       <c r="I238" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J238" t="str">
         <v>https://heinrich.watch/en-us</v>
@@ -10243,7 +10243,7 @@
         <v/>
       </c>
       <c r="I240" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J240" t="str">
         <v>https://www.henryarcherwatches.com</v>
@@ -10325,7 +10325,7 @@
         <v>Marinor Classic</v>
       </c>
       <c r="I242" t="str">
-        <v>2024-10-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J242" t="str">
         <v>https://www.heronwatches.com/</v>
@@ -10448,7 +10448,7 @@
         <v>SIGNATURE ORNAMENT</v>
       </c>
       <c r="I245" t="str">
-        <v>2025</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J245" t="str">
         <v>https://www.holthinrichs.com</v>
@@ -10489,7 +10489,7 @@
         <v>K-TMR Micro-Rotor Tourbillon</v>
       </c>
       <c r="I246" t="str">
-        <v>2024-07-24</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J246" t="str">
         <v>https://www.horage.com</v>
@@ -10694,7 +10694,7 @@
         <v>Horopod</v>
       </c>
       <c r="I251" t="str">
-        <v>2025-01-08</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J251" t="str">
         <v>https://www.ikepod.com</v>
@@ -10899,7 +10899,7 @@
         <v/>
       </c>
       <c r="I256" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J256" t="str">
         <v>https://www.isotopewatches.com</v>
@@ -11309,7 +11309,7 @@
         <v/>
       </c>
       <c r="I266" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J266" t="str">
         <v>https://www.jswatch.com</v>
@@ -11350,7 +11350,7 @@
         <v>Aquaris Diver</v>
       </c>
       <c r="I267" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J267" t="str">
         <v>https://www.junghans.de</v>
@@ -11842,7 +11842,7 @@
         <v>Klok-01 5th Anniversary</v>
       </c>
       <c r="I279" t="str">
-        <v>2024-10-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J279" t="str">
         <v>https://www.klokers.com</v>
@@ -11965,7 +11965,7 @@
         <v>Projekt 02 Variant B</v>
       </c>
       <c r="I282" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J282" t="str">
         <v>https://kollokium.com/</v>
@@ -12170,7 +12170,7 @@
         <v>Laco Köln</v>
       </c>
       <c r="I287" t="str">
-        <v>2024-12-19</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J287" t="str">
         <v>https://www.laco.de</v>
@@ -12416,7 +12416,7 @@
         <v/>
       </c>
       <c r="I293" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J293" t="str">
         <v>https://www.laventure.ch</v>
@@ -12867,7 +12867,7 @@
         <v>Model No.2 Chronograph</v>
       </c>
       <c r="I304" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J304" t="str">
         <v>https://www.lorcawatches.com</v>
@@ -12908,7 +12908,7 @@
         <v>LS06</v>
       </c>
       <c r="I305" t="str">
-        <v>2024-12-31</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J305" t="str">
         <v>https://loresum.watch/collections/all-products</v>
@@ -13236,7 +13236,7 @@
         <v>Hudson 38 MK5</v>
       </c>
       <c r="I313" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J313" t="str">
         <v>https://www.maenwatches.com</v>
@@ -13523,7 +13523,7 @@
         <v/>
       </c>
       <c r="I320" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J320" t="str">
         <v>https://www.marc-and-sons.com</v>
@@ -13892,7 +13892,7 @@
         <v>Dark Surge 300A (Adriatic)</v>
       </c>
       <c r="I329" t="str">
-        <v>2025-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J329" t="str">
         <v>https://www.marnaut.com</v>
@@ -14261,7 +14261,7 @@
         <v>PROSPERITY GMT SNOWY OWL</v>
       </c>
       <c r="I338" t="str">
-        <v>2025-08-25</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J338" t="str">
         <v>https://www.maystonewatches.com/</v>
@@ -14343,7 +14343,7 @@
         <v>C1</v>
       </c>
       <c r="I340" t="str">
-        <v>2025-11-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J340" t="str">
         <v>https://mcquaide.co.uk/</v>
@@ -14753,7 +14753,7 @@
         <v>Milgraph T5 Pilot Series Worldtimer</v>
       </c>
       <c r="I350" t="str">
-        <v>2025-08-14</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J350" t="str">
         <v>https://www.micromilspec.com</v>
@@ -15450,7 +15450,7 @@
         <v>Daydreamer</v>
       </c>
       <c r="I367" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J367" t="str">
         <v>https://www.mrjoneswatches.com</v>
@@ -15573,7 +15573,7 @@
         <v>Diver II Automatic</v>
       </c>
       <c r="I370" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J370" t="str">
         <v>https://nautage.com/</v>
@@ -15614,7 +15614,7 @@
         <v>LM02 Type C</v>
       </c>
       <c r="I371" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J371" t="str">
         <v>https://www.neotypewatches.com</v>
@@ -15737,7 +15737,7 @@
         <v>6BB NP Professional Chronograph</v>
       </c>
       <c r="I374" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J374" t="str">
         <v>https://newmarkwatchcompany.com/</v>
@@ -15901,7 +15901,7 @@
         <v>F77 SST GREEN AVENTURINE MK2</v>
       </c>
       <c r="I378" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J378" t="str">
         <v>https://www.nivadagrenchenofficial.com</v>
@@ -16024,7 +16024,7 @@
         <v>The Brú 750</v>
       </c>
       <c r="I381" t="str">
-        <v>2026-03-20</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J381" t="str">
         <v>https://nomadicwatches.com/en-us</v>
@@ -16844,7 +16844,7 @@
         <v>Sector</v>
       </c>
       <c r="I401" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J401" t="str">
         <v>https://www.pareawatches.com</v>
@@ -16926,7 +16926,7 @@
         <v>Neo Collection</v>
       </c>
       <c r="I403" t="str">
-        <v>2026-03-23</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J403" t="str">
         <v>https://www.paulinwatches.com</v>
@@ -16967,7 +16967,7 @@
         <v>Final Frontier</v>
       </c>
       <c r="I404" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J404" t="str">
         <v>https://www.pedral.eu/</v>
@@ -17213,7 +17213,7 @@
         <v>Pure</v>
       </c>
       <c r="I410" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J410" t="str">
         <v>https://www.pinionwatches.com</v>
@@ -17664,7 +17664,7 @@
         <v>L'INSTANT SONORE</v>
       </c>
       <c r="I421" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J421" t="str">
         <v>https://www.radcliffewatches.com</v>
@@ -18156,7 +18156,7 @@
         <v/>
       </c>
       <c r="I433" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J433" t="str">
         <v>https://www.revue-thommen.com</v>
@@ -18853,7 +18853,7 @@
         <v/>
       </c>
       <c r="I450" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J450" t="str">
         <v>https://www.sangin-instruments.com</v>
@@ -18894,7 +18894,7 @@
         <v/>
       </c>
       <c r="I451" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J451" t="str">
         <v>https://www.sartorybillard.com</v>
@@ -19017,7 +19017,7 @@
         <v>The GMT</v>
       </c>
       <c r="I454" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J454" t="str">
         <v>https://www.schofieldwatches.com</v>
@@ -19099,7 +19099,7 @@
         <v>Diver One D1-500</v>
       </c>
       <c r="I456" t="str">
-        <v>2026-03-06</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J456" t="str">
         <v>https://www.scurfawatches.com</v>
@@ -19263,7 +19263,7 @@
         <v>M1 Moonphase</v>
       </c>
       <c r="I460" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J460" t="str">
         <v>https://seltenwatch.com/</v>
@@ -19386,7 +19386,7 @@
         <v>Serica Field Watch</v>
       </c>
       <c r="I463" t="str">
-        <v>2024-09-15</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J463" t="str">
         <v>https://serica-watches.com/en</v>
@@ -19591,7 +19591,7 @@
         <v/>
       </c>
       <c r="I468" t="str">
-        <v>2024-10-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J468" t="str">
         <v>https://www.sinn.de</v>
@@ -19960,7 +19960,7 @@
         <v/>
       </c>
       <c r="I477" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J477" t="str">
         <v>https://www.spaceone-watches.com</v>
@@ -20042,7 +20042,7 @@
         <v>Squale Matic S</v>
       </c>
       <c r="I479" t="str">
-        <v>2024-12-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J479" t="str">
         <v>https://www.squalewatches.com</v>
@@ -20206,7 +20206,7 @@
         <v>Marus 2.0 Edition Küste</v>
       </c>
       <c r="I483" t="str">
-        <v>2025-12-03</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J483" t="str">
         <v>https://www.sternglas.com</v>
@@ -20288,7 +20288,7 @@
         <v>Chrono Black Forest Moon</v>
       </c>
       <c r="I485" t="str">
-        <v>2024-11-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J485" t="str">
         <v>https://www.stowa.de</v>
@@ -20329,7 +20329,7 @@
         <v/>
       </c>
       <c r="I486" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J486" t="str">
         <v>https://straumwatches.com</v>
@@ -20534,7 +20534,7 @@
         <v/>
       </c>
       <c r="I491" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J491" t="str">
         <v>https://www.studiounderd0g.com</v>
@@ -20739,7 +20739,7 @@
         <v>Cannonball GMT</v>
       </c>
       <c r="I496" t="str">
-        <v>2024-12-31</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J496" t="str">
         <v>https://www.syewatches.com</v>
@@ -21026,7 +21026,7 @@
         <v/>
       </c>
       <c r="I503" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J503" t="str">
         <v>https://www.terraCielomare.com</v>
@@ -21149,7 +21149,7 @@
         <v>Smiths Commander 71 PRS-71</v>
       </c>
       <c r="I506" t="str">
-        <v>2026-03-10</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J506" t="str">
         <v>https://www.timefactors.com</v>
@@ -21354,7 +21354,7 @@
         <v>Marine Automatik 37mm</v>
       </c>
       <c r="I511" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J511" t="str">
         <v>https://www.tourby.de</v>
@@ -21436,7 +21436,7 @@
         <v>1000M</v>
       </c>
       <c r="I513" t="str">
-        <v>2024-06-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J513" t="str">
         <v>https://www.trematic.de</v>
@@ -21600,7 +21600,7 @@
         <v/>
       </c>
       <c r="I517" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J517" t="str">
         <v>https://tufinawatches.com/</v>
@@ -21641,7 +21641,7 @@
         <v>Shellback V2</v>
       </c>
       <c r="I518" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J518" t="str">
         <v>https://www.tuseno.com</v>
@@ -21805,7 +21805,7 @@
         <v>TREK DUAL SERIES 01</v>
       </c>
       <c r="I522" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J522" t="str">
         <v>https://www.ubiqwatches.com</v>
@@ -21928,7 +21928,7 @@
         <v/>
       </c>
       <c r="I525" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J525" t="str">
         <v>https://www.undonewatches.com</v>
@@ -21969,7 +21969,7 @@
         <v>Modello Tre U3FB-ROPS</v>
       </c>
       <c r="I526" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J526" t="str">
         <v>https://www.unimaticwatches.com</v>
@@ -22092,7 +22092,7 @@
         <v>Schallmauer Automatik</v>
       </c>
       <c r="I529" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J529" t="str">
         <v>https://www.vandaag.de/en/</v>
@@ -22297,7 +22297,7 @@
         <v>Redentore Utopia II</v>
       </c>
       <c r="I534" t="str">
-        <v>2026-01-25</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J534" t="str">
         <v>https://www.venezianico.it</v>
@@ -23281,7 +23281,7 @@
         <v>Dunkirk Watch</v>
       </c>
       <c r="I558" t="str">
-        <v>2024-10-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J558" t="str">
         <v>https://www.williamwoodwatches.com</v>
@@ -23445,7 +23445,7 @@
         <v>Superman Titanium MoonTide CMM.11 Limited Edition</v>
       </c>
       <c r="I562" t="str">
-        <v>2024-10-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J562" t="str">
         <v>https://www.yema.com</v>
@@ -23650,7 +23650,7 @@
         <v/>
       </c>
       <c r="I567" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J567" t="str">
         <v>https://www.zenowatch.ch</v>
@@ -23691,7 +23691,7 @@
         <v>S6e Spitfire Escape</v>
       </c>
       <c r="I568" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J568" t="str">
         <v>https://zerowest.watch/</v>
@@ -23963,7 +23963,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J2" t="str">
         <v>https://www.5280watch.com</v>
@@ -24209,7 +24209,7 @@
         <v>Aquatico Automatic Dive Watch</v>
       </c>
       <c r="I8" t="str">
-        <v>2024-09-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J8" t="str">
         <v>https://www.aquaticowatches.com</v>
@@ -24291,7 +24291,7 @@
         <v>Caribe</v>
       </c>
       <c r="I10" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J10" t="str">
         <v>https://ardiowatches.com/</v>
@@ -24496,7 +24496,7 @@
         <v>Terra Scout</v>
       </c>
       <c r="I15" t="str">
-        <v>2026-02-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J15" t="str">
         <v>https://astorandbanks.com</v>
@@ -24906,7 +24906,7 @@
         <v>Scarifour Automatic</v>
       </c>
       <c r="I25" t="str">
-        <v>2026-01-08</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J25" t="str">
         <v>https://benjaminjameswatches.com</v>
@@ -25029,7 +25029,7 @@
         <v/>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J28" t="str">
         <v>https://bernhardtwatch.com</v>
@@ -25152,7 +25152,7 @@
         <v>Odyssey MGP</v>
       </c>
       <c r="I31" t="str">
-        <v>2025-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J31" t="str">
         <v>https://www.boldrwatches.com</v>
@@ -25193,7 +25193,7 @@
         <v/>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J32" t="str">
         <v>https://www.borealiswatches.com</v>
@@ -25357,7 +25357,7 @@
         <v>Super Metric</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J36" t="str">
         <v>https://www.brew-watches.com</v>
@@ -25603,7 +25603,7 @@
         <v>Brooklyn Gent</v>
       </c>
       <c r="I42" t="str">
-        <v>2025-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J42" t="str">
         <v>https://carpenterwatches.com/</v>
@@ -25808,7 +25808,7 @@
         <v/>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J47" t="str">
         <v>https://www.cincinnatiwatchcompany.com</v>
@@ -25849,7 +25849,7 @@
         <v>Mechanic Ocean Mark II</v>
       </c>
       <c r="I48" t="str">
-        <v>2025-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J48" t="str">
         <v>https://www.crafterblue.com</v>
@@ -26177,7 +26177,7 @@
         <v>1975 Skin Diver</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J56" t="str">
         <v>https://www.danhenrywatches.com</v>
@@ -26505,7 +26505,7 @@
         <v>Westlake</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J64" t="str">
         <v>https://www.dufranewatches.com</v>
@@ -26956,7 +26956,7 @@
         <v>Seaplane Automatic</v>
       </c>
       <c r="I75" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J75" t="str">
         <v>https://www.farrandswit.com/</v>
@@ -27038,7 +27038,7 @@
         <v/>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J77" t="str">
         <v>https://www.feymantimekeepers.com</v>
@@ -27079,7 +27079,7 @@
         <v>FLX004</v>
       </c>
       <c r="I78" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J78" t="str">
         <v>https://www.fleuxwatches.com/</v>
@@ -27325,7 +27325,7 @@
         <v>Ocean Rover</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J84" t="str">
         <v>https://www.ginaultocean.com</v>
@@ -27366,7 +27366,7 @@
         <v/>
       </c>
       <c r="I85" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J85" t="str">
         <v>https://grandeur-usa.com/</v>
@@ -27612,7 +27612,7 @@
         <v/>
       </c>
       <c r="I91" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J91" t="str">
         <v>https://www.helmwatches.com</v>
@@ -27653,7 +27653,7 @@
         <v>Sky Racer</v>
       </c>
       <c r="I92" t="str">
-        <v>2024</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J92" t="str">
         <v>https://www.hemelwatches.com</v>
@@ -27694,7 +27694,7 @@
         <v>Bexley</v>
       </c>
       <c r="I93" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J93" t="str">
         <v>https://www.heritorwatches.com</v>
@@ -27940,7 +27940,7 @@
         <v/>
       </c>
       <c r="I99" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J99" t="str">
         <v>https://www.islanderwatches.com</v>
@@ -28555,7 +28555,7 @@
         <v>Astra</v>
       </c>
       <c r="I114" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J114" t="str">
         <v>https://www.lorierwatches.com</v>
@@ -28596,7 +28596,7 @@
         <v>M94 Bronze Date</v>
       </c>
       <c r="I115" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J115" t="str">
         <v>https://www.lum-tec.com</v>
@@ -29047,7 +29047,7 @@
         <v>Splash Eclipse</v>
       </c>
       <c r="I126" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J126" t="str">
         <v>https://www.momentumwatch.com</v>
@@ -29088,7 +29088,7 @@
         <v>Triumph</v>
       </c>
       <c r="I127" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J127" t="str">
         <v>https://www.montawatch.com</v>
@@ -29416,7 +29416,7 @@
         <v>Sector Deep</v>
       </c>
       <c r="I135" t="str">
-        <v>2024-12-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J135" t="str">
         <v>https://www.noduswatches.com</v>
@@ -29457,7 +29457,7 @@
         <v>Sentinel Collection</v>
       </c>
       <c r="I136" t="str">
-        <v>2024-12-19</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J136" t="str">
         <v>https://www.northernstarwatch.com/</v>
@@ -29662,7 +29662,7 @@
         <v>Core Diver</v>
       </c>
       <c r="I141" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J141" t="str">
         <v>https://www.oceancrawlerwatch.com</v>
@@ -29908,7 +29908,7 @@
         <v/>
       </c>
       <c r="I147" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J147" t="str">
         <v>https://www.orionwatches.com</v>
@@ -30113,7 +30113,7 @@
         <v>Jungle Field Automatic 38</v>
       </c>
       <c r="I152" t="str">
-        <v>2024-12-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J152" t="str">
         <v>https://www.praesidus.com</v>
@@ -30277,7 +30277,7 @@
         <v/>
       </c>
       <c r="I156" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J156" t="str">
         <v>https://www.ravenwatchco.com</v>
@@ -30318,7 +30318,7 @@
         <v>Crystal 2</v>
       </c>
       <c r="I157" t="str">
-        <v>2024-05-05</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J157" t="str">
         <v>https://www.reactorwatch.com</v>
@@ -30441,7 +30441,7 @@
         <v>Recon - C-47 Pathfinder (Full-Lume)</v>
       </c>
       <c r="I160" t="str">
-        <v>2024-11-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J160" t="str">
         <v>https://www.redwoodwatches.com</v>
@@ -32122,7 +32122,7 @@
         <v>Commuter</v>
       </c>
       <c r="I201" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J201" t="str">
         <v>https://www.traskawatch.com</v>
@@ -32245,7 +32245,7 @@
         <v>Torsk GMT 39</v>
       </c>
       <c r="I204" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J204" t="str">
         <v>https://www.tsaobaltimore.com</v>
@@ -32327,7 +32327,7 @@
         <v>C1 Ceremony Salmon</v>
       </c>
       <c r="I206" t="str">
-        <v>2024-12-19</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J206" t="str">
         <v>https://www.vaerwatches.com</v>
@@ -32614,7 +32614,7 @@
         <v>Duneshore Shallows</v>
       </c>
       <c r="I213" t="str">
-        <v>2025-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J213" t="str">
         <v>https://www.visitorwatchco.com/</v>
@@ -33024,7 +33024,7 @@
         <v/>
       </c>
       <c r="I223" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J223" t="str">
         <v>https://www.wolfpointwatches.com</v>
@@ -33065,7 +33065,7 @@
         <v>Enforcer</v>
       </c>
       <c r="I224" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J224" t="str">
         <v>https://www.xericdesigns.com</v>
@@ -33188,7 +33188,7 @@
         <v>Ultrathin</v>
       </c>
       <c r="I227" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J227" t="str">
         <v>https://www.zeloswatch.com</v>
@@ -33337,7 +33337,7 @@
         <v>Horizon Voyager</v>
       </c>
       <c r="I3" t="str">
-        <v>2024-12-19</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J3" t="str">
         <v>https://aethelsohnwatch.com/</v>
@@ -33378,7 +33378,7 @@
         <v>Volcano</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J4" t="str">
         <v>https://agelocer.com</v>
@@ -33419,7 +33419,7 @@
         <v>Kakori 8 Down- Centenary Edition</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-03-27</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J5" t="str">
         <v>https://ajwa.in/</v>
@@ -33501,7 +33501,7 @@
         <v>Voyager Worldtimer GMT</v>
       </c>
       <c r="I7" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J7" t="str">
         <v>https://alcadus.com/</v>
@@ -33665,7 +33665,7 @@
         <v>Inflection</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J11" t="str">
         <v>https://www.atelierwen.com</v>
@@ -33788,7 +33788,7 @@
         <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J14" t="str">
         <v>https://awakewatches.com.au</v>
@@ -33911,7 +33911,7 @@
         <v/>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J17" t="str">
         <v>https://bangalorewatch.com</v>
@@ -34116,7 +34116,7 @@
         <v>Voyager Chronograph</v>
       </c>
       <c r="I22" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J22" t="str">
         <v>https://www.boderry.com</v>
@@ -34362,7 +34362,7 @@
         <v/>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J28" t="str">
         <v>https://www.cigadesign.com</v>
@@ -34567,7 +34567,7 @@
         <v>DW-D3</v>
       </c>
       <c r="I33" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J33" t="str">
         <v>https://www.duzuwatches.com/</v>
@@ -34608,7 +34608,7 @@
         <v/>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J34" t="str">
         <v>https://www.earthenco.com</v>
@@ -35059,7 +35059,7 @@
         <v>Broadway 40</v>
       </c>
       <c r="I45" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J45" t="str">
         <v>https://www.havaantuvali.com/</v>
@@ -35264,7 +35264,7 @@
         <v>Pilbara Rock Dive Watch - Second Release</v>
       </c>
       <c r="I50" t="str">
-        <v>2024-12-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J50" t="str">
         <v>https://houtmanwatch.com/</v>
@@ -35674,7 +35674,7 @@
         <v/>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J60" t="str">
         <v>https://kiwametokyo.com/en/collections/watches</v>
@@ -35756,7 +35756,7 @@
         <v/>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J62" t="str">
         <v>https://www.kuoe-en.com/</v>
@@ -35838,7 +35838,7 @@
         <v>Kronosprinter</v>
       </c>
       <c r="I64" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J64" t="str">
         <v>https://us.limawatch.com/</v>
@@ -35920,7 +35920,7 @@
         <v>Moana</v>
       </c>
       <c r="I66" t="str">
-        <v>2024-05-10</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J66" t="str">
         <v>https://www.magrette.com</v>
@@ -36289,7 +36289,7 @@
         <v/>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J75" t="str">
         <v>https://www.melbournewatchco.com</v>
@@ -36412,7 +36412,7 @@
         <v>37.09 Bluefin</v>
       </c>
       <c r="I78" t="str">
-        <v>2024-12-31</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J78" t="str">
         <v>https://www.ming.watch</v>
@@ -36658,7 +36658,7 @@
         <v>BALEINE – 202</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J84" t="str">
         <v>https://www.nezumistudios.com</v>
@@ -36699,7 +36699,7 @@
         <v>Himalayan Project</v>
       </c>
       <c r="I85" t="str">
-        <v>2024-04-15</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J85" t="str">
         <v>https://www.oceantoorbit.com/</v>
@@ -36904,7 +36904,7 @@
         <v>Storm Corsair</v>
       </c>
       <c r="I90" t="str">
-        <v>2024-04-06</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J90" t="str">
         <v>https://www.phoiboswatch.com</v>
@@ -37396,7 +37396,7 @@
         <v>The Fusion</v>
       </c>
       <c r="I102" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J102" t="str">
         <v>https://www.secondhour.com.au</v>
@@ -37888,7 +37888,7 @@
         <v>1918 Trench &amp; Medic</v>
       </c>
       <c r="I114" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J114" t="str">
         <v>https://www.vario.sg</v>
@@ -37970,7 +37970,7 @@
         <v/>
       </c>
       <c r="I116" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J116" t="str">
         <v>https://wancherwatch.com/</v>
@@ -38339,7 +38339,7 @@
         <v/>
       </c>
       <c r="I125" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J125" t="str">
         <v>https://www.zeroo.jp</v>
@@ -40333,7 +40333,7 @@
         <v>Fieldtimer</v>
       </c>
       <c r="I47" t="str">
-        <v>2025-11-25</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J47" t="str">
         <v>https://campwatches.com/</v>
@@ -41071,7 +41071,7 @@
         <v>Gatekeeper</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J65" t="str">
         <v>https://decima-watches.com/</v>
@@ -41317,7 +41317,7 @@
         <v>DRZ 07 Universo</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J71" t="str">
         <v>https://direnzowatches.com/</v>
@@ -41809,7 +41809,7 @@
         <v/>
       </c>
       <c r="I83" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J83" t="str">
         <v>https://englemaan.com</v>
@@ -41850,7 +41850,7 @@
         <v>Twenty-Four</v>
       </c>
       <c r="I84" t="str">
-        <v>2024-12-19</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J84" t="str">
         <v>https://erebuswatches.com/</v>
@@ -42465,7 +42465,7 @@
         <v>March 5</v>
       </c>
       <c r="I99" t="str">
-        <v>2025-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J99" t="str">
         <v>https://watchesgalo.com/</v>
@@ -42957,7 +42957,7 @@
         <v/>
       </c>
       <c r="I111" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J111" t="str">
         <v>https://halcyonwatch.com/</v>
@@ -43039,7 +43039,7 @@
         <v/>
       </c>
       <c r="I113" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J113" t="str">
         <v>https://havenwatchco.com/</v>
@@ -43367,7 +43367,7 @@
         <v>Racing 40</v>
       </c>
       <c r="I121" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J121" t="str">
         <v>https://hoffmanwatches.com/</v>
@@ -43613,7 +43613,7 @@
         <v>Aquatique GMT</v>
       </c>
       <c r="I127" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J127" t="str">
         <v>https://hultwatches.com/</v>
@@ -43982,7 +43982,7 @@
         <v>IXDAO Pilot Series</v>
       </c>
       <c r="I136" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J136" t="str">
         <v>https://ixdaowatches.com/</v>
@@ -44597,7 +44597,7 @@
         <v>Chiming Watch 2.0</v>
       </c>
       <c r="I151" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J151" t="str">
         <v>https://luckyharveywatch.com/</v>
@@ -44925,7 +44925,7 @@
         <v>Odyssey: Baja</v>
       </c>
       <c r="I159" t="str">
-        <v>2026-01-26</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J159" t="str">
         <v>https://www.marininstruments.com/</v>
@@ -44966,7 +44966,7 @@
         <v>M 6</v>
       </c>
       <c r="I160" t="str">
-        <v>2024-12-15</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J160" t="str">
         <v>https://marktimewatches.com/</v>
@@ -45335,7 +45335,7 @@
         <v>Milifortic S103</v>
       </c>
       <c r="I169" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J169" t="str">
         <v>https://miliforticwatch.com/</v>
@@ -45540,7 +45540,7 @@
         <v>MB3 TRINOVA</v>
       </c>
       <c r="I174" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J174" t="str">
         <v>https://monbrey.com/</v>
@@ -45909,7 +45909,7 @@
         <v>Vespera GMT</v>
       </c>
       <c r="I183" t="str">
-        <v>2026-03-09</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J183" t="str">
         <v>https://nadirwatches.com/</v>
@@ -46032,7 +46032,7 @@
         <v>SHIRAHAMA 2</v>
       </c>
       <c r="I186" t="str">
-        <v>2024-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J186" t="str">
         <v>https://www.namicawatches.com/</v>
@@ -46524,7 +46524,7 @@
         <v>LUNØR</v>
       </c>
       <c r="I198" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J198" t="str">
         <v>https://nordicmarineinstruments.com/</v>
@@ -47508,7 +47508,7 @@
         <v>Onward Future Field Watch</v>
       </c>
       <c r="I222" t="str">
-        <v>2024-12-31</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J222" t="str">
         <v>https://prevailwatches.com/</v>
@@ -47836,7 +47836,7 @@
         <v>Terra 38 Casablanca</v>
       </c>
       <c r="I230" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J230" t="str">
         <v>https://www.revelot.com/</v>
@@ -48779,7 +48779,7 @@
         <v>VisiLume GMT</v>
       </c>
       <c r="I253" t="str">
-        <v>2024-12-19</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J253" t="str">
         <v>https://sheffieldwatches.com/</v>
@@ -50050,7 +50050,7 @@
         <v>Daytripper Season Two</v>
       </c>
       <c r="I284" t="str">
-        <v>2024-12-19</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J284" t="str">
         <v>https://www.traffordwatchco.com/</v>
@@ -50255,7 +50255,7 @@
         <v>Adamas Aster</v>
       </c>
       <c r="I289" t="str">
-        <v>2026-01-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J289" t="str">
         <v>https://uglywatchco.com/</v>
@@ -50501,7 +50501,7 @@
         <v>Northstar N-8 'Full Lume'</v>
       </c>
       <c r="I295" t="str">
-        <v/>
+        <v>2026-04-04</v>
       </c>
       <c r="J295" t="str">
         <v>https://ventuswatches.com/</v>
@@ -50829,7 +50829,7 @@
         <v>WIC006 GMT</v>
       </c>
       <c r="I303" t="str">
-        <v>2024-10-01</v>
+        <v>2026-04-04</v>
       </c>
       <c r="J303" t="str">
         <v>https://www.wickedwatch.ch/</v>
@@ -51569,7 +51569,7 @@
         <v>Last Updated</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-04</v>
       </c>
     </row>
     <row r="3">

--- a/watch-microbrand-database.xlsx
+++ b/watch-microbrand-database.xlsx
@@ -590,7 +590,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>Tetbury</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -713,7 +713,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>Geneva</v>
       </c>
       <c r="D8">
         <v>1894</v>
@@ -836,7 +836,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C11" t="str">
-        <v>Les Brenets</v>
+        <v>Saignelégier</v>
       </c>
       <c r="D11">
         <v>1942</v>
@@ -851,10 +851,10 @@
         <v>Active</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Renaissance Squelette Cobweb</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>2019-01-01</v>
       </c>
       <c r="J11" t="str">
         <v>https://www.aerowatch.ch</v>
@@ -997,7 +997,7 @@
         <v>AIRIN</v>
       </c>
       <c r="B15" t="str">
-        <v>France</v>
+        <v>Switzerland</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -1656,7 +1656,7 @@
         <v>Germany</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>Hamburg</v>
       </c>
       <c r="D31">
         <v>1960</v>
@@ -1721,7 +1721,7 @@
         <v>https://aquastar.ch/</v>
       </c>
       <c r="K32" t="str">
-        <v/>
+        <v>aquastarwatches</v>
       </c>
       <c r="L32" t="str">
         <v>MBWDB</v>
@@ -1738,7 +1738,7 @@
         <v>France</v>
       </c>
       <c r="C33" t="str">
-        <v>Paris</v>
+        <v>Grenoble</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -1861,7 +1861,7 @@
         <v>Germany</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>Pforzheim</v>
       </c>
       <c r="D36">
         <v>1924</v>
@@ -1943,7 +1943,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>Tramelan</v>
       </c>
       <c r="D38">
         <v>1875</v>
@@ -1961,7 +1961,7 @@
         <v>M02 Special Edition Toni Art</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>2024-11-01</v>
       </c>
       <c r="J38" t="str">
         <v>https://www.armandnicolet.com</v>
@@ -2025,16 +2025,16 @@
         <v>Germany</v>
       </c>
       <c r="C40" t="str">
-        <v>Berlin</v>
+        <v>Rathenow</v>
       </c>
       <c r="D40" t="str">
         <v/>
       </c>
-      <c r="E40" t="str">
-        <v/>
-      </c>
-      <c r="F40" t="str">
-        <v/>
+      <c r="E40">
+        <v>39</v>
+      </c>
+      <c r="F40">
+        <v>10700</v>
       </c>
       <c r="G40" t="str">
         <v>Active</v>
@@ -2268,7 +2268,7 @@
         <v>Augmé</v>
       </c>
       <c r="B46" t="str">
-        <v>France</v>
+        <v>Denmark</v>
       </c>
       <c r="C46" t="str">
         <v>Paris</v>
@@ -2286,7 +2286,7 @@
         <v>Active</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>Serenity Petite</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2295,7 +2295,7 @@
         <v>https://augustberg.com/</v>
       </c>
       <c r="K46" t="str">
-        <v/>
+        <v>augustbergofficial</v>
       </c>
       <c r="L46" t="str">
         <v>existing-db</v>
@@ -2645,11 +2645,11 @@
       <c r="D55">
         <v>1903</v>
       </c>
-      <c r="E55" t="str">
-        <v/>
-      </c>
-      <c r="F55" t="str">
-        <v/>
+      <c r="E55">
+        <v>425</v>
+      </c>
+      <c r="F55">
+        <v>900</v>
       </c>
       <c r="G55" t="str">
         <v>Active</v>
@@ -2658,13 +2658,13 @@
         <v>Holland Automatic BL-3150-03</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J55" t="str">
         <v>https://www.ballast1903.com/</v>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>ballast1903</v>
       </c>
       <c r="L55" t="str">
         <v>MBWDB</v>
@@ -2845,7 +2845,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>London</v>
       </c>
       <c r="D60">
         <v>2002</v>
@@ -2886,16 +2886,16 @@
         <v>Netherlands</v>
       </c>
       <c r="C61" t="str">
-        <v>Amsterdam</v>
+        <v>Tilburg</v>
       </c>
       <c r="D61" t="str">
         <v/>
       </c>
-      <c r="E61" t="str">
-        <v/>
-      </c>
-      <c r="F61" t="str">
-        <v/>
+      <c r="E61">
+        <v>26</v>
+      </c>
+      <c r="F61">
+        <v>710</v>
       </c>
       <c r="G61" t="str">
         <v>Active</v>
@@ -2904,13 +2904,13 @@
         <v>Batavi Geograaf</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J61" t="str">
         <v>https://www.batavi-watches.com/</v>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>batavi_watches</v>
       </c>
       <c r="L61" t="str">
         <v>MBWDB</v>
@@ -2927,7 +2927,7 @@
         <v>Hong Kong</v>
       </c>
       <c r="C62" t="str">
-        <v>Kwun Tong</v>
+        <v>Hong Kong</v>
       </c>
       <c r="D62" t="str">
         <v/>
@@ -3091,7 +3091,7 @@
         <v>Italy</v>
       </c>
       <c r="C66" t="str">
-        <v>Roma</v>
+        <v>Rome</v>
       </c>
       <c r="D66">
         <v>1882</v>
@@ -3419,7 +3419,7 @@
         <v>Slovakia</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>Banská Bystrica</v>
       </c>
       <c r="D74">
         <v>2010</v>
@@ -3601,7 +3601,7 @@
         <v>MNGRA</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J78" t="str">
         <v>https://bnd-watches.com/?lang=en</v>
@@ -3665,7 +3665,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C80" t="str">
-        <v/>
+        <v>Neuchâtel</v>
       </c>
       <c r="D80" t="str">
         <v/>
@@ -3788,7 +3788,7 @@
         <v>Germany</v>
       </c>
       <c r="C83" t="str">
-        <v/>
+        <v>Königstein</v>
       </c>
       <c r="D83">
         <v>1986</v>
@@ -4154,7 +4154,7 @@
         <v>Briston</v>
       </c>
       <c r="B92" t="str">
-        <v>France</v>
+        <v>United Kingdom</v>
       </c>
       <c r="C92" t="str">
         <v>Paris</v>
@@ -4198,7 +4198,7 @@
         <v>France</v>
       </c>
       <c r="C93" t="str">
-        <v/>
+        <v>Paris</v>
       </c>
       <c r="D93">
         <v>2005</v>
@@ -4321,7 +4321,7 @@
         <v>Norway</v>
       </c>
       <c r="C96" t="str">
-        <v/>
+        <v>Oslo</v>
       </c>
       <c r="D96" t="str">
         <v/>
@@ -4690,16 +4690,16 @@
         <v>Switzerland</v>
       </c>
       <c r="C105" t="str">
-        <v>Les Breuleux</v>
+        <v>Uznach</v>
       </c>
       <c r="D105">
         <v>1858</v>
       </c>
-      <c r="E105" t="str">
-        <v/>
-      </c>
-      <c r="F105" t="str">
-        <v/>
+      <c r="E105">
+        <v>400</v>
+      </c>
+      <c r="F105">
+        <v>1200</v>
       </c>
       <c r="G105" t="str">
         <v>Active</v>
@@ -4728,7 +4728,7 @@
         <v>Celadon (Maison Celadon Watches)</v>
       </c>
       <c r="B106" t="str">
-        <v>France</v>
+        <v>China</v>
       </c>
       <c r="C106" t="str">
         <v/>
@@ -5228,11 +5228,11 @@
       <c r="D118">
         <v>2014</v>
       </c>
-      <c r="E118" t="str">
-        <v/>
-      </c>
-      <c r="F118" t="str">
-        <v/>
+      <c r="E118">
+        <v>499</v>
+      </c>
+      <c r="F118">
+        <v>2388</v>
       </c>
       <c r="G118" t="str">
         <v>Active</v>
@@ -5241,13 +5241,13 @@
         <v>Airspeed</v>
       </c>
       <c r="I118" t="str">
-        <v/>
+        <v>2021-01-01</v>
       </c>
       <c r="J118" t="str">
         <v>https://www.cjrwatches.com</v>
       </c>
       <c r="K118" t="str">
-        <v/>
+        <v>cjrwatches</v>
       </c>
       <c r="L118" t="str">
         <v>MBWDB</v>
@@ -5305,7 +5305,7 @@
         <v>Denmark</v>
       </c>
       <c r="C120" t="str">
-        <v>Copenhagen</v>
+        <v>St Andrews</v>
       </c>
       <c r="D120" t="str">
         <v/>
@@ -5540,7 +5540,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M125" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>UK-based military watch brand specializing in diver watches and vintage military-inspired timepieces. Product range includes Royal Navy style divers watches, WW2 pattern German Luftwaffe replicas, and modern tactical military watches with water resistance up to 300m.</v>
       </c>
     </row>
     <row r="126">
@@ -5592,7 +5592,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C127" t="str">
-        <v>Zurich</v>
+        <v>Geneva</v>
       </c>
       <c r="D127">
         <v>2010</v>
@@ -6852,7 +6852,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M157" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Italian watch brand featuring diver watches and neo-vintage timepieces. Collections include models like Patriota, Amalfi, and Fano with movements including automatic and mecha-quartz chronographs. Currently selling 110 watch models in stock.</v>
       </c>
     </row>
     <row r="158">
@@ -6863,7 +6863,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C158" t="str">
-        <v>Neuchâtel</v>
+        <v>Cormondrèche</v>
       </c>
       <c r="D158">
         <v>2016</v>
@@ -7032,11 +7032,11 @@
       <c r="D162">
         <v>2019</v>
       </c>
-      <c r="E162" t="str">
-        <v/>
-      </c>
-      <c r="F162" t="str">
-        <v/>
+      <c r="E162">
+        <v>528</v>
+      </c>
+      <c r="F162">
+        <v>556</v>
       </c>
       <c r="G162" t="str">
         <v>Active</v>
@@ -7045,7 +7045,7 @@
         <v>DV-02</v>
       </c>
       <c r="I162" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J162" t="str">
         <v>https://draytonwatches.com/</v>
@@ -7191,7 +7191,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C166" t="str">
-        <v/>
+        <v>Bolton</v>
       </c>
       <c r="D166">
         <v>1920</v>
@@ -7232,7 +7232,7 @@
         <v>Germany</v>
       </c>
       <c r="C167" t="str">
-        <v/>
+        <v>Hamburg</v>
       </c>
       <c r="D167">
         <v>2007</v>
@@ -7273,7 +7273,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C168" t="str">
-        <v/>
+        <v>Lugano</v>
       </c>
       <c r="D168">
         <v>2011</v>
@@ -7281,8 +7281,8 @@
       <c r="E168">
         <v>1400</v>
       </c>
-      <c r="F168" t="str">
-        <v/>
+      <c r="F168">
+        <v>1347</v>
       </c>
       <c r="G168" t="str">
         <v>Active</v>
@@ -7291,7 +7291,7 @@
         <v>A1</v>
       </c>
       <c r="I168" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J168" t="str">
         <v>https://www.dwiss.com</v>
@@ -7314,7 +7314,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C169" t="str">
-        <v/>
+        <v>London</v>
       </c>
       <c r="D169">
         <v>2013</v>
@@ -7396,7 +7396,7 @@
         <v>Italy</v>
       </c>
       <c r="C171" t="str">
-        <v>Milan, Italy</v>
+        <v>Milano</v>
       </c>
       <c r="D171">
         <v>2019</v>
@@ -7434,7 +7434,7 @@
         <v>Edmond</v>
       </c>
       <c r="B172" t="str">
-        <v>Sweden</v>
+        <v>Switzerland</v>
       </c>
       <c r="C172" t="str">
         <v/>
@@ -7724,7 +7724,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C179" t="str">
-        <v/>
+        <v>Kendal</v>
       </c>
       <c r="D179">
         <v>2012</v>
@@ -7847,7 +7847,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C182" t="str">
-        <v/>
+        <v>La Chaux de Fonds</v>
       </c>
       <c r="D182">
         <v>1948</v>
@@ -7871,7 +7871,7 @@
         <v>http://www.enicar.com/</v>
       </c>
       <c r="K182" t="str">
-        <v/>
+        <v>enicarswiss</v>
       </c>
       <c r="L182" t="str">
         <v>MBWDB</v>
@@ -8000,7 +8000,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M185" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>German watchmaker Roland Kemmner, former Fricker employee, builds custom Marine-style watches inspired by WW2 Kriegsmarine designs. Offers affordable alternatives featuring Swiss Unitas movements and 316L steel cases, sold through eBay shop Erkahund with direct commission options.</v>
       </c>
     </row>
     <row r="186">
@@ -8180,11 +8180,11 @@
       <c r="D190" t="str">
         <v/>
       </c>
-      <c r="E190" t="str">
-        <v/>
-      </c>
-      <c r="F190" t="str">
-        <v/>
+      <c r="E190">
+        <v>1057</v>
+      </c>
+      <c r="F190">
+        <v>1271</v>
       </c>
       <c r="G190" t="str">
         <v>Active</v>
@@ -8544,7 +8544,7 @@
         <v>United States</v>
       </c>
       <c r="C199" t="str">
-        <v>Indiana</v>
+        <v>Indianapolis</v>
       </c>
       <c r="D199" t="str">
         <v/>
@@ -8603,7 +8603,7 @@
         <v>FLORIJN</v>
       </c>
       <c r="I200" t="str">
-        <v/>
+        <v>2017-05-01</v>
       </c>
       <c r="J200" t="str">
         <v>https://www.blessthisstuff.com/stuff/wear/watches/florijn-watch/</v>
@@ -8913,7 +8913,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C208" t="str">
-        <v>Norwich</v>
+        <v>Norfolk</v>
       </c>
       <c r="D208" t="str">
         <v/>
@@ -9036,16 +9036,16 @@
         <v>Poland</v>
       </c>
       <c r="C211" t="str">
-        <v/>
+        <v>Szczecin</v>
       </c>
       <c r="D211" t="str">
         <v/>
       </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v/>
+      <c r="E211">
+        <v>700</v>
+      </c>
+      <c r="F211">
+        <v>1000</v>
       </c>
       <c r="G211" t="str">
         <v>Active</v>
@@ -9115,28 +9115,28 @@
         <v>Giorgio Martino</v>
       </c>
       <c r="B213" t="str">
-        <v>Italy</v>
+        <v>United Kingdom</v>
       </c>
       <c r="C213" t="str">
-        <v/>
-      </c>
-      <c r="D213" t="str">
-        <v/>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v/>
+        <v>London</v>
+      </c>
+      <c r="D213">
+        <v>2020</v>
+      </c>
+      <c r="E213">
+        <v>52</v>
+      </c>
+      <c r="F213">
+        <v>107</v>
       </c>
       <c r="G213" t="str">
         <v>Active</v>
       </c>
       <c r="H213" t="str">
-        <v/>
+        <v>VEROSTY GX 650</v>
       </c>
       <c r="I213" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J213" t="str">
         <v>https://giorgiomartino.club/</v>
@@ -9530,29 +9530,29 @@
       <c r="C223" t="str">
         <v>Frankfurt am Main</v>
       </c>
-      <c r="D223" t="str">
-        <v/>
-      </c>
-      <c r="E223" t="str">
-        <v/>
-      </c>
-      <c r="F223" t="str">
-        <v/>
+      <c r="D223">
+        <v>1865</v>
+      </c>
+      <c r="E223">
+        <v>1800</v>
+      </c>
+      <c r="F223">
+        <v>2500</v>
       </c>
       <c r="G223" t="str">
         <v>Active</v>
       </c>
       <c r="H223" t="str">
-        <v/>
+        <v>Deepwave Whitewater</v>
       </c>
       <c r="I223" t="str">
-        <v/>
+        <v>2024-09-03</v>
       </c>
       <c r="J223" t="str">
         <v>https://www.guinand-uhren.de/home-en.html</v>
       </c>
       <c r="K223" t="str">
-        <v/>
+        <v>guinandwatches</v>
       </c>
       <c r="L223" t="str">
         <v>MBWDB</v>
@@ -9628,7 +9628,7 @@
         <v>NAVI S</v>
       </c>
       <c r="I225" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J225" t="str">
         <v>https://gyavius.com/about</v>
@@ -9651,7 +9651,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C226" t="str">
-        <v/>
+        <v>Schaffhausen</v>
       </c>
       <c r="D226">
         <v>1828</v>
@@ -9856,7 +9856,7 @@
         <v>Sweden</v>
       </c>
       <c r="C231" t="str">
-        <v>Svängsta</v>
+        <v>Sollentuna</v>
       </c>
       <c r="D231">
         <v>1887</v>
@@ -9938,7 +9938,7 @@
         <v>Germany</v>
       </c>
       <c r="C233" t="str">
-        <v/>
+        <v>Schonachbach</v>
       </c>
       <c r="D233">
         <v>1882</v>
@@ -10315,8 +10315,8 @@
       <c r="E242">
         <v>360</v>
       </c>
-      <c r="F242" t="str">
-        <v/>
+      <c r="F242">
+        <v>550</v>
       </c>
       <c r="G242" t="str">
         <v>Active</v>
@@ -10348,7 +10348,7 @@
         <v>Netherlands</v>
       </c>
       <c r="C243" t="str">
-        <v/>
+        <v>Delft</v>
       </c>
       <c r="D243">
         <v>2016</v>
@@ -10430,7 +10430,7 @@
         <v>Netherlands</v>
       </c>
       <c r="C245" t="str">
-        <v>Heerde, Netherlands</v>
+        <v>Heerde</v>
       </c>
       <c r="D245">
         <v>2014</v>
@@ -10473,23 +10473,23 @@
       <c r="C246" t="str">
         <v>Besançon</v>
       </c>
-      <c r="D246" t="str">
-        <v/>
-      </c>
-      <c r="E246" t="str">
-        <v/>
-      </c>
-      <c r="F246" t="str">
-        <v/>
+      <c r="D246">
+        <v>1964</v>
+      </c>
+      <c r="E246">
+        <v>699</v>
+      </c>
+      <c r="F246">
+        <v>1090</v>
       </c>
       <c r="G246" t="str">
         <v>Active</v>
       </c>
       <c r="H246" t="str">
-        <v/>
+        <v>HD6.1 Chronographe</v>
       </c>
       <c r="I246" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J246" t="str">
         <v>https://www.humbert-droz.fr/en/</v>
@@ -10758,7 +10758,7 @@
         <v>Germany</v>
       </c>
       <c r="C253" t="str">
-        <v/>
+        <v>Hamburg</v>
       </c>
       <c r="D253">
         <v>2014</v>
@@ -10796,7 +10796,7 @@
         <v>Isotope</v>
       </c>
       <c r="B254" t="str">
-        <v>England</v>
+        <v>United Kingdom</v>
       </c>
       <c r="C254" t="str">
         <v>Henfield</v>
@@ -10858,7 +10858,7 @@
         <v>New Series</v>
       </c>
       <c r="I255" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J255" t="str">
         <v>https://www.jacobjensen.com</v>
@@ -11009,26 +11009,26 @@
       <c r="D259" t="str">
         <v/>
       </c>
-      <c r="E259" t="str">
-        <v/>
-      </c>
-      <c r="F259" t="str">
-        <v/>
+      <c r="E259">
+        <v>230</v>
+      </c>
+      <c r="F259">
+        <v>390</v>
       </c>
       <c r="G259" t="str">
         <v>Active</v>
       </c>
       <c r="H259" t="str">
-        <v/>
+        <v>Rally Automatic</v>
       </c>
       <c r="I259" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J259" t="str">
         <v>https://mccabewatches.com/</v>
       </c>
       <c r="K259" t="str">
-        <v/>
+        <v>mccabewatches</v>
       </c>
       <c r="L259" t="str">
         <v>MBWDB</v>
@@ -11045,7 +11045,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C260" t="str">
-        <v/>
+        <v>Grenchen</v>
       </c>
       <c r="D260">
         <v>1992</v>
@@ -11129,14 +11129,14 @@
       <c r="C262" t="str">
         <v/>
       </c>
-      <c r="D262" t="str">
-        <v/>
-      </c>
-      <c r="E262" t="str">
-        <v/>
-      </c>
-      <c r="F262" t="str">
-        <v/>
+      <c r="D262">
+        <v>2012</v>
+      </c>
+      <c r="E262">
+        <v>195</v>
+      </c>
+      <c r="F262">
+        <v>495</v>
       </c>
       <c r="G262" t="str">
         <v>Active</v>
@@ -11151,7 +11151,7 @@
         <v>https://www.jorggrey.com</v>
       </c>
       <c r="K262" t="str">
-        <v/>
+        <v>jorggreyofficial</v>
       </c>
       <c r="L262" t="str">
         <v>MBWDB</v>
@@ -11211,8 +11211,8 @@
       <c r="C264" t="str">
         <v>Reykjavik</v>
       </c>
-      <c r="D264" t="str">
-        <v/>
+      <c r="D264">
+        <v>2004</v>
       </c>
       <c r="E264" t="str">
         <v/>
@@ -11224,7 +11224,7 @@
         <v>Active</v>
       </c>
       <c r="H264" t="str">
-        <v/>
+        <v>SIF Protector Special Edition</v>
       </c>
       <c r="I264" t="str">
         <v>2026-04-04</v>
@@ -11233,7 +11233,7 @@
         <v>https://www.jswatch.com</v>
       </c>
       <c r="K264" t="str">
-        <v/>
+        <v>jswatch</v>
       </c>
       <c r="L264" t="str">
         <v>MBWDB</v>
@@ -11291,7 +11291,7 @@
         <v>Germany</v>
       </c>
       <c r="C266" t="str">
-        <v/>
+        <v>Schramberg</v>
       </c>
       <c r="D266">
         <v>1897</v>
@@ -11370,7 +11370,7 @@
         <v>K.Grun &amp; Sohne</v>
       </c>
       <c r="B268" t="str">
-        <v>Switzerland</v>
+        <v>United Kingdom</v>
       </c>
       <c r="C268" t="str">
         <v>Surrey</v>
@@ -11501,11 +11501,11 @@
       <c r="D271" t="str">
         <v/>
       </c>
-      <c r="E271" t="str">
-        <v/>
-      </c>
-      <c r="F271" t="str">
-        <v/>
+      <c r="E271">
+        <v>399</v>
+      </c>
+      <c r="F271">
+        <v>399</v>
       </c>
       <c r="G271" t="str">
         <v>Active</v>
@@ -11514,13 +11514,13 @@
         <v>Baltic Shield</v>
       </c>
       <c r="I271" t="str">
-        <v/>
+        <v>2022-12-31</v>
       </c>
       <c r="J271" t="str">
         <v>https://www.karlskronawatch.com/</v>
       </c>
       <c r="K271" t="str">
-        <v/>
+        <v>karlskronawatch</v>
       </c>
       <c r="L271" t="str">
         <v>MBWDB</v>
@@ -11575,7 +11575,7 @@
         <v>Kazimon</v>
       </c>
       <c r="B273" t="str">
-        <v>Germany</v>
+        <v>Switzerland</v>
       </c>
       <c r="C273" t="str">
         <v>Steinhausen</v>
@@ -11952,8 +11952,8 @@
       <c r="D282">
         <v>2020</v>
       </c>
-      <c r="E282" t="str">
-        <v/>
+      <c r="E282">
+        <v>2500</v>
       </c>
       <c r="F282">
         <v>152352</v>
@@ -11971,7 +11971,7 @@
         <v>https://www.krossstudio.com</v>
       </c>
       <c r="K282" t="str">
-        <v/>
+        <v>kross_studio</v>
       </c>
       <c r="L282" t="str">
         <v>existing-db</v>
@@ -12070,7 +12070,7 @@
         <v>Germany</v>
       </c>
       <c r="C285" t="str">
-        <v/>
+        <v>Pforzheim</v>
       </c>
       <c r="D285">
         <v>1925</v>
@@ -12152,7 +12152,7 @@
         <v>Germany</v>
       </c>
       <c r="C287" t="str">
-        <v>Dresden</v>
+        <v>Saxony</v>
       </c>
       <c r="D287" t="str">
         <v/>
@@ -12428,7 +12428,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M293" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Le Marquand is a Swiss watchmaker based in Bulle, operating under parent company MASTER TIMEKEEPER SA (MTK SA), which merged the André Le Marquand watch company with Side Watch. The brand designs and manufactures watches and watch components for other prestigious labels.</v>
       </c>
     </row>
     <row r="294">
@@ -12685,7 +12685,7 @@
         <v>Italy</v>
       </c>
       <c r="C300" t="str">
-        <v>Elba Island, Italy</v>
+        <v>Marina di Campo</v>
       </c>
       <c r="D300">
         <v>1988</v>
@@ -12892,14 +12892,14 @@
       <c r="C305" t="str">
         <v/>
       </c>
-      <c r="D305" t="str">
-        <v/>
-      </c>
-      <c r="E305" t="str">
-        <v/>
-      </c>
-      <c r="F305" t="str">
-        <v/>
+      <c r="D305">
+        <v>2015</v>
+      </c>
+      <c r="E305">
+        <v>400</v>
+      </c>
+      <c r="F305">
+        <v>1200</v>
       </c>
       <c r="G305" t="str">
         <v>Active</v>
@@ -12914,7 +12914,7 @@
         <v>https://www.louisxvi.de</v>
       </c>
       <c r="K305" t="str">
-        <v/>
+        <v>louisxvi_watches</v>
       </c>
       <c r="L305" t="str">
         <v>MBWDB</v>
@@ -13084,7 +13084,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M309" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>LWC Services is an independent luxury watch service centre based in North Yorkshire, founded by Charlie Walker with over 10 years of industry experience. Specializes in servicing and restoration of Swiss watches including Rolex, Patek Philippe, Audemars Piguet, and Omega. Operates as a boutique buying and servicing experience with trained watchmakers.</v>
       </c>
     </row>
     <row r="310">
@@ -13218,7 +13218,7 @@
         <v>France</v>
       </c>
       <c r="C313" t="str">
-        <v>Paris</v>
+        <v>Reims</v>
       </c>
       <c r="D313" t="str">
         <v/>
@@ -13259,7 +13259,7 @@
         <v>France</v>
       </c>
       <c r="C314" t="str">
-        <v>Paris</v>
+        <v>Lyon</v>
       </c>
       <c r="D314" t="str">
         <v/>
@@ -13423,7 +13423,7 @@
         <v>Germany</v>
       </c>
       <c r="C318" t="str">
-        <v/>
+        <v>Hamburg</v>
       </c>
       <c r="D318">
         <v>2014</v>
@@ -13464,7 +13464,7 @@
         <v>Italy</v>
       </c>
       <c r="C319" t="str">
-        <v>Asti, Italy</v>
+        <v>Asti</v>
       </c>
       <c r="D319" t="str">
         <v/>
@@ -13479,7 +13479,7 @@
         <v>Active</v>
       </c>
       <c r="H319" t="str">
-        <v/>
+        <v>Lunar day</v>
       </c>
       <c r="I319" t="str">
         <v/>
@@ -13488,7 +13488,7 @@
         <v>https://www.marcdarno.com</v>
       </c>
       <c r="K319" t="str">
-        <v/>
+        <v>marcdarno_official</v>
       </c>
       <c r="L319" t="str">
         <v>existing-db</v>
@@ -13710,7 +13710,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C325" t="str">
-        <v/>
+        <v>London</v>
       </c>
       <c r="D325">
         <v>2015</v>
@@ -13956,7 +13956,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C331" t="str">
-        <v/>
+        <v>Geneva</v>
       </c>
       <c r="D331">
         <v>1886</v>
@@ -14094,7 +14094,7 @@
         <v>Active</v>
       </c>
       <c r="H334" t="str">
-        <v/>
+        <v>ZÜRI-DATE</v>
       </c>
       <c r="I334" t="str">
         <v>2024-01-01</v>
@@ -14325,7 +14325,7 @@
         <v>France</v>
       </c>
       <c r="C340" t="str">
-        <v>Toulouse</v>
+        <v>Bordeaux</v>
       </c>
       <c r="D340" t="str">
         <v/>
@@ -14366,7 +14366,7 @@
         <v>Germany</v>
       </c>
       <c r="C341" t="str">
-        <v/>
+        <v>Münster</v>
       </c>
       <c r="D341">
         <v>2001</v>
@@ -14571,7 +14571,7 @@
         <v>China</v>
       </c>
       <c r="C346" t="str">
-        <v>Pforzheim</v>
+        <v>Beijing</v>
       </c>
       <c r="D346" t="str">
         <v/>
@@ -14650,10 +14650,10 @@
         <v>Micromilspec</v>
       </c>
       <c r="B348" t="str">
-        <v>Switzerland</v>
+        <v>Norway</v>
       </c>
       <c r="C348" t="str">
-        <v>Paris</v>
+        <v>Oslo</v>
       </c>
       <c r="D348" t="str">
         <v/>
@@ -14873,7 +14873,7 @@
         <v>Active</v>
       </c>
       <c r="H353" t="str">
-        <v/>
+        <v>Moduco (First Collection)</v>
       </c>
       <c r="I353" t="str">
         <v>2018-01-24</v>
@@ -15872,7 +15872,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M377" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Dutch watch brand designed in Amsterdam and made in Europe. Known for the NOWATCH, described as the world's first Awareable analog watch that tracks nervous system health via Reactivity Monitor technology. Offers two main collections: NOWATCH B (comfort-focused) and NOWATCH X (curated craftsmanship).</v>
       </c>
     </row>
     <row r="378">
@@ -16021,10 +16021,10 @@
         <v>Active</v>
       </c>
       <c r="H381" t="str">
-        <v/>
+        <v>Guardian Automatic 36mm</v>
       </c>
       <c r="I381" t="str">
-        <v/>
+        <v>2024-12-19</v>
       </c>
       <c r="J381" t="str">
         <v>https://nordgreen.com/en-us</v>
@@ -16129,7 +16129,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C384" t="str">
-        <v>Bologna</v>
+        <v>La Neuveville</v>
       </c>
       <c r="D384">
         <v>1985</v>
@@ -16252,7 +16252,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C387" t="str">
-        <v/>
+        <v>London</v>
       </c>
       <c r="D387" t="str">
         <v/>
@@ -16298,11 +16298,11 @@
       <c r="D388">
         <v>2019</v>
       </c>
-      <c r="E388" t="str">
-        <v/>
-      </c>
-      <c r="F388" t="str">
-        <v/>
+      <c r="E388">
+        <v>655</v>
+      </c>
+      <c r="F388">
+        <v>1030</v>
       </c>
       <c r="G388" t="str">
         <v>Active</v>
@@ -16580,7 +16580,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C395" t="str">
-        <v>Mold</v>
+        <v>Wales</v>
       </c>
       <c r="D395">
         <v>2024</v>
@@ -16700,7 +16700,7 @@
         <v>Palmos</v>
       </c>
       <c r="B398" t="str">
-        <v>United Kingdom</v>
+        <v>Switzerland</v>
       </c>
       <c r="C398" t="str">
         <v>London</v>
@@ -16990,7 +16990,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C405" t="str">
-        <v>La Chaux-de-Fonds</v>
+        <v>Vallée de Joux</v>
       </c>
       <c r="D405">
         <v>2004</v>
@@ -17008,7 +17008,7 @@
         <v>Grandcliff 1004</v>
       </c>
       <c r="I405" t="str">
-        <v/>
+        <v>2024-11-01</v>
       </c>
       <c r="J405" t="str">
         <v>https://www.pierrederoche.com</v>
@@ -17277,7 +17277,7 @@
         <v>Finland</v>
       </c>
       <c r="C412" t="str">
-        <v>Jänsä</v>
+        <v>Joensuu</v>
       </c>
       <c r="D412" t="str">
         <v/>
@@ -17400,7 +17400,7 @@
         <v>Czech Republic</v>
       </c>
       <c r="C415" t="str">
-        <v/>
+        <v>Frýdek-Místek</v>
       </c>
       <c r="D415">
         <v>1949</v>
@@ -17692,11 +17692,11 @@
       <c r="D422" t="str">
         <v/>
       </c>
-      <c r="E422" t="str">
-        <v/>
-      </c>
-      <c r="F422" t="str">
-        <v/>
+      <c r="E422">
+        <v>22</v>
+      </c>
+      <c r="F422">
+        <v>33</v>
       </c>
       <c r="G422" t="str">
         <v>Active</v>
@@ -17848,7 +17848,7 @@
         <v>REC Watches</v>
       </c>
       <c r="B426" t="str">
-        <v>United Kingdom</v>
+        <v>Denmark</v>
       </c>
       <c r="C426" t="str">
         <v/>
@@ -17963,7 +17963,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M428" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Reloj.es is a Spanish watch retailer specializing in men's watches (Relojes Para Hombres). Part of Holland Watch Group B.V., the site operates as a multi-brand distributor carrying 70+ watch brands rather than as an independent watch manufacturer.</v>
       </c>
     </row>
     <row r="429">
@@ -18184,17 +18184,17 @@
       <c r="D434" t="str">
         <v/>
       </c>
-      <c r="E434" t="str">
-        <v/>
-      </c>
-      <c r="F434" t="str">
-        <v/>
+      <c r="E434">
+        <v>302</v>
+      </c>
+      <c r="F434">
+        <v>1670</v>
       </c>
       <c r="G434" t="str">
         <v>Active</v>
       </c>
       <c r="H434" t="str">
-        <v/>
+        <v>CHAPTER 3</v>
       </c>
       <c r="I434" t="str">
         <v/>
@@ -18203,7 +18203,7 @@
         <v>https://riskers-watches.com/</v>
       </c>
       <c r="K434" t="str">
-        <v/>
+        <v>riskers_watches</v>
       </c>
       <c r="L434" t="str">
         <v>MBWDB</v>
@@ -18425,7 +18425,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C440" t="str">
-        <v/>
+        <v>La Chaux-de-Fonds</v>
       </c>
       <c r="D440">
         <v>1895</v>
@@ -18712,7 +18712,7 @@
         <v>Italy</v>
       </c>
       <c r="C447" t="str">
-        <v/>
+        <v>Florence</v>
       </c>
       <c r="D447">
         <v>1927</v>
@@ -18835,7 +18835,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C450" t="str">
-        <v>Le Locle</v>
+        <v>Alle</v>
       </c>
       <c r="D450" t="str">
         <v/>
@@ -18917,7 +18917,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C452" t="str">
-        <v/>
+        <v>London</v>
       </c>
       <c r="D452">
         <v>2014</v>
@@ -19250,11 +19250,11 @@
       <c r="D460">
         <v>2019</v>
       </c>
-      <c r="E460" t="str">
-        <v/>
-      </c>
-      <c r="F460" t="str">
-        <v/>
+      <c r="E460">
+        <v>400</v>
+      </c>
+      <c r="F460">
+        <v>800</v>
       </c>
       <c r="G460" t="str">
         <v>Active</v>
@@ -19269,7 +19269,7 @@
         <v>https://www.serica.watch</v>
       </c>
       <c r="K460" t="str">
-        <v/>
+        <v>serica_watches</v>
       </c>
       <c r="L460" t="str">
         <v>existing-db</v>
@@ -19491,7 +19491,7 @@
         <v>Germany</v>
       </c>
       <c r="C466" t="str">
-        <v>Frankfurt</v>
+        <v>Frankfurt am Main</v>
       </c>
       <c r="D466">
         <v>1961</v>
@@ -19767,7 +19767,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M472" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Swedish watch brand exclusively dedicated to rectangular and square case watches. Offers four main collections: Legacy (3-year battery), Nostalgia (11-year battery), Momentum (self-winding), and Amorous (self-winding). Backed by 10-year warranty and available in multiple case finishes and dial colors.</v>
       </c>
     </row>
     <row r="473">
@@ -19901,7 +19901,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C476" t="str">
-        <v>Neuchâtel</v>
+        <v>Geneva</v>
       </c>
       <c r="D476">
         <v>2002</v>
@@ -20062,10 +20062,10 @@
         <v>Steinhart</v>
       </c>
       <c r="B480" t="str">
-        <v>Switzerland</v>
+        <v>Germany</v>
       </c>
       <c r="C480" t="str">
-        <v/>
+        <v>Hamburg</v>
       </c>
       <c r="D480">
         <v>2001</v>
@@ -20188,7 +20188,7 @@
         <v>Germany</v>
       </c>
       <c r="C483" t="str">
-        <v/>
+        <v>Pforzheim</v>
       </c>
       <c r="D483">
         <v>1927</v>
@@ -20431,7 +20431,7 @@
         <v>Subdelta</v>
       </c>
       <c r="B489" t="str">
-        <v>Germany</v>
+        <v>Netherlands</v>
       </c>
       <c r="C489" t="str">
         <v>Hengelo</v>
@@ -20721,7 +20721,7 @@
         <v>United Kingdom</v>
       </c>
       <c r="C496" t="str">
-        <v>Southwell</v>
+        <v>London</v>
       </c>
       <c r="D496" t="str">
         <v/>
@@ -20759,10 +20759,10 @@
         <v>Techne Instruments</v>
       </c>
       <c r="B497" t="str">
-        <v>Sweden</v>
+        <v>United States</v>
       </c>
       <c r="C497" t="str">
-        <v/>
+        <v>Berkeley</v>
       </c>
       <c r="D497">
         <v>2007</v>
@@ -20967,7 +20967,7 @@
         <v>Germany</v>
       </c>
       <c r="C502" t="str">
-        <v/>
+        <v>Munich</v>
       </c>
       <c r="D502">
         <v>2004</v>
@@ -21054,11 +21054,11 @@
       <c r="D504" t="str">
         <v/>
       </c>
-      <c r="E504" t="str">
-        <v/>
-      </c>
-      <c r="F504" t="str">
-        <v/>
+      <c r="E504">
+        <v>1015</v>
+      </c>
+      <c r="F504">
+        <v>1585</v>
       </c>
       <c r="G504" t="str">
         <v>Active</v>
@@ -21073,7 +21073,7 @@
         <v>https://timeless-watch.ch/</v>
       </c>
       <c r="K504" t="str">
-        <v/>
+        <v>timeless.swiss.watch</v>
       </c>
       <c r="L504" t="str">
         <v>MBWDB</v>
@@ -21087,7 +21087,7 @@
         <v>Tissel</v>
       </c>
       <c r="B505" t="str">
-        <v>South Korea</v>
+        <v>Czech Republic</v>
       </c>
       <c r="C505" t="str">
         <v/>
@@ -21128,7 +21128,7 @@
         <v>Titus Watches</v>
       </c>
       <c r="B506" t="str">
-        <v>Switzerland</v>
+        <v>Hong Kong</v>
       </c>
       <c r="C506" t="str">
         <v/>
@@ -21272,7 +21272,7 @@
         <v>P96 OdP Color</v>
       </c>
       <c r="I509" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J509" t="str">
         <v>https://www.traser.ch</v>
@@ -21295,7 +21295,7 @@
         <v>Germany</v>
       </c>
       <c r="C510" t="str">
-        <v/>
+        <v>Hamburg</v>
       </c>
       <c r="D510">
         <v>2014</v>
@@ -21459,16 +21459,16 @@
         <v>Germany</v>
       </c>
       <c r="C514" t="str">
-        <v>Evanston</v>
-      </c>
-      <c r="D514" t="str">
-        <v/>
-      </c>
-      <c r="E514" t="str">
-        <v/>
-      </c>
-      <c r="F514" t="str">
-        <v/>
+        <v>Munich</v>
+      </c>
+      <c r="D514">
+        <v>1828</v>
+      </c>
+      <c r="E514">
+        <v>289</v>
+      </c>
+      <c r="F514">
+        <v>2265</v>
       </c>
       <c r="G514" t="str">
         <v>Active</v>
@@ -21483,7 +21483,7 @@
         <v>https://tufinawatches.com/</v>
       </c>
       <c r="K514" t="str">
-        <v/>
+        <v>tufina_watches</v>
       </c>
       <c r="L514" t="str">
         <v>MBWDB</v>
@@ -21770,7 +21770,7 @@
         <v>https://ugolinimeccanicawatches.com/</v>
       </c>
       <c r="K521" t="str">
-        <v/>
+        <v>ugolinimeccanicawatches</v>
       </c>
       <c r="L521" t="str">
         <v>MBWDB</v>
@@ -21787,7 +21787,7 @@
         <v>Hong Kong</v>
       </c>
       <c r="C522" t="str">
-        <v/>
+        <v>Hong Kong</v>
       </c>
       <c r="D522">
         <v>2014</v>
@@ -21828,7 +21828,7 @@
         <v>Italy</v>
       </c>
       <c r="C523" t="str">
-        <v/>
+        <v>Milan</v>
       </c>
       <c r="D523">
         <v>2015</v>
@@ -21869,7 +21869,7 @@
         <v>Germany</v>
       </c>
       <c r="C524" t="str">
-        <v>Munich</v>
+        <v>Holzkirchen</v>
       </c>
       <c r="D524" t="str">
         <v/>
@@ -21915,11 +21915,11 @@
       <c r="D525" t="str">
         <v/>
       </c>
-      <c r="E525" t="str">
-        <v/>
-      </c>
-      <c r="F525" t="str">
-        <v/>
+      <c r="E525">
+        <v>349</v>
+      </c>
+      <c r="F525">
+        <v>809</v>
       </c>
       <c r="G525" t="str">
         <v>Active</v>
@@ -21934,7 +21934,7 @@
         <v>https://www.valhallaofnorway.no/</v>
       </c>
       <c r="K525" t="str">
-        <v/>
+        <v>valhallawatches</v>
       </c>
       <c r="L525" t="str">
         <v>MBWDB</v>
@@ -22637,7 +22637,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M542" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Norwegian watch brand creating timeless wristwatches inspired by Norwegian nature, culture and history. Designs are made in Norway with Swiss movements. Collections include Tandberg, URÆD GMT, Runde, and special editions like Norway Chess collaboration.</v>
       </c>
     </row>
     <row r="543">
@@ -22689,7 +22689,7 @@
         <v>Lithuania</v>
       </c>
       <c r="C544" t="str">
-        <v/>
+        <v>Vilnius</v>
       </c>
       <c r="D544">
         <v>2003</v>
@@ -22730,7 +22730,7 @@
         <v>Russia</v>
       </c>
       <c r="C545" t="str">
-        <v/>
+        <v>Chistopol</v>
       </c>
       <c r="D545" t="str">
         <v/>
@@ -22738,8 +22738,8 @@
       <c r="E545" t="str">
         <v/>
       </c>
-      <c r="F545" t="str">
-        <v/>
+      <c r="F545">
+        <v>606</v>
       </c>
       <c r="G545" t="str">
         <v>Active</v>
@@ -22894,7 +22894,7 @@
         <v>United States</v>
       </c>
       <c r="C549" t="str">
-        <v/>
+        <v>Meriden</v>
       </c>
       <c r="D549">
         <v>1978</v>
@@ -22912,7 +22912,7 @@
         <v>Heritage Sportline</v>
       </c>
       <c r="I549" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J549" t="str">
         <v>https://delraywatch.com/waldan-international-1/</v>
@@ -22935,7 +22935,7 @@
         <v>Poland</v>
       </c>
       <c r="C550" t="str">
-        <v/>
+        <v>Warsaw</v>
       </c>
       <c r="D550" t="str">
         <v/>
@@ -23304,7 +23304,7 @@
         <v>France</v>
       </c>
       <c r="C559" t="str">
-        <v/>
+        <v>Morteau</v>
       </c>
       <c r="D559">
         <v>1948</v>
@@ -23629,7 +23629,7 @@
         <v>Zlatoust</v>
       </c>
       <c r="B567" t="str">
-        <v>Soviet Union</v>
+        <v>Russia</v>
       </c>
       <c r="C567" t="str">
         <v>Zlatoust</v>
@@ -23675,8 +23675,8 @@
       <c r="C568" t="str">
         <v>Zlatoust</v>
       </c>
-      <c r="D568" t="str">
-        <v/>
+      <c r="D568">
+        <v>1947</v>
       </c>
       <c r="E568" t="str">
         <v/>
@@ -24221,7 +24221,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M11" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>No homepage content provided for data extraction. Unable to verify current status or details for ARETHUSA Watch Company.</v>
       </c>
     </row>
     <row r="12">
@@ -24847,16 +24847,16 @@
         <v>United States</v>
       </c>
       <c r="C27" t="str">
-        <v>Bern</v>
+        <v>Denver</v>
       </c>
       <c r="D27">
         <v>2016</v>
       </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27" t="str">
-        <v/>
+      <c r="E27">
+        <v>495</v>
+      </c>
+      <c r="F27">
+        <v>695</v>
       </c>
       <c r="G27" t="str">
         <v>Active</v>
@@ -24871,7 +24871,7 @@
         <v>https://bernwatches.com</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>bernwatch</v>
       </c>
       <c r="L27" t="str">
         <v>MBWDB</v>
@@ -24929,7 +24929,7 @@
         <v>United States</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>Cuyahoga Falls</v>
       </c>
       <c r="D29">
         <v>1990</v>
@@ -25328,7 +25328,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M38" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>California Watch Co. designs timepieces with attention to dimensional details including concave subdials, raised indices, and domed dials. The brand offers diverse collections including PCH Driver Jump Hour, Venice Beach Digital, and chronograph models. Currently carries 42 products ranging from $79.99 to $149.99.</v>
       </c>
     </row>
     <row r="39">
@@ -25503,7 +25503,7 @@
         <v>Chile</v>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>Valparaíso</v>
       </c>
       <c r="D43" t="str">
         <v/>
@@ -25585,7 +25585,7 @@
         <v>United States</v>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>Denver</v>
       </c>
       <c r="D45">
         <v>2009</v>
@@ -25623,19 +25623,19 @@
         <v>Chase-Durer Watch Company</v>
       </c>
       <c r="B46" t="str">
-        <v>USA</v>
+        <v>United States</v>
       </c>
       <c r="C46" t="str">
-        <v>Los Angeles, California</v>
-      </c>
-      <c r="D46" t="str">
-        <v/>
-      </c>
-      <c r="E46" t="str">
-        <v/>
-      </c>
-      <c r="F46" t="str">
-        <v/>
+        <v>Houston</v>
+      </c>
+      <c r="D46">
+        <v>1988</v>
+      </c>
+      <c r="E46">
+        <v>1200</v>
+      </c>
+      <c r="F46">
+        <v>2800</v>
       </c>
       <c r="G46" t="str">
         <v>Active</v>
@@ -25650,7 +25650,7 @@
         <v>https://www.chase-durer.com</v>
       </c>
       <c r="K46" t="str">
-        <v/>
+        <v>chasedurer</v>
       </c>
       <c r="L46" t="str">
         <v>existing-db</v>
@@ -25669,8 +25669,8 @@
       <c r="C47" t="str">
         <v>Cincinnati</v>
       </c>
-      <c r="D47" t="str">
-        <v/>
+      <c r="D47">
+        <v>1869</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -25808,7 +25808,7 @@
         <v>MILLENIUM</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J50" t="str">
         <v>https://www.crotonwatch.com</v>
@@ -25915,14 +25915,14 @@
       <c r="C53" t="str">
         <v>Los Angeles</v>
       </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
-      <c r="F53" t="str">
-        <v/>
+      <c r="D53">
+        <v>2009</v>
+      </c>
+      <c r="E53">
+        <v>5000</v>
+      </c>
+      <c r="F53">
+        <v>50000</v>
       </c>
       <c r="G53" t="str">
         <v>Active</v>
@@ -26010,10 +26010,10 @@
         <v>Active</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>Seiko Yachtmaster Stealth Mod</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>2024-07-17</v>
       </c>
       <c r="J55" t="str">
         <v>https://www.dagazwatch.com</v>
@@ -26077,7 +26077,7 @@
         <v>United States</v>
       </c>
       <c r="C57" t="str">
-        <v>Dallas</v>
+        <v>Texas</v>
       </c>
       <c r="D57" t="str">
         <v/>
@@ -26118,7 +26118,7 @@
         <v>United States</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>New York</v>
       </c>
       <c r="D58">
         <v>2007</v>
@@ -26279,10 +26279,10 @@
         <v>Draken</v>
       </c>
       <c r="B62" t="str">
-        <v>United States</v>
+        <v>New Zealand</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>Waipu</v>
       </c>
       <c r="D62" t="str">
         <v/>
@@ -26435,7 +26435,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M65" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Duxot was a watch brand under Dartmouth Brands in the United States. Limited reliable information available in training data. Brand appears to be inactive or defunct.</v>
       </c>
     </row>
     <row r="66">
@@ -26446,7 +26446,7 @@
         <v>United States</v>
       </c>
       <c r="C66" t="str">
-        <v>Hagerstown</v>
+        <v>Baltimore</v>
       </c>
       <c r="D66" t="str">
         <v/>
@@ -26569,7 +26569,7 @@
         <v>United States</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>San Francisco</v>
       </c>
       <c r="D69">
         <v>2012</v>
@@ -26774,7 +26774,7 @@
         <v>United States</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>Antelope</v>
       </c>
       <c r="D74" t="str">
         <v/>
@@ -26804,7 +26804,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M74" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Famine Studios is a US-based brand based in Antelope, California. The company primarily sells apparel and accessories, with limited watch offerings including the Moneyman Watch. Brand is currently active with an ongoing sweepstakes promotion (September-December 2025).</v>
       </c>
     </row>
     <row r="75">
@@ -26815,7 +26815,7 @@
         <v>United States</v>
       </c>
       <c r="C75" t="str">
-        <v>Elmhurst</v>
+        <v>Chicago</v>
       </c>
       <c r="D75" t="str">
         <v/>
@@ -27158,7 +27158,7 @@
         <v>Active</v>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>Windmaster</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -27230,11 +27230,11 @@
       <c r="D85" t="str">
         <v/>
       </c>
-      <c r="E85" t="str">
-        <v/>
-      </c>
-      <c r="F85" t="str">
-        <v/>
+      <c r="E85">
+        <v>864</v>
+      </c>
+      <c r="F85">
+        <v>2227</v>
       </c>
       <c r="G85" t="str">
         <v>Active</v>
@@ -27249,7 +27249,7 @@
         <v>https://grandeur-usa.com/</v>
       </c>
       <c r="K85" t="str">
-        <v/>
+        <v>grandeur</v>
       </c>
       <c r="L85" t="str">
         <v>MBWDB</v>
@@ -27430,7 +27430,7 @@
         <v>Canada</v>
       </c>
       <c r="C90" t="str">
-        <v/>
+        <v>Toronto</v>
       </c>
       <c r="D90">
         <v>2015</v>
@@ -27473,14 +27473,14 @@
       <c r="C91" t="str">
         <v/>
       </c>
-      <c r="D91" t="str">
-        <v/>
-      </c>
-      <c r="E91" t="str">
-        <v/>
-      </c>
-      <c r="F91" t="str">
-        <v/>
+      <c r="D91">
+        <v>2012</v>
+      </c>
+      <c r="E91">
+        <v>295</v>
+      </c>
+      <c r="F91">
+        <v>595</v>
       </c>
       <c r="G91" t="str">
         <v>Active</v>
@@ -27495,7 +27495,7 @@
         <v>https://www.helmwatches.com</v>
       </c>
       <c r="K91" t="str">
-        <v/>
+        <v>helmwatches</v>
       </c>
       <c r="L91" t="str">
         <v>MBWDB</v>
@@ -27594,7 +27594,7 @@
         <v>United States</v>
       </c>
       <c r="C94" t="str">
-        <v>Brooklyn</v>
+        <v>New York</v>
       </c>
       <c r="D94" t="str">
         <v/>
@@ -27804,11 +27804,11 @@
       <c r="D99">
         <v>2019</v>
       </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
-        <v/>
+      <c r="E99">
+        <v>195</v>
+      </c>
+      <c r="F99">
+        <v>395</v>
       </c>
       <c r="G99" t="str">
         <v>Active</v>
@@ -27878,10 +27878,10 @@
         <v>JEAN VERNIER</v>
       </c>
       <c r="B101" t="str">
-        <v>Brazil</v>
+        <v>United States</v>
       </c>
       <c r="C101" t="str">
-        <v>Rio de Janeiro</v>
+        <v>New York</v>
       </c>
       <c r="D101">
         <v>1991</v>
@@ -28004,7 +28004,7 @@
         <v>United States</v>
       </c>
       <c r="C104" t="str">
-        <v>Washington, DC</v>
+        <v>Washington, D.C.</v>
       </c>
       <c r="D104" t="str">
         <v/>
@@ -28086,7 +28086,7 @@
         <v>United States</v>
       </c>
       <c r="C106" t="str">
-        <v>Washington DC</v>
+        <v>Washington, D.C.</v>
       </c>
       <c r="D106" t="str">
         <v/>
@@ -28104,7 +28104,7 @@
         <v>Round Signature Shades</v>
       </c>
       <c r="I106" t="str">
-        <v/>
+        <v>2021-12-31</v>
       </c>
       <c r="J106" t="str">
         <v>https://www.kjosephwatches.com/</v>
@@ -28198,7 +28198,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M108" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Canadian microbrand based in Montreal. Specializes in automatic GMT watches designed for global travelers. Watches are hand-assembled and tested in Montreal with Miyota 9075 Japanese movements and 24-month warranty.</v>
       </c>
     </row>
     <row r="109">
@@ -28580,14 +28580,14 @@
       <c r="C118" t="str">
         <v/>
       </c>
-      <c r="D118" t="str">
-        <v/>
-      </c>
-      <c r="E118" t="str">
-        <v/>
-      </c>
-      <c r="F118" t="str">
-        <v/>
+      <c r="D118">
+        <v>2007</v>
+      </c>
+      <c r="E118">
+        <v>295</v>
+      </c>
+      <c r="F118">
+        <v>595</v>
       </c>
       <c r="G118" t="str">
         <v>Active</v>
@@ -28602,7 +28602,7 @@
         <v>https://www.maratac.com</v>
       </c>
       <c r="K118" t="str">
-        <v/>
+        <v>maratac</v>
       </c>
       <c r="L118" t="str">
         <v>MBWDB</v>
@@ -28783,7 +28783,7 @@
         <v>United States</v>
       </c>
       <c r="C123" t="str">
-        <v/>
+        <v>Chenoa</v>
       </c>
       <c r="D123">
         <v>2017</v>
@@ -29029,7 +29029,7 @@
         <v>United States</v>
       </c>
       <c r="C129" t="str">
-        <v>North Carolina</v>
+        <v>Charlotte</v>
       </c>
       <c r="D129" t="str">
         <v/>
@@ -29272,7 +29272,7 @@
         <v>Nodus Watches</v>
       </c>
       <c r="B135" t="str">
-        <v>USA</v>
+        <v>United States</v>
       </c>
       <c r="C135" t="str">
         <v>Los Angeles</v>
@@ -29357,7 +29357,7 @@
         <v>United States</v>
       </c>
       <c r="C137" t="str">
-        <v/>
+        <v>Portland</v>
       </c>
       <c r="D137">
         <v>2017</v>
@@ -29480,7 +29480,7 @@
         <v>Hong Kong</v>
       </c>
       <c r="C140" t="str">
-        <v/>
+        <v>Hong Kong</v>
       </c>
       <c r="D140" t="str">
         <v/>
@@ -29879,7 +29879,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M149" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>US-based microbrand assembling adventure-ready field watches. Cascadia Field Watch features 316L stainless steel case, sapphire crystal, Ameriquartz movement with 5-year warranty, and 100m water resistance. Emphasizes slow goods philosophy with American assembly and quick-release strap system.</v>
       </c>
     </row>
     <row r="150">
@@ -30056,14 +30056,14 @@
       <c r="C154" t="str">
         <v/>
       </c>
-      <c r="D154" t="str">
-        <v/>
-      </c>
-      <c r="E154" t="str">
-        <v/>
-      </c>
-      <c r="F154" t="str">
-        <v/>
+      <c r="D154">
+        <v>2010</v>
+      </c>
+      <c r="E154">
+        <v>295</v>
+      </c>
+      <c r="F154">
+        <v>595</v>
       </c>
       <c r="G154" t="str">
         <v>Active</v>
@@ -30177,7 +30177,7 @@
         <v>United States</v>
       </c>
       <c r="C157" t="str">
-        <v/>
+        <v>Agoura Hills</v>
       </c>
       <c r="D157">
         <v>2017</v>
@@ -30505,7 +30505,7 @@
         <v>United States</v>
       </c>
       <c r="C165" t="str">
-        <v/>
+        <v>Lancaster</v>
       </c>
       <c r="D165">
         <v>1992</v>
@@ -30874,7 +30874,7 @@
         <v>Puerto Rico</v>
       </c>
       <c r="C174" t="str">
-        <v>San Juan</v>
+        <v>Santurce</v>
       </c>
       <c r="D174" t="str">
         <v/>
@@ -31381,16 +31381,16 @@
         <v>Active</v>
       </c>
       <c r="H186" t="str">
-        <v/>
+        <v>Speidel x Life Is Good Watches</v>
       </c>
       <c r="I186" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J186" t="str">
         <v>https://www.speidel.com</v>
       </c>
       <c r="K186" t="str">
-        <v/>
+        <v>speidel1904</v>
       </c>
       <c r="L186" t="str">
         <v>MBWDB</v>
@@ -31876,7 +31876,7 @@
         <v>TIME BOLD - CX2</v>
       </c>
       <c r="I198" t="str">
-        <v/>
+        <v>2024-12-01</v>
       </c>
       <c r="J198" t="str">
         <v>https://torinocarrero.com/</v>
@@ -31888,7 +31888,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M198" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Torino Carrero is a US-based watch brand based in Encino, California. The brand offers diverse collections including automatic, quartz, chronograph, and multi-function watches for men and women, with models like Catania, Milazo, Avatar, and Gem Master series. Known for sport and diving watches with prices ranging from approximately $1,900 to $3,200.</v>
       </c>
     </row>
     <row r="199">
@@ -31899,10 +31899,10 @@
         <v>United States</v>
       </c>
       <c r="C199" t="str">
-        <v/>
-      </c>
-      <c r="D199" t="str">
-        <v/>
+        <v>New York</v>
+      </c>
+      <c r="D199">
+        <v>1993</v>
       </c>
       <c r="E199">
         <v>99</v>
@@ -31917,13 +31917,13 @@
         <v>TR-660</v>
       </c>
       <c r="I199" t="str">
-        <v/>
+        <v>2024-08-15</v>
       </c>
       <c r="J199" t="str">
         <v>https://www.tornekrayville.com</v>
       </c>
       <c r="K199" t="str">
-        <v/>
+        <v>tornekrayville</v>
       </c>
       <c r="L199" t="str">
         <v>MBWDB</v>
@@ -32019,7 +32019,7 @@
         <v>Trintec</v>
       </c>
       <c r="B202" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="C202" t="str">
         <v/>
@@ -32040,7 +32040,7 @@
         <v>CoPilot GMT</v>
       </c>
       <c r="I202" t="str">
-        <v/>
+        <v>2024-12-31</v>
       </c>
       <c r="J202" t="str">
         <v>https://www.trintecwatches.com</v>
@@ -32347,7 +32347,7 @@
         <v>VeriWatch</v>
       </c>
       <c r="B210" t="str">
-        <v>Italy</v>
+        <v>United States</v>
       </c>
       <c r="C210" t="str">
         <v/>
@@ -32432,7 +32432,7 @@
         <v>United States</v>
       </c>
       <c r="C212" t="str">
-        <v/>
+        <v>Austin</v>
       </c>
       <c r="D212">
         <v>2014</v>
@@ -32924,7 +32924,7 @@
         <v>United States</v>
       </c>
       <c r="C224" t="str">
-        <v/>
+        <v>Los Angeles</v>
       </c>
       <c r="D224">
         <v>2012</v>
@@ -33006,7 +33006,7 @@
         <v>Brazil</v>
       </c>
       <c r="C226" t="str">
-        <v>Rio</v>
+        <v>São Paulo</v>
       </c>
       <c r="D226" t="str">
         <v/>
@@ -33047,7 +33047,7 @@
         <v>Singapore</v>
       </c>
       <c r="C227" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="D227">
         <v>2014</v>
@@ -33196,7 +33196,7 @@
         <v>Hong Kong</v>
       </c>
       <c r="C3" t="str">
-        <v>Hong Kong</v>
+        <v>Kowloon</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -33319,7 +33319,7 @@
         <v>Netherlands</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Horst</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -33524,7 +33524,7 @@
         <v>China</v>
       </c>
       <c r="C11" t="str">
-        <v>Singapore, Singapore</v>
+        <v>Hong Kong</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -33565,7 +33565,7 @@
         <v>Indonesia</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>Jakarta</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -33624,7 +33624,7 @@
         <v>Ettore Drift</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>2024-12-23</v>
       </c>
       <c r="J13" t="str">
         <v>https://www.atowak.com</v>
@@ -33688,7 +33688,7 @@
         <v>Hong Kong</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>Hong Kong</v>
       </c>
       <c r="D15">
         <v>2010</v>
@@ -33729,7 +33729,7 @@
         <v>China</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>Dongguan</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -34062,11 +34062,11 @@
       <c r="D24">
         <v>1993</v>
       </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v/>
+      <c r="E24">
+        <v>19</v>
+      </c>
+      <c r="F24">
+        <v>175</v>
       </c>
       <c r="G24" t="str">
         <v>Active</v>
@@ -34081,7 +34081,7 @@
         <v>https://bureiwatches.com/</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>bureiwatches</v>
       </c>
       <c r="L24" t="str">
         <v>MBWDB</v>
@@ -34267,11 +34267,11 @@
       <c r="D29">
         <v>2019</v>
       </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v/>
+      <c r="E29">
+        <v>2200</v>
+      </c>
+      <c r="F29">
+        <v>2500</v>
       </c>
       <c r="G29" t="str">
         <v>Active</v>
@@ -34286,7 +34286,7 @@
         <v>https://linkandtag.com/2025/10/18/ckl-watches/</v>
       </c>
       <c r="K29" t="str">
-        <v/>
+        <v>linkandtag2017</v>
       </c>
       <c r="L29" t="str">
         <v>MBWDB</v>
@@ -34308,11 +34308,11 @@
       <c r="D30" t="str">
         <v/>
       </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-      <c r="F30" t="str">
-        <v/>
+      <c r="E30">
+        <v>153</v>
+      </c>
+      <c r="F30">
+        <v>228</v>
       </c>
       <c r="G30" t="str">
         <v>Active</v>
@@ -34327,7 +34327,7 @@
         <v>https://corgeutwatchco.com/</v>
       </c>
       <c r="K30" t="str">
-        <v/>
+        <v>corgeut_watches</v>
       </c>
       <c r="L30" t="str">
         <v>MBWDB</v>
@@ -34795,7 +34795,7 @@
         <v>Singapore</v>
       </c>
       <c r="C42" t="str">
-        <v>Geylang</v>
+        <v>Singapore</v>
       </c>
       <c r="D42" t="str">
         <v/>
@@ -34877,10 +34877,10 @@
         <v>China</v>
       </c>
       <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="D44" t="str">
-        <v/>
+        <v>Foshan</v>
+      </c>
+      <c r="D44">
+        <v>1989</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -34895,7 +34895,7 @@
         <v/>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>2025-01-01</v>
       </c>
       <c r="J44" t="str">
         <v>https://guanqin-watch.com/</v>
@@ -35082,7 +35082,7 @@
         <v>India</v>
       </c>
       <c r="C49" t="str">
-        <v/>
+        <v>Bangalore</v>
       </c>
       <c r="D49">
         <v>1949</v>
@@ -35393,7 +35393,7 @@
         <v>https://jaipur.watch/en-us</v>
       </c>
       <c r="K56" t="str">
-        <v/>
+        <v>jaipurwatchcompany</v>
       </c>
       <c r="L56" t="str">
         <v>MBWDB</v>
@@ -35410,7 +35410,7 @@
         <v>Singapore</v>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="D57" t="str">
         <v/>
@@ -35507,10 +35507,10 @@
         <v>Active</v>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>Classic Standard</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>2024-09-30</v>
       </c>
       <c r="J59" t="str">
         <v>http://www.kentexwatch.com/</v>
@@ -35533,16 +35533,16 @@
         <v>Japan</v>
       </c>
       <c r="C60" t="str">
-        <v>Asakusa</v>
+        <v>Tokyo</v>
       </c>
       <c r="D60">
         <v>2025</v>
       </c>
-      <c r="E60" t="str">
-        <v/>
-      </c>
-      <c r="F60" t="str">
-        <v/>
+      <c r="E60">
+        <v>650</v>
+      </c>
+      <c r="F60">
+        <v>690</v>
       </c>
       <c r="G60" t="str">
         <v>Active</v>
@@ -35557,7 +35557,7 @@
         <v>https://kiwametokyo.com/en/collections/watches</v>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>kiwametokyo</v>
       </c>
       <c r="L60" t="str">
         <v>MBWDB</v>
@@ -35620,17 +35620,17 @@
       <c r="D62">
         <v>2020</v>
       </c>
-      <c r="E62" t="str">
-        <v/>
-      </c>
-      <c r="F62" t="str">
-        <v/>
+      <c r="E62">
+        <v>596</v>
+      </c>
+      <c r="F62">
+        <v>889</v>
       </c>
       <c r="G62" t="str">
         <v>Active</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>ROYAL SMITH 90-010</v>
       </c>
       <c r="I62" t="str">
         <v>2026-04-04</v>
@@ -36096,7 +36096,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M73" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>KENKO Mayonnaise is a Japanese food company, not a watch brand. The homepage and provided content relate to mayonnaise and salad dressing products, not timepieces.</v>
       </c>
     </row>
     <row r="74">
@@ -36115,8 +36115,8 @@
       <c r="E74">
         <v>600</v>
       </c>
-      <c r="F74" t="str">
-        <v/>
+      <c r="F74">
+        <v>800</v>
       </c>
       <c r="G74" t="str">
         <v>Active</v>
@@ -36131,7 +36131,7 @@
         <v>https://www.melbournewatchco.com</v>
       </c>
       <c r="K74" t="str">
-        <v/>
+        <v>melbournewatchco</v>
       </c>
       <c r="L74" t="str">
         <v>MBWDB</v>
@@ -36153,11 +36153,11 @@
       <c r="D75">
         <v>2013</v>
       </c>
-      <c r="E75" t="str">
-        <v/>
-      </c>
-      <c r="F75" t="str">
-        <v/>
+      <c r="E75">
+        <v>400</v>
+      </c>
+      <c r="F75">
+        <v>800</v>
       </c>
       <c r="G75" t="str">
         <v>Active</v>
@@ -36172,7 +36172,7 @@
         <v>https://www.melbournewatchco.com</v>
       </c>
       <c r="K75" t="str">
-        <v/>
+        <v>melbournewatchcompany</v>
       </c>
       <c r="L75" t="str">
         <v>MBWDB</v>
@@ -36219,7 +36219,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M76" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Singapore-based microbrand founded in 2018 by Benjamin Chee HH. Specializes in classical dress watches with vintage-inspired design, including the Merveilleux collection featuring 1950s teardrop lug cases and Art Deco sector dials. Offers both standard handcrafted watches and a Haute Horlogerie Division using platinum, rose gold, and Swiss haute horlogerie movements from Vaucher Manufacture Fleurier.</v>
       </c>
     </row>
     <row r="77">
@@ -36353,7 +36353,7 @@
         <v>Singapore</v>
       </c>
       <c r="C80" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="D80" t="str">
         <v/>
@@ -36737,7 +36737,7 @@
         <v>Active</v>
       </c>
       <c r="H89" t="str">
-        <v/>
+        <v>Chronograph C-08</v>
       </c>
       <c r="I89" t="str">
         <v>2025-01-01</v>
@@ -36763,7 +36763,7 @@
         <v>Hong Kong</v>
       </c>
       <c r="C90" t="str">
-        <v/>
+        <v>Kowloon</v>
       </c>
       <c r="D90" t="str">
         <v/>
@@ -36806,14 +36806,14 @@
       <c r="C91" t="str">
         <v>Seoul</v>
       </c>
-      <c r="D91" t="str">
-        <v/>
+      <c r="D91">
+        <v>2021</v>
       </c>
       <c r="E91">
         <v>875</v>
       </c>
-      <c r="F91" t="str">
-        <v/>
+      <c r="F91">
+        <v>1499</v>
       </c>
       <c r="G91" t="str">
         <v>Active</v>
@@ -36828,7 +36828,7 @@
         <v>https://www.pitzmann.com/</v>
       </c>
       <c r="K91" t="str">
-        <v/>
+        <v>pitzmann_official</v>
       </c>
       <c r="L91" t="str">
         <v>MBWDB</v>
@@ -36968,7 +36968,7 @@
         <v>China</v>
       </c>
       <c r="C95" t="str">
-        <v/>
+        <v>Roma</v>
       </c>
       <c r="D95">
         <v>2019</v>
@@ -37088,10 +37088,10 @@
         <v>Relax</v>
       </c>
       <c r="B98" t="str">
-        <v>United States</v>
+        <v>China</v>
       </c>
       <c r="C98" t="str">
-        <v/>
+        <v>Guangzhou</v>
       </c>
       <c r="D98" t="str">
         <v/>
@@ -37132,7 +37132,7 @@
         <v>Singapore</v>
       </c>
       <c r="C99" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="D99">
         <v>2014</v>
@@ -37173,7 +37173,7 @@
         <v>Hong Kong</v>
       </c>
       <c r="C100" t="str">
-        <v/>
+        <v>Hong Kong</v>
       </c>
       <c r="D100" t="str">
         <v/>
@@ -37244,7 +37244,7 @@
         <v>MBWDB</v>
       </c>
       <c r="M101" t="str">
-        <v>Unknown brand — manual review needed</v>
+        <v>Singapore-based watch brand founded in 2020, specializing in titanium sports watches inspired by aerospace engineering. Known for durable adventure timepieces with UltraHEX™ titanium construction and models like Resolute, Valour, and Urbanist.</v>
       </c>
     </row>
     <row r="102">
@@ -37342,26 +37342,26 @@
       <c r="D104" t="str">
         <v/>
       </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
-        <v/>
+      <c r="E104">
+        <v>189</v>
+      </c>
+      <c r="F104">
+        <v>499</v>
       </c>
       <c r="G104" t="str">
         <v>Active</v>
       </c>
       <c r="H104" t="str">
-        <v/>
+        <v>MoonPhase Chrono Master S468</v>
       </c>
       <c r="I104" t="str">
-        <v/>
+        <v>2024-01-01</v>
       </c>
       <c r="J104" t="str">
         <v>https://sugesswatch.com/</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>sugess_watches</v>
       </c>
       <c r="L104" t="str">
         <v>MBWDB</v>
@@ -37542,7 +37542,7 @@
         <v>South Korea</v>
       </c>
       <c r="C109" t="str">
-        <v/>
+        <v>Seoul</v>
       </c>
       <c r="D109">
         <v>2017</v>
@@ -37588,26 +37588,26 @@
       <c r="D110" t="str">
         <v/>
       </c>
-      <c r="E110" t="str">
-        <v/>
-      </c>
-      <c r="F110" t="str">
-        <v/>
+      <c r="E110">
+        <v>208</v>
+      </c>
+      <c r="F110">
+        <v>640</v>
       </c>
       <c r="G110" t="str">
         <v>Active</v>
       </c>
       <c r="H110" t="str">
-        <v/>
+        <v>Fair Lady</v>
       </c>
       <c r="I110" t="str">
-        <v/>
+        <v>2024-10-01</v>
       </c>
       <c r="J110" t="str">
         <v>https://solvil-et-titus.sg/</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>solvilettitussg</v>
       </c>
       <c r="L110" t="str">
         <v>MBWDB</v>
@@ -37747,7 +37747,7 @@
         <v>Singapore</v>
       </c>
       <c r="C114" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="D114">
         <v>2014</v>
@@ -37834,11 +37834,11 @@
       <c r="D116">
         <v>2021</v>
       </c>
-      <c r="E116" t="str">
-        <v/>
-      </c>
-      <c r="F116" t="str">
-        <v/>
+      <c r="E116">
+        <v>66</v>
+      </c>
+      <c r="F116">
+        <v>3000</v>
       </c>
       <c r="G116" t="str">
         <v>Active</v>
@@ -37853,7 +37853,7 @@
         <v>https://wancherwatch.com/</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>wancherwatch_official</v>
       </c>
       <c r="L116" t="str">
         <v>MBWDB</v>
@@ -39864,7 +39864,7 @@
         <v>Switzerland</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>Bangkok</v>
       </c>
       <c r="D39" t="str">
         <v/>
@@ -40804,7 +40804,7 @@
         <v>Cronos</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>China</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -44638,7 +44638,7 @@
         <v>Invader</v>
       </c>
       <c r="I155" t="str">
-        <v/>
+        <v>2026-01-01</v>
       </c>
       <c r="J155" t="str">
         <v>https://poshmark.com/brand/MAGICO-Men</v>
@@ -45276,7 +45276,7 @@
         <v>Singapore</v>
       </c>
       <c r="C171" t="str">
-        <v/>
+        <v>Singapore</v>
       </c>
       <c r="D171">
         <v>2019</v>
@@ -50811,7 +50811,7 @@
         <v>United States</v>
       </c>
       <c r="C306" t="str">
-        <v>Los Angeles</v>
+        <v>Austin</v>
       </c>
       <c r="D306" t="str">
         <v/>
@@ -51386,7 +51386,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B74"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -51525,7 +51525,7 @@
         <v>Brazil</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -51541,7 +51541,7 @@
         <v>Canada</v>
       </c>
       <c r="B19">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -51557,7 +51557,7 @@
         <v>China</v>
       </c>
       <c r="B21">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -51573,7 +51573,7 @@
         <v>Czech Republic</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -51581,76 +51581,76 @@
         <v>Denmark</v>
       </c>
       <c r="B24">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>England</v>
+        <v>Finland</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Finland</v>
+        <v>France</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>France</v>
+        <v>France and Switzerland</v>
       </c>
       <c r="B27">
-        <v>80</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>France and Switzerland</v>
+        <v>Germany</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Germany</v>
+        <v>Hong Kong</v>
       </c>
       <c r="B29">
-        <v>87</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Hong Kong</v>
+        <v>Hungary</v>
       </c>
       <c r="B30">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Hungary</v>
+        <v>Iceland</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Iceland</v>
+        <v>India</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>India</v>
+        <v>Indonesia</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -51658,119 +51658,119 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Indonesia</v>
+        <v>Ireland</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ireland</v>
+        <v>Israel</v>
       </c>
       <c r="B35">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Israel</v>
+        <v>Italy</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Italy</v>
+        <v>Jamaica</v>
       </c>
       <c r="B37">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Jamaica</v>
+        <v>Japan</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Japan</v>
+        <v>Jordan</v>
       </c>
       <c r="B39">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Jordan</v>
+        <v>Lithuania</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lithuania</v>
+        <v>Macau</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Macau</v>
+        <v>Malaysia</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Malaysia</v>
+        <v>Netherlands</v>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Netherlands</v>
+        <v>New Zealand</v>
       </c>
       <c r="B44">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>New Zealand</v>
+        <v>Norway</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Norway</v>
+        <v>null</v>
       </c>
       <c r="B46">
-        <v>9</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>null</v>
+        <v>Pakistan</v>
       </c>
       <c r="B47">
-        <v>139</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Pakistan</v>
+        <v>Peru</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -51778,39 +51778,39 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Peru</v>
+        <v>Philippines</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Philippines</v>
+        <v>Poland</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Poland</v>
+        <v>Portugal</v>
       </c>
       <c r="B51">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Portugal</v>
+        <v>Puerto Rico</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Puerto Rico</v>
+        <v>Romania</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -51818,31 +51818,31 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Romania</v>
+        <v>Russia</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Russia</v>
+        <v>Singapore</v>
       </c>
       <c r="B55">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Singapore</v>
+        <v>Slovakia</v>
       </c>
       <c r="B56">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Slovakia</v>
+        <v>Slovenia</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -51850,95 +51850,95 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Slovenia</v>
+        <v>South Africa</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>South Africa</v>
+        <v>South Korea</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>South Korea</v>
+        <v>Soviet Union</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Soviet Union</v>
+        <v>Spain</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Spain</v>
+        <v>Sweden</v>
       </c>
       <c r="B62">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Sweden</v>
+        <v>Switzerland</v>
       </c>
       <c r="B63">
-        <v>21</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Switzerland</v>
+        <v>Taiwan</v>
       </c>
       <c r="B64">
-        <v>177</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Taiwan</v>
+        <v>Thailand</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Thailand</v>
+        <v>United Kingdom</v>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>110</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>United Kingdom</v>
+        <v>United States</v>
       </c>
       <c r="B67">
-        <v>108</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>United States</v>
+        <v>Unknown</v>
       </c>
       <c r="B68">
-        <v>222</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Unknown</v>
+        <v>Vietnam</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -51946,63 +51946,47 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>USA</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
+        <v/>
+      </c>
+      <c r="B70" t="str">
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Vietnam</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
+        <v>Status</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Count</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v/>
-      </c>
-      <c r="B72" t="str">
-        <v/>
+        <v>Active</v>
+      </c>
+      <c r="B72">
+        <v>1236</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Status</v>
-      </c>
-      <c r="B73" t="str">
-        <v>Count</v>
+        <v>Dormant</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Active</v>
+        <v>Defunct</v>
       </c>
       <c r="B74">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Dormant</v>
-      </c>
-      <c r="B75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Defunct</v>
-      </c>
-      <c r="B76">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B76"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B74"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/watch-microbrand-database.xlsx
+++ b/watch-microbrand-database.xlsx
@@ -56776,7 +56776,7 @@
         <v>Last Updated</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-26</v>
       </c>
     </row>
     <row r="3">
